--- a/research/traditional_assets/database/data/spain/spain_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_drugs_biotechnology.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,121 +590,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07150000000000001</v>
+        <v>0.0415</v>
       </c>
       <c r="E2">
         <v>-0.218</v>
       </c>
       <c r="F2">
-        <v>0.456</v>
+        <v>0.7705</v>
       </c>
       <c r="G2">
-        <v>0.2005861199626316</v>
+        <v>0.211091690290242</v>
       </c>
       <c r="H2">
-        <v>0.1459797033567525</v>
+        <v>0.1428708859684083</v>
       </c>
       <c r="I2">
-        <v>0.1386851972715988</v>
+        <v>0.1346387623203869</v>
       </c>
       <c r="J2">
-        <v>0.08729317322604783</v>
+        <v>0.1180079114274787</v>
       </c>
       <c r="K2">
-        <v>180.1</v>
+        <v>177.524</v>
       </c>
       <c r="L2">
-        <v>0.02304807975326653</v>
+        <v>0.02217938258447953</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>30.889</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.004203042508028085</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1739990085847547</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.001728079246720731</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.07153962281156351</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>18.189</v>
+      </c>
+      <c r="T2">
+        <v>0.5888503998187057</v>
       </c>
       <c r="U2">
-        <v>719.3</v>
+        <v>758.751</v>
       </c>
       <c r="V2">
-        <v>0.1222966539717084</v>
+        <v>0.1032426658683938</v>
       </c>
       <c r="W2">
-        <v>0.02777135279332624</v>
+        <v>0.003180568285976168</v>
       </c>
       <c r="X2">
-        <v>0.2242173859816904</v>
+        <v>0.128046427671559</v>
       </c>
       <c r="Y2">
-        <v>-0.1964460331883642</v>
+        <v>-0.1248658593855829</v>
       </c>
       <c r="Z2">
-        <v>0.4420915062262026</v>
+        <v>0.4477635820191483</v>
       </c>
       <c r="AA2">
-        <v>0.0385915704347683</v>
+        <v>-0.02076761303890641</v>
       </c>
       <c r="AB2">
-        <v>0.1210266186172968</v>
+        <v>0.1196439377999284</v>
       </c>
       <c r="AC2">
-        <v>-0.08243504818252853</v>
+        <v>-0.1404115508388348</v>
       </c>
       <c r="AD2">
-        <v>10989.4</v>
+        <v>11051.66</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10989.4</v>
+        <v>11051.66</v>
       </c>
       <c r="AG2">
-        <v>10270.1</v>
+        <v>10292.909</v>
       </c>
       <c r="AH2">
-        <v>0.6513781044395709</v>
+        <v>0.6006056238675801</v>
       </c>
       <c r="AI2">
-        <v>0.552050837666089</v>
+        <v>0.5476622546420412</v>
       </c>
       <c r="AJ2">
-        <v>0.635852572794195</v>
+        <v>0.5834284891902662</v>
       </c>
       <c r="AK2">
-        <v>0.5352578802535023</v>
+        <v>0.5299900123315292</v>
       </c>
       <c r="AL2">
-        <v>673.9</v>
+        <v>676.885</v>
       </c>
       <c r="AM2">
-        <v>604.4</v>
+        <v>603.5839999999999</v>
       </c>
       <c r="AN2">
-        <v>7.826093149124056</v>
+        <v>7.883748933535355</v>
       </c>
       <c r="AO2">
-        <v>1.608102092298561</v>
+        <v>1.592072508624065</v>
       </c>
       <c r="AP2">
-        <v>7.313844181740492</v>
+        <v>7.342490662192509</v>
       </c>
       <c r="AQ2">
-        <v>1.793017868960953</v>
+        <v>1.785418433888241</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +784,10 @@
         <v>0.02777135279332624</v>
       </c>
       <c r="X3">
-        <v>0.2242173859816904</v>
+        <v>0.2241691131292655</v>
       </c>
       <c r="Y3">
-        <v>-0.1964460331883642</v>
+        <v>-0.1963977603359393</v>
       </c>
       <c r="Z3">
         <v>0.4420915062262026</v>
@@ -793,10 +796,10 @@
         <v>0.0385915704347683</v>
       </c>
       <c r="AB3">
-        <v>0.1210266186172968</v>
+        <v>0.1210097896439803</v>
       </c>
       <c r="AC3">
-        <v>-0.08243504818252853</v>
+        <v>-0.08241821920921205</v>
       </c>
       <c r="AD3">
         <v>10989.4</v>
@@ -839,6 +842,271 @@
       </c>
       <c r="AQ3">
         <v>1.793017868960953</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pharma Mar, S.A. (BME:PHM)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Drugs (Biotechnology)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0415</v>
+      </c>
+      <c r="F4">
+        <v>1.085</v>
+      </c>
+      <c r="G4">
+        <v>0.6217391304347826</v>
+      </c>
+      <c r="H4">
+        <v>-0.006816961889425657</v>
+      </c>
+      <c r="I4">
+        <v>-0.02120236178207193</v>
+      </c>
+      <c r="J4">
+        <v>-0.02120236178207193</v>
+      </c>
+      <c r="K4">
+        <v>0.694</v>
+      </c>
+      <c r="L4">
+        <v>0.003725174449812131</v>
+      </c>
+      <c r="M4">
+        <v>30.7</v>
+      </c>
+      <c r="N4">
+        <v>0.02118702553485162</v>
+      </c>
+      <c r="O4">
+        <v>44.23631123919309</v>
+      </c>
+      <c r="P4">
+        <v>12.7</v>
+      </c>
+      <c r="Q4">
+        <v>0.008764665286404417</v>
+      </c>
+      <c r="R4">
+        <v>18.29971181556196</v>
+      </c>
+      <c r="S4">
+        <v>18</v>
+      </c>
+      <c r="T4">
+        <v>0.5863192182410424</v>
+      </c>
+      <c r="U4">
+        <v>38.8</v>
+      </c>
+      <c r="V4">
+        <v>0.02677708764665286</v>
+      </c>
+      <c r="W4">
+        <v>0.003180568285976168</v>
+      </c>
+      <c r="X4">
+        <v>0.122370800454657</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1191902321686808</v>
+      </c>
+      <c r="Z4">
+        <v>0.9794952681388013</v>
+      </c>
+      <c r="AA4">
+        <v>-0.02076761303890641</v>
+      </c>
+      <c r="AB4">
+        <v>0.1196439377999284</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1404115508388348</v>
+      </c>
+      <c r="AD4">
+        <v>59.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>59.6</v>
+      </c>
+      <c r="AG4">
+        <v>20.8</v>
+      </c>
+      <c r="AH4">
+        <v>0.03950682752220602</v>
+      </c>
+      <c r="AI4">
+        <v>0.2267884322678843</v>
+      </c>
+      <c r="AJ4">
+        <v>0.01415158524969384</v>
+      </c>
+      <c r="AK4">
+        <v>0.09285714285714287</v>
+      </c>
+      <c r="AL4">
+        <v>2.69</v>
+      </c>
+      <c r="AM4">
+        <v>-1.11</v>
+      </c>
+      <c r="AN4">
+        <v>-112.0300751879699</v>
+      </c>
+      <c r="AO4">
+        <v>-1.468401486988848</v>
+      </c>
+      <c r="AP4">
+        <v>-39.09774436090226</v>
+      </c>
+      <c r="AQ4">
+        <v>3.558558558558559</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Biotechnology Assets, S.A. (BME:BST)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Drugs (Biotechnology)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.382</v>
+      </c>
+      <c r="G5">
+        <v>1.759002770083103</v>
+      </c>
+      <c r="H5">
+        <v>1.138504155124654</v>
+      </c>
+      <c r="I5">
+        <v>-0.5817174515235457</v>
+      </c>
+      <c r="J5">
+        <v>-0.5817174515235457</v>
+      </c>
+      <c r="K5">
+        <v>-3.27</v>
+      </c>
+      <c r="L5">
+        <v>-0.9058171745152355</v>
+      </c>
+      <c r="M5">
+        <v>0.189</v>
+      </c>
+      <c r="N5">
+        <v>0.01016129032258064</v>
+      </c>
+      <c r="O5">
+        <v>-0.05779816513761468</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0.189</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>0.651</v>
+      </c>
+      <c r="V5">
+        <v>0.035</v>
+      </c>
+      <c r="W5">
+        <v>-0.3793503480278423</v>
+      </c>
+      <c r="X5">
+        <v>0.128046427671559</v>
+      </c>
+      <c r="Y5">
+        <v>-0.5073967756994013</v>
+      </c>
+      <c r="Z5">
+        <v>0.3600279246035704</v>
+      </c>
+      <c r="AA5">
+        <v>-0.2094345267777003</v>
+      </c>
+      <c r="AB5">
+        <v>0.1189349649734562</v>
+      </c>
+      <c r="AC5">
+        <v>-0.3283694917511565</v>
+      </c>
+      <c r="AD5">
+        <v>2.66</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.66</v>
+      </c>
+      <c r="AG5">
+        <v>2.009</v>
+      </c>
+      <c r="AH5">
+        <v>0.1251175917215428</v>
+      </c>
+      <c r="AI5">
+        <v>0.2557692307692307</v>
+      </c>
+      <c r="AJ5">
+        <v>0.09748168275995925</v>
+      </c>
+      <c r="AK5">
+        <v>0.206072417683865</v>
+      </c>
+      <c r="AL5">
+        <v>0.295</v>
+      </c>
+      <c r="AM5">
+        <v>0.294</v>
+      </c>
+      <c r="AN5">
+        <v>-1.445652173913043</v>
+      </c>
+      <c r="AO5">
+        <v>-7.118644067796611</v>
+      </c>
+      <c r="AP5">
+        <v>-1.091847826086957</v>
+      </c>
+      <c r="AQ5">
+        <v>-7.142857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -1133,49 +1401,49 @@
         <v>1.60810209229856</v>
       </c>
       <c r="F2">
-        <v>3.03530137149493</v>
+        <v>3.06557554146558</v>
       </c>
       <c r="G2">
         <v>7.82609314912406</v>
       </c>
       <c r="H2">
-        <v>4.56557470445805</v>
+        <v>4.68572140720695</v>
       </c>
       <c r="I2">
         <v>0.651378104439571</v>
       </c>
       <c r="J2">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="K2">
         <v>5881.6</v>
       </c>
       <c r="L2">
-        <v>11033.2947985216</v>
+        <v>10981.0496205623</v>
       </c>
       <c r="M2">
         <v>16151.7</v>
       </c>
       <c r="N2">
-        <v>16724.9747985216</v>
+        <v>16841.4396205623</v>
       </c>
       <c r="O2">
         <v>10989.4</v>
       </c>
       <c r="P2">
-        <v>6410.98</v>
+        <v>6579.69</v>
       </c>
       <c r="Q2">
-        <v>0.121026618617297</v>
+        <v>0.12100978964398</v>
       </c>
       <c r="R2">
-        <v>0.116650348239759</v>
+        <v>0.11578093933417</v>
       </c>
       <c r="S2">
         <v>0.06579823332506821</v>
       </c>
       <c r="T2">
-        <v>0.0552982333250682</v>
+        <v>0.0533482333250682</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1456,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.22421738598169</v>
+        <v>0.224169113129266</v>
       </c>
       <c r="X2">
-        <v>0.154253257381022</v>
+        <v>0.155696931700646</v>
       </c>
       <c r="Y2">
         <v>2.75931345193403</v>
       </c>
       <c r="Z2">
-        <v>1.67728346848567</v>
+        <v>1.70007058199648</v>
       </c>
       <c r="AA2">
         <v>10989.4</v>
@@ -1230,7 +1498,7 @@
         <v>5881.6</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1200994691450093</v>
+        <v>0.1200793665788297</v>
       </c>
       <c r="C2">
-        <v>16989.14802987886</v>
+        <v>16989.57004404403</v>
       </c>
       <c r="D2">
-        <v>16269.84802987886</v>
+        <v>16270.27004404403</v>
       </c>
       <c r="E2">
         <v>-10989.4</v>
@@ -1469,19 +1737,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1200994691450093</v>
+        <v>0.1200793665788297</v>
       </c>
       <c r="T2">
         <v>1.149078177305102</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1768,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1199622028053974</v>
+        <v>0.1199316504956333</v>
       </c>
       <c r="C3">
-        <v>16838.07713822349</v>
+        <v>16839.84481116528</v>
       </c>
       <c r="D3">
-        <v>16287.48713822348</v>
+        <v>16289.25481116528</v>
       </c>
       <c r="E3">
         <v>-10820.69</v>
@@ -1533,37 +1801,37 @@
         <v>1434.75</v>
       </c>
       <c r="M3">
-        <v>11.39315125902967</v>
+        <v>11.15695725902967</v>
       </c>
       <c r="N3">
-        <v>1423.35684874097</v>
+        <v>1423.59304274097</v>
       </c>
       <c r="O3">
-        <v>355.8392121852426</v>
+        <v>355.8982606852426</v>
       </c>
       <c r="P3">
-        <v>1067.517636555728</v>
+        <v>1067.694782055728</v>
       </c>
       <c r="Q3">
-        <v>1388.017636555728</v>
+        <v>1388.194782055728</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1206623439112594</v>
+        <v>0.1206420890529117</v>
       </c>
       <c r="T3">
         <v>1.157783315011959</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1839,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>125.9309182666108</v>
+        <v>128.5968895183149</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1850,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1198249364657856</v>
+        <v>0.1197839344124369</v>
       </c>
       <c r="C4">
-        <v>16687.04453528869</v>
+        <v>16690.16393433302</v>
       </c>
       <c r="D4">
-        <v>16305.16453528869</v>
+        <v>16308.28393433302</v>
       </c>
       <c r="E4">
         <v>-10651.98</v>
@@ -1615,37 +1883,37 @@
         <v>1434.75</v>
       </c>
       <c r="M4">
-        <v>22.78630251805935</v>
+        <v>22.31391451805935</v>
       </c>
       <c r="N4">
-        <v>1411.963697481941</v>
+        <v>1412.436085481941</v>
       </c>
       <c r="O4">
-        <v>352.9909243704852</v>
+        <v>353.1090213704852</v>
       </c>
       <c r="P4">
-        <v>1058.972773111456</v>
+        <v>1059.327064111455</v>
       </c>
       <c r="Q4">
-        <v>1379.472773111456</v>
+        <v>1379.827064111455</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.121236705917637</v>
+        <v>0.1212162956591179</v>
       </c>
       <c r="T4">
         <v>1.166666108590384</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1921,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.96545913330541</v>
+        <v>64.29844475915743</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1932,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1196876701261738</v>
+        <v>0.1196362183292405</v>
       </c>
       <c r="C5">
-        <v>16536.05034587833</v>
+        <v>16540.52756917939</v>
       </c>
       <c r="D5">
-        <v>16322.88034587833</v>
+        <v>16327.3575691794</v>
       </c>
       <c r="E5">
         <v>-10483.27</v>
@@ -1697,37 +1965,37 @@
         <v>1434.75</v>
       </c>
       <c r="M5">
-        <v>34.17945377708902</v>
+        <v>33.47087177708902</v>
       </c>
       <c r="N5">
-        <v>1400.570546222911</v>
+        <v>1401.279128222911</v>
       </c>
       <c r="O5">
-        <v>350.1426365557277</v>
+        <v>350.3197820557277</v>
       </c>
       <c r="P5">
-        <v>1050.427909667183</v>
+        <v>1050.959346167183</v>
       </c>
       <c r="Q5">
-        <v>1370.927909667183</v>
+        <v>1371.459346167183</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.12182291043961</v>
+        <v>0.1218023415767922</v>
       </c>
       <c r="T5">
         <v>1.17573205255187</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +2003,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.97697275553693</v>
+        <v>42.86562983943828</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +2014,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1195504037865619</v>
+        <v>0.1194885022460441</v>
       </c>
       <c r="C6">
-        <v>16385.09469533924</v>
+        <v>16390.93587206547</v>
       </c>
       <c r="D6">
-        <v>16340.63469533924</v>
+        <v>16346.47587206548</v>
       </c>
       <c r="E6">
         <v>-10314.56</v>
@@ -1779,37 +2047,37 @@
         <v>1434.75</v>
       </c>
       <c r="M6">
-        <v>45.57260503611869</v>
+        <v>44.6278290361187</v>
       </c>
       <c r="N6">
-        <v>1389.177394963881</v>
+        <v>1390.122170963881</v>
       </c>
       <c r="O6">
-        <v>347.2943487409703</v>
+        <v>347.5305427409703</v>
       </c>
       <c r="P6">
-        <v>1041.883046222911</v>
+        <v>1042.591628222911</v>
       </c>
       <c r="Q6">
-        <v>1362.383046222911</v>
+        <v>1363.091628222911</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1224213275557908</v>
+        <v>0.1224005967844181</v>
       </c>
       <c r="T6">
         <v>1.184986870345887</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +2085,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.48272956665271</v>
+        <v>32.14922237957872</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +2096,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1194131374469501</v>
+        <v>0.1193407861628478</v>
       </c>
       <c r="C7">
-        <v>16234.17770956421</v>
+        <v>16241.38900008556</v>
       </c>
       <c r="D7">
-        <v>16358.4277095642</v>
+        <v>16365.63900008556</v>
       </c>
       <c r="E7">
         <v>-10145.85</v>
@@ -1861,37 +2129,37 @@
         <v>1434.75</v>
       </c>
       <c r="M7">
-        <v>56.96575629514837</v>
+        <v>55.78478629514837</v>
       </c>
       <c r="N7">
-        <v>1377.784243704852</v>
+        <v>1378.965213704852</v>
       </c>
       <c r="O7">
-        <v>344.4460609262129</v>
+        <v>344.7413034262129</v>
       </c>
       <c r="P7">
-        <v>1033.338182778639</v>
+        <v>1034.223910278639</v>
       </c>
       <c r="Q7">
-        <v>1353.838182778639</v>
+        <v>1354.723910278639</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1230323429270491</v>
+        <v>0.1230114468385204</v>
       </c>
       <c r="T7">
         <v>1.194436526409251</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2167,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.18618365332216</v>
+        <v>25.71937790366297</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2178,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1192758711073382</v>
+        <v>0.1191930700796514</v>
       </c>
       <c r="C8">
-        <v>16083.29951499494</v>
+        <v>16091.88711107146</v>
       </c>
       <c r="D8">
-        <v>16376.25951499494</v>
+        <v>16384.84711107146</v>
       </c>
       <c r="E8">
         <v>-9977.139999999999</v>
@@ -1943,37 +2211,37 @@
         <v>1434.75</v>
       </c>
       <c r="M8">
-        <v>68.35890755417805</v>
+        <v>66.94174355417805</v>
       </c>
       <c r="N8">
-        <v>1366.391092445822</v>
+        <v>1367.808256445822</v>
       </c>
       <c r="O8">
-        <v>341.5977731114555</v>
+        <v>341.9520641114555</v>
       </c>
       <c r="P8">
-        <v>1024.793319334367</v>
+        <v>1025.856192334367</v>
       </c>
       <c r="Q8">
-        <v>1345.293319334367</v>
+        <v>1346.356192334367</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1236563586253555</v>
+        <v>0.1236352937022843</v>
       </c>
       <c r="T8">
         <v>1.204087238984602</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2249,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.98848637776847</v>
+        <v>21.43281491971915</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2260,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1191386047677264</v>
+        <v>0.119045353996455</v>
       </c>
       <c r="C9">
-        <v>15932.46023862509</v>
+        <v>15942.43036359684</v>
       </c>
       <c r="D9">
-        <v>16394.13023862509</v>
+        <v>16404.10036359684</v>
       </c>
       <c r="E9">
         <v>-9808.43</v>
@@ -2025,37 +2293,37 @@
         <v>1434.75</v>
       </c>
       <c r="M9">
-        <v>79.75205881320771</v>
+        <v>78.09870081320771</v>
       </c>
       <c r="N9">
-        <v>1354.997941186792</v>
+        <v>1356.651299186792</v>
       </c>
       <c r="O9">
-        <v>338.7494852966981</v>
+        <v>339.1628247966981</v>
       </c>
       <c r="P9">
-        <v>1016.248455890094</v>
+        <v>1017.488474390094</v>
       </c>
       <c r="Q9">
-        <v>1336.748455890094</v>
+        <v>1337.988474390094</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1242937940160985</v>
+        <v>0.1242725566276346</v>
       </c>
       <c r="T9">
         <v>1.213945493765874</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2331,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.99013118094441</v>
+        <v>18.37098421690213</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2342,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1190013384281146</v>
+        <v>0.1188976379132586</v>
       </c>
       <c r="C10">
-        <v>15781.66000800321</v>
+        <v>15793.01891698157</v>
       </c>
       <c r="D10">
-        <v>16412.04000800321</v>
+        <v>16423.39891698157</v>
       </c>
       <c r="E10">
         <v>-9639.719999999999</v>
@@ -2107,37 +2375,37 @@
         <v>1434.75</v>
       </c>
       <c r="M10">
-        <v>91.14521007223739</v>
+        <v>89.2556580722374</v>
       </c>
       <c r="N10">
-        <v>1343.604789927763</v>
+        <v>1345.494341927763</v>
       </c>
       <c r="O10">
-        <v>335.9011974819406</v>
+        <v>336.3735854819407</v>
       </c>
       <c r="P10">
-        <v>1007.703592445822</v>
+        <v>1009.120756445822</v>
       </c>
       <c r="Q10">
-        <v>1328.203592445822</v>
+        <v>1329.620756445822</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1249450866979447</v>
+        <v>0.1249236730948403</v>
       </c>
       <c r="T10">
         <v>1.224018058433696</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2413,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.74136478332635</v>
+        <v>16.07461118978936</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2424,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1188640720885027</v>
+        <v>0.1187499218300622</v>
       </c>
       <c r="C11">
-        <v>15630.89895123586</v>
+        <v>15643.65293129614</v>
       </c>
       <c r="D11">
-        <v>16429.98895123586</v>
+        <v>16442.74293129614</v>
       </c>
       <c r="E11">
         <v>-9471.01</v>
@@ -2189,37 +2457,37 @@
         <v>1434.75</v>
       </c>
       <c r="M11">
-        <v>102.5383613312671</v>
+        <v>100.4126153312671</v>
       </c>
       <c r="N11">
-        <v>1332.211638668733</v>
+        <v>1334.337384668733</v>
       </c>
       <c r="O11">
-        <v>333.0529096671833</v>
+        <v>333.5843461671832</v>
       </c>
       <c r="P11">
-        <v>999.1587290015498</v>
+        <v>1000.75303850155</v>
       </c>
       <c r="Q11">
-        <v>1319.65872900155</v>
+        <v>1321.25303850155</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1256106935046666</v>
+        <v>0.1255890998140726</v>
       </c>
       <c r="T11">
         <v>1.234311998149162</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2495,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.99232425184565</v>
+        <v>14.28854327981276</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2506,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1187268057488909</v>
+        <v>0.1186022057468658</v>
       </c>
       <c r="C12">
-        <v>15480.17719699061</v>
+        <v>15494.33256736606</v>
       </c>
       <c r="D12">
-        <v>16447.97719699061</v>
+        <v>16462.13256736606</v>
       </c>
       <c r="E12">
         <v>-9302.299999999999</v>
@@ -2271,37 +2539,37 @@
         <v>1434.75</v>
       </c>
       <c r="M12">
-        <v>113.9315125902967</v>
+        <v>111.5695725902967</v>
       </c>
       <c r="N12">
-        <v>1320.818487409703</v>
+        <v>1323.180427409703</v>
       </c>
       <c r="O12">
-        <v>330.2046218524258</v>
+        <v>330.7951068524258</v>
       </c>
       <c r="P12">
-        <v>990.6138655572774</v>
+        <v>992.3853205572775</v>
       </c>
       <c r="Q12">
-        <v>1311.113865557277</v>
+        <v>1312.885320557278</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1262910915737601</v>
+        <v>0.1262693137937322</v>
       </c>
       <c r="T12">
         <v>1.244834692080527</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2577,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.59309182666108</v>
+        <v>12.85968895183149</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2588,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.118589539409279</v>
+        <v>0.1184544896636694</v>
       </c>
       <c r="C13">
-        <v>15329.49487449913</v>
+        <v>15345.05798677635</v>
       </c>
       <c r="D13">
-        <v>16466.00487449913</v>
+        <v>16481.56798677635</v>
       </c>
       <c r="E13">
         <v>-9133.59</v>
@@ -2353,37 +2621,37 @@
         <v>1434.75</v>
       </c>
       <c r="M13">
-        <v>125.3246638493264</v>
+        <v>122.7265298493264</v>
       </c>
       <c r="N13">
-        <v>1309.425336150674</v>
+        <v>1312.023470150674</v>
       </c>
       <c r="O13">
-        <v>327.3563340376684</v>
+        <v>328.0058675376684</v>
       </c>
       <c r="P13">
-        <v>982.0690021130051</v>
+        <v>984.0176026130052</v>
       </c>
       <c r="Q13">
-        <v>1302.569002113005</v>
+        <v>1304.517602613005</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1269867794871029</v>
+        <v>0.1269648134807999</v>
       </c>
       <c r="T13">
         <v>1.255593851044058</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2659,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.44826529696462</v>
+        <v>11.69062631984681</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2670,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1184522730696672</v>
+        <v>0.118306773580473</v>
       </c>
       <c r="C14">
-        <v>15178.85211356028</v>
+        <v>15195.829351876</v>
       </c>
       <c r="D14">
-        <v>16484.07211356028</v>
+        <v>16501.049351876</v>
       </c>
       <c r="E14">
         <v>-8964.879999999999</v>
@@ -2435,37 +2703,37 @@
         <v>1434.75</v>
       </c>
       <c r="M14">
-        <v>136.7178151083561</v>
+        <v>133.8834871083561</v>
       </c>
       <c r="N14">
-        <v>1298.032184891644</v>
+        <v>1300.866512891644</v>
       </c>
       <c r="O14">
-        <v>324.508046222911</v>
+        <v>325.216628222911</v>
       </c>
       <c r="P14">
-        <v>973.524138668733</v>
+        <v>975.649884668733</v>
       </c>
       <c r="Q14">
-        <v>1294.024138668733</v>
+        <v>1296.149884668733</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1276982784893853</v>
+        <v>0.1276761199789373</v>
       </c>
       <c r="T14">
         <v>1.26659753634767</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2741,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.49424318888424</v>
+        <v>10.71640745985957</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2752,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1183150067300554</v>
+        <v>0.1181590574972766</v>
       </c>
       <c r="C15">
-        <v>15028.24904454324</v>
+        <v>15046.64682578249</v>
       </c>
       <c r="D15">
-        <v>16502.17904454325</v>
+        <v>16520.57682578249</v>
       </c>
       <c r="E15">
         <v>-8796.17</v>
@@ -2517,37 +2785,37 @@
         <v>1434.75</v>
       </c>
       <c r="M15">
-        <v>148.1109663673858</v>
+        <v>145.0404443673858</v>
       </c>
       <c r="N15">
-        <v>1286.639033632614</v>
+        <v>1289.709555632614</v>
       </c>
       <c r="O15">
-        <v>321.6597584081536</v>
+        <v>322.4273889081535</v>
       </c>
       <c r="P15">
-        <v>964.9792752244607</v>
+        <v>967.2821667244607</v>
       </c>
       <c r="Q15">
-        <v>1285.479275224461</v>
+        <v>1287.782166724461</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1284261337905707</v>
+        <v>0.1284037783505951</v>
       </c>
       <c r="T15">
         <v>1.277854179934122</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2823,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.686993712816216</v>
+        <v>9.892068424485759</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2834,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1181777403904435</v>
+        <v>0.1180113414140802</v>
       </c>
       <c r="C16">
-        <v>14877.68579839065</v>
+        <v>14897.51057238636</v>
       </c>
       <c r="D16">
-        <v>16520.32579839065</v>
+        <v>16540.15057238636</v>
       </c>
       <c r="E16">
         <v>-8627.459999999999</v>
@@ -2599,37 +2867,37 @@
         <v>1434.75</v>
       </c>
       <c r="M16">
-        <v>159.5041176264154</v>
+        <v>156.1974016264154</v>
       </c>
       <c r="N16">
-        <v>1275.245882373585</v>
+        <v>1278.552598373584</v>
       </c>
       <c r="O16">
-        <v>318.8114705933962</v>
+        <v>319.6381495933961</v>
       </c>
       <c r="P16">
-        <v>956.4344117801885</v>
+        <v>958.9144487801884</v>
       </c>
       <c r="Q16">
-        <v>1276.934411780188</v>
+        <v>1279.414448780188</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1291709159592255</v>
+        <v>0.1291483590099659</v>
       </c>
       <c r="T16">
         <v>1.289372605929562</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2905,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.995065590472201</v>
+        <v>9.185492108451061</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2916,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1181642240508317</v>
+        <v>0.1180323753308838</v>
       </c>
       <c r="C17">
-        <v>14710.76483131128</v>
+        <v>14726.01055237468</v>
       </c>
       <c r="D17">
-        <v>16522.11483131128</v>
+        <v>16537.36055237468</v>
       </c>
       <c r="E17">
         <v>-8458.75</v>
@@ -2681,37 +2949,37 @@
         <v>1434.75</v>
       </c>
       <c r="M17">
-        <v>173.6809838854451</v>
+        <v>171.1503338854451</v>
       </c>
       <c r="N17">
-        <v>1261.069016114555</v>
+        <v>1263.599666114555</v>
       </c>
       <c r="O17">
-        <v>315.2672540286387</v>
+        <v>315.8999165286388</v>
       </c>
       <c r="P17">
-        <v>945.8017620859162</v>
+        <v>947.6997495859163</v>
       </c>
       <c r="Q17">
-        <v>1266.301762085916</v>
+        <v>1268.199749585916</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1299332224142017</v>
+        <v>0.129910459214263</v>
       </c>
       <c r="T17">
         <v>1.30116205371313</v>
       </c>
       <c r="U17">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2987,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.260835284917082</v>
+        <v>8.382981016912954</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2998,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1180352077112198</v>
+        <v>0.1178959092476874</v>
       </c>
       <c r="C18">
-        <v>14559.15105275039</v>
+        <v>14575.41871601075</v>
       </c>
       <c r="D18">
-        <v>16539.21105275039</v>
+        <v>16555.47871601075</v>
       </c>
       <c r="E18">
         <v>-8290.039999999999</v>
@@ -2763,37 +3031,37 @@
         <v>1434.75</v>
       </c>
       <c r="M18">
-        <v>185.2597161444748</v>
+        <v>182.5603561444748</v>
       </c>
       <c r="N18">
-        <v>1249.490283855525</v>
+        <v>1252.189643855525</v>
       </c>
       <c r="O18">
-        <v>312.3725709638813</v>
+        <v>313.0474109638813</v>
       </c>
       <c r="P18">
-        <v>937.1177128916438</v>
+        <v>939.142232891644</v>
       </c>
       <c r="Q18">
-        <v>1257.617712891644</v>
+        <v>1259.642232891644</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1307136790228678</v>
+        <v>0.1306907046615197</v>
       </c>
       <c r="T18">
         <v>1.313232202634403</v>
       </c>
       <c r="U18">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +3069,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.744533079609765</v>
+        <v>7.859044703355894</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +3080,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.117906191371608</v>
+        <v>0.117759443164491</v>
       </c>
       <c r="C19">
-        <v>14407.57269139131</v>
+        <v>14424.86662334037</v>
       </c>
       <c r="D19">
-        <v>16556.34269139131</v>
+        <v>16573.63662334037</v>
       </c>
       <c r="E19">
         <v>-8121.33</v>
@@ -2845,37 +3113,37 @@
         <v>1434.75</v>
       </c>
       <c r="M19">
-        <v>196.8384484035044</v>
+        <v>193.9703784035044</v>
       </c>
       <c r="N19">
-        <v>1237.911551596496</v>
+        <v>1240.779621596496</v>
       </c>
       <c r="O19">
-        <v>309.4778878991239</v>
+        <v>310.1949053991239</v>
       </c>
       <c r="P19">
-        <v>928.4336636973717</v>
+        <v>930.5847161973718</v>
       </c>
       <c r="Q19">
-        <v>1248.933663697372</v>
+        <v>1251.084716197372</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1315129418148752</v>
+        <v>0.1314897512038909</v>
       </c>
       <c r="T19">
         <v>1.325593198517633</v>
       </c>
       <c r="U19">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3151,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.288972310220956</v>
+        <v>7.396747956099665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3162,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1177771750319961</v>
+        <v>0.1176229770812947</v>
       </c>
       <c r="C20">
-        <v>14256.02985740566</v>
+        <v>14274.35440527874</v>
       </c>
       <c r="D20">
-        <v>16573.50985740566</v>
+        <v>16591.83440527874</v>
       </c>
       <c r="E20">
         <v>-7952.62</v>
@@ -2927,37 +3195,37 @@
         <v>1434.75</v>
       </c>
       <c r="M20">
-        <v>208.4171806625341</v>
+        <v>205.3804006625341</v>
       </c>
       <c r="N20">
-        <v>1226.332819337466</v>
+        <v>1229.369599337466</v>
       </c>
       <c r="O20">
-        <v>306.5832048343665</v>
+        <v>307.3423998343665</v>
       </c>
       <c r="P20">
-        <v>919.7496145030995</v>
+        <v>922.0271995030994</v>
       </c>
       <c r="Q20">
-        <v>1240.2496145031</v>
+        <v>1242.527199503099</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1323316988213218</v>
+        <v>0.13230828668632</v>
       </c>
       <c r="T20">
         <v>1.338255682105332</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3233,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.88402940409757</v>
+        <v>6.985817514094129</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3244,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1179616586923843</v>
+        <v>0.1177287609980983</v>
       </c>
       <c r="C21">
-        <v>14062.78302825672</v>
+        <v>14091.53461750456</v>
       </c>
       <c r="D21">
-        <v>16548.97302825672</v>
+        <v>16577.72461750456</v>
       </c>
       <c r="E21">
         <v>-7783.91</v>
@@ -3009,37 +3277,37 @@
         <v>1434.75</v>
       </c>
       <c r="M21">
-        <v>227.0479909215638</v>
+        <v>222.2397559215638</v>
       </c>
       <c r="N21">
-        <v>1207.702009078436</v>
+        <v>1212.510244078436</v>
       </c>
       <c r="O21">
-        <v>301.9255022696091</v>
+        <v>303.1275610196091</v>
       </c>
       <c r="P21">
-        <v>905.7765068088272</v>
+        <v>909.3826830588272</v>
       </c>
       <c r="Q21">
-        <v>1226.276506808827</v>
+        <v>1229.882683058827</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1331706720501498</v>
+        <v>0.1331470329214016</v>
       </c>
       <c r="T21">
         <v>1.351230819608778</v>
       </c>
       <c r="U21">
-        <v>0.07083097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3315,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.319148626581109</v>
+        <v>6.455865621569408</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3326,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1178491423527725</v>
+        <v>0.1176050449149019</v>
       </c>
       <c r="C22">
-        <v>13909.02935711618</v>
+        <v>13939.3286346085</v>
       </c>
       <c r="D22">
-        <v>16563.92935711618</v>
+        <v>16594.2286346085</v>
       </c>
       <c r="E22">
         <v>-7615.199999999999</v>
@@ -3091,37 +3359,37 @@
         <v>1434.75</v>
       </c>
       <c r="M22">
-        <v>238.9978851805935</v>
+        <v>233.9365851805935</v>
       </c>
       <c r="N22">
-        <v>1195.752114819406</v>
+        <v>1200.813414819406</v>
       </c>
       <c r="O22">
-        <v>298.9380287048516</v>
+        <v>300.2033537048516</v>
       </c>
       <c r="P22">
-        <v>896.8140861145548</v>
+        <v>900.6100611145548</v>
       </c>
       <c r="Q22">
-        <v>1217.314086114555</v>
+        <v>1221.110061114555</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1340306196096985</v>
+        <v>0.1340067478123603</v>
       </c>
       <c r="T22">
         <v>1.364530335549809</v>
       </c>
       <c r="U22">
-        <v>0.07083097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3397,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.003191195252053</v>
+        <v>6.133072340490937</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3408,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1177366260131606</v>
+        <v>0.1174813288317055</v>
       </c>
       <c r="C23">
-        <v>13755.3027443459</v>
+        <v>13787.15554573483</v>
       </c>
       <c r="D23">
-        <v>16578.9127443459</v>
+        <v>16610.76554573483</v>
       </c>
       <c r="E23">
         <v>-7446.49</v>
@@ -3173,37 +3441,37 @@
         <v>1434.75</v>
       </c>
       <c r="M23">
-        <v>250.9477794396231</v>
+        <v>245.6334144396231</v>
       </c>
       <c r="N23">
-        <v>1183.802220560377</v>
+        <v>1189.116585560377</v>
       </c>
       <c r="O23">
-        <v>295.9505551400942</v>
+        <v>297.2791463900942</v>
       </c>
       <c r="P23">
-        <v>887.8516654202826</v>
+        <v>891.8374391702828</v>
       </c>
       <c r="Q23">
-        <v>1208.351665420283</v>
+        <v>1212.337439170283</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1349123379935396</v>
+        <v>0.1348882276372673</v>
       </c>
       <c r="T23">
         <v>1.378166548096942</v>
       </c>
       <c r="U23">
-        <v>0.07083097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3479,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.717324947859098</v>
+        <v>5.841021276658036</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3490,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1178716096735488</v>
+        <v>0.1173576127485091</v>
       </c>
       <c r="C24">
-        <v>13568.62070991777</v>
+        <v>13635.01544932285</v>
       </c>
       <c r="D24">
-        <v>16560.94070991777</v>
+        <v>16627.33544932285</v>
       </c>
       <c r="E24">
         <v>-7277.78</v>
@@ -3255,45 +3523,45 @@
         <v>1434.75</v>
       </c>
       <c r="M24">
-        <v>268.4651036986528</v>
+        <v>257.3302436986528</v>
       </c>
       <c r="N24">
-        <v>1166.284896301347</v>
+        <v>1177.419756301347</v>
       </c>
       <c r="O24">
-        <v>291.5712240753368</v>
+        <v>294.3549390753368</v>
       </c>
       <c r="P24">
-        <v>874.7136722260103</v>
+        <v>883.0648172260104</v>
       </c>
       <c r="Q24">
-        <v>1195.21367222601</v>
+        <v>1203.56481722601</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1358166645410689</v>
+        <v>0.1357923095089668</v>
       </c>
       <c r="T24">
         <v>1.392152407119643</v>
       </c>
       <c r="U24">
-        <v>0.07233097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05424823332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.344270000955062</v>
+        <v>5.575520309537216</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3572,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1177703433339369</v>
+        <v>0.1173718966653127</v>
       </c>
       <c r="C25">
-        <v>13413.38988902907</v>
+        <v>13464.39064620704</v>
       </c>
       <c r="D25">
-        <v>16574.41988902908</v>
+        <v>16625.42064620704</v>
       </c>
       <c r="E25">
         <v>-7109.07</v>
@@ -3337,37 +3605,37 @@
         <v>1434.75</v>
       </c>
       <c r="M25">
-        <v>280.6680629576825</v>
+        <v>272.1313369576825</v>
       </c>
       <c r="N25">
-        <v>1154.081937042317</v>
+        <v>1162.618663042318</v>
       </c>
       <c r="O25">
-        <v>288.5204842605793</v>
+        <v>290.6546657605794</v>
       </c>
       <c r="P25">
-        <v>865.561452781738</v>
+        <v>871.9639972817382</v>
       </c>
       <c r="Q25">
-        <v>1186.061452781738</v>
+        <v>1192.463997281738</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1367444800898328</v>
+        <v>0.1367198740266844</v>
       </c>
       <c r="T25">
         <v>1.406501535207869</v>
       </c>
       <c r="U25">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3643,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.111910435696145</v>
+        <v>5.272270426625322</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3654,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1176690769943251</v>
+        <v>0.1172541805821163</v>
       </c>
       <c r="C26">
-        <v>13258.18102779494</v>
+        <v>13311.47402181889</v>
       </c>
       <c r="D26">
-        <v>16587.92102779494</v>
+        <v>16641.21402181889</v>
       </c>
       <c r="E26">
         <v>-6940.36</v>
@@ -3419,37 +3687,37 @@
         <v>1434.75</v>
       </c>
       <c r="M26">
-        <v>292.8710222167122</v>
+        <v>283.9631342167121</v>
       </c>
       <c r="N26">
-        <v>1141.878977783288</v>
+        <v>1150.786865783288</v>
       </c>
       <c r="O26">
-        <v>285.469744445822</v>
+        <v>287.6967164458219</v>
       </c>
       <c r="P26">
-        <v>856.4092333374658</v>
+        <v>863.0901493374658</v>
       </c>
       <c r="Q26">
-        <v>1176.909233337466</v>
+        <v>1183.590149337466</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1376967118372484</v>
+        <v>0.1376718481369736</v>
       </c>
       <c r="T26">
         <v>1.421228271929995</v>
       </c>
       <c r="U26">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3725,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.89891416754214</v>
+        <v>5.0525924921826</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3736,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1175678106547133</v>
+        <v>0.1171364644989199</v>
       </c>
       <c r="C27">
-        <v>13102.9941799226</v>
+        <v>13158.58743190522</v>
       </c>
       <c r="D27">
-        <v>16601.4441799226</v>
+        <v>16657.03743190522</v>
       </c>
       <c r="E27">
         <v>-6771.65</v>
@@ -3501,37 +3769,37 @@
         <v>1434.75</v>
       </c>
       <c r="M27">
-        <v>305.0739814757418</v>
+        <v>295.7949314757418</v>
       </c>
       <c r="N27">
-        <v>1129.676018524258</v>
+        <v>1138.955068524258</v>
       </c>
       <c r="O27">
-        <v>282.4190046310645</v>
+        <v>284.7387671310645</v>
       </c>
       <c r="P27">
-        <v>847.2570138931935</v>
+        <v>854.2163013931936</v>
       </c>
       <c r="Q27">
-        <v>1167.757013893194</v>
+        <v>1174.716301393194</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1386743364312616</v>
+        <v>0.1386492082235371</v>
       </c>
       <c r="T27">
         <v>1.436347721631378</v>
       </c>
       <c r="U27">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3807,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.702957600840454</v>
+        <v>4.850488792495296</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3818,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1174665443151014</v>
+        <v>0.1170187484157235</v>
       </c>
       <c r="C28">
-        <v>12947.82939929454</v>
+        <v>13005.73096222303</v>
       </c>
       <c r="D28">
-        <v>16614.98939929454</v>
+        <v>16672.89096222303</v>
       </c>
       <c r="E28">
         <v>-6602.94</v>
@@ -3583,37 +3851,37 @@
         <v>1434.75</v>
       </c>
       <c r="M28">
-        <v>317.2769407347715</v>
+        <v>307.6267287347715</v>
       </c>
       <c r="N28">
-        <v>1117.473059265229</v>
+        <v>1127.123271265229</v>
       </c>
       <c r="O28">
-        <v>279.3682648163071</v>
+        <v>281.7808178163071</v>
       </c>
       <c r="P28">
-        <v>838.1047944489214</v>
+        <v>845.3424534489214</v>
       </c>
       <c r="Q28">
-        <v>1158.604794448921</v>
+        <v>1165.842453448921</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1396783833115996</v>
+        <v>0.1396529834475754</v>
       </c>
       <c r="T28">
         <v>1.451875805108474</v>
       </c>
       <c r="U28">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3889,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.522074616192745</v>
+        <v>4.663931531245479</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3900,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1173652779754896</v>
+        <v>0.1169010323325271</v>
       </c>
       <c r="C29">
-        <v>12792.68673996928</v>
+        <v>12852.90469885608</v>
       </c>
       <c r="D29">
-        <v>16628.55673996928</v>
+        <v>16688.77469885608</v>
       </c>
       <c r="E29">
         <v>-6434.23</v>
@@ -3665,37 +3933,37 @@
         <v>1434.75</v>
       </c>
       <c r="M29">
-        <v>329.4798999938012</v>
+        <v>319.4585259938012</v>
       </c>
       <c r="N29">
-        <v>1105.270100006199</v>
+        <v>1115.291474006199</v>
       </c>
       <c r="O29">
-        <v>276.3175250015497</v>
+        <v>278.8228685015497</v>
       </c>
       <c r="P29">
-        <v>828.9525750046491</v>
+        <v>836.4686055046491</v>
       </c>
       <c r="Q29">
-        <v>1149.452575004649</v>
+        <v>1156.968605504649</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1407099383256454</v>
+        <v>0.1406842593626832</v>
       </c>
       <c r="T29">
         <v>1.467829315530148</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3971,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.354590371148569</v>
+        <v>4.491193326384534</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3982,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1175580116358777</v>
+        <v>0.1167833162493307</v>
       </c>
       <c r="C30">
-        <v>12598.17391538211</v>
+        <v>12700.10872821652</v>
       </c>
       <c r="D30">
-        <v>16602.75391538211</v>
+        <v>16704.68872821652</v>
       </c>
       <c r="E30">
         <v>-6265.52</v>
@@ -3747,45 +4015,45 @@
         <v>1434.75</v>
       </c>
       <c r="M30">
-        <v>348.2962912528309</v>
+        <v>331.2903232528308</v>
       </c>
       <c r="N30">
-        <v>1086.453708747169</v>
+        <v>1103.459676747169</v>
       </c>
       <c r="O30">
-        <v>271.6134271867923</v>
+        <v>275.8649191867923</v>
       </c>
       <c r="P30">
-        <v>814.8402815603768</v>
+        <v>827.5947575603768</v>
       </c>
       <c r="Q30">
-        <v>1135.340281560377</v>
+        <v>1148.094757560377</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.141770147645637</v>
+        <v>0.1417441818309884</v>
       </c>
       <c r="T30">
         <v>1.48422597901909</v>
       </c>
       <c r="U30">
-        <v>0.07373097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.0552982333250682</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.119337575600264</v>
+        <v>4.330793564727944</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +4064,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1174672452962659</v>
+        <v>0.1168831001661343</v>
       </c>
       <c r="C31">
-        <v>12441.60556123347</v>
+        <v>12517.90698925039</v>
       </c>
       <c r="D31">
-        <v>16614.89556123347</v>
+        <v>16691.19698925039</v>
       </c>
       <c r="E31">
         <v>-6096.81</v>
@@ -3829,37 +4097,37 @@
         <v>1434.75</v>
       </c>
       <c r="M31">
-        <v>360.7354445118605</v>
+        <v>348.0147105118605</v>
       </c>
       <c r="N31">
-        <v>1074.01455548814</v>
+        <v>1086.73528948814</v>
       </c>
       <c r="O31">
-        <v>268.5036388720349</v>
+        <v>271.6838223720349</v>
       </c>
       <c r="P31">
-        <v>805.5109166161047</v>
+        <v>815.0514671161047</v>
       </c>
       <c r="Q31">
-        <v>1126.010916616105</v>
+        <v>1135.551467116105</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1428602220168959</v>
+        <v>0.1428339612702318</v>
       </c>
       <c r="T31">
         <v>1.501084520352792</v>
       </c>
       <c r="U31">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +4135,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.977291452303705</v>
+        <v>4.12267055576406</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4146,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1173764789566541</v>
+        <v>0.1167728840829379</v>
       </c>
       <c r="C32">
-        <v>12285.05497852828</v>
+        <v>12364.10051624733</v>
       </c>
       <c r="D32">
-        <v>16627.05497852828</v>
+        <v>16706.10051624733</v>
       </c>
       <c r="E32">
         <v>-5928.099999999999</v>
@@ -3911,37 +4179,37 @@
         <v>1434.75</v>
       </c>
       <c r="M32">
-        <v>373.1745977708902</v>
+        <v>360.0152177708902</v>
       </c>
       <c r="N32">
-        <v>1061.57540222911</v>
+        <v>1074.73478222911</v>
       </c>
       <c r="O32">
-        <v>265.3938505572775</v>
+        <v>268.6836955572775</v>
       </c>
       <c r="P32">
-        <v>796.1815516718324</v>
+        <v>806.0510866718324</v>
       </c>
       <c r="Q32">
-        <v>1116.681551671832</v>
+        <v>1126.551086671832</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1439814413701909</v>
+        <v>0.1439548772648821</v>
       </c>
       <c r="T32">
         <v>1.518424734296028</v>
       </c>
       <c r="U32">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4217,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.844715070560247</v>
+        <v>3.985248203905257</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4228,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1172857126170422</v>
+        <v>0.1166626679997415</v>
       </c>
       <c r="C33">
-        <v>12128.52220631261</v>
+        <v>12210.32068167173</v>
       </c>
       <c r="D33">
-        <v>16639.23220631261</v>
+        <v>16721.03068167173</v>
       </c>
       <c r="E33">
         <v>-5759.389999999999</v>
@@ -3993,37 +4261,37 @@
         <v>1434.75</v>
       </c>
       <c r="M33">
-        <v>385.6137510299199</v>
+        <v>372.0157250299198</v>
       </c>
       <c r="N33">
-        <v>1049.13624897008</v>
+        <v>1062.73427497008</v>
       </c>
       <c r="O33">
-        <v>262.28406224252</v>
+        <v>265.68356874252</v>
       </c>
       <c r="P33">
-        <v>786.85218672756</v>
+        <v>797.0507062275601</v>
       </c>
       <c r="Q33">
-        <v>1107.35218672756</v>
+        <v>1117.55070622756</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1451351598351755</v>
+        <v>0.145108283578218</v>
       </c>
       <c r="T33">
         <v>1.536267563136169</v>
       </c>
       <c r="U33">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4299,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.720692003767981</v>
+        <v>3.856691810230894</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4310,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1171949462774304</v>
+        <v>0.1165524519165451</v>
       </c>
       <c r="C34">
-        <v>11972.00728374696</v>
+        <v>12056.56755700741</v>
       </c>
       <c r="D34">
-        <v>16651.42728374696</v>
+        <v>16735.98755700741</v>
       </c>
       <c r="E34">
         <v>-5590.679999999999</v>
@@ -4075,37 +4343,37 @@
         <v>1434.75</v>
       </c>
       <c r="M34">
-        <v>398.0529042889495</v>
+        <v>384.0162322889495</v>
       </c>
       <c r="N34">
-        <v>1036.69709571105</v>
+        <v>1050.73376771105</v>
       </c>
       <c r="O34">
-        <v>259.1742739277626</v>
+        <v>262.6834419277626</v>
       </c>
       <c r="P34">
-        <v>777.5228217832878</v>
+        <v>788.0503257832878</v>
       </c>
       <c r="Q34">
-        <v>1098.022821783288</v>
+        <v>1108.550325783288</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1463228111961891</v>
+        <v>0.146295613606652</v>
       </c>
       <c r="T34">
         <v>1.554635181059844</v>
       </c>
       <c r="U34">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4381,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.604420378650232</v>
+        <v>3.736170191161178</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4392,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1171041799378185</v>
+        <v>0.1164422358333488</v>
       </c>
       <c r="C35">
-        <v>11815.51025010673</v>
+        <v>11902.84121399417</v>
       </c>
       <c r="D35">
-        <v>16663.64025010674</v>
+        <v>16750.97121399417</v>
       </c>
       <c r="E35">
         <v>-5421.969999999999</v>
@@ -4157,37 +4425,37 @@
         <v>1434.75</v>
       </c>
       <c r="M35">
-        <v>410.4920575479792</v>
+        <v>396.0167395479792</v>
       </c>
       <c r="N35">
-        <v>1024.257942452021</v>
+        <v>1038.733260452021</v>
       </c>
       <c r="O35">
-        <v>256.0644856130052</v>
+        <v>259.6833151130052</v>
       </c>
       <c r="P35">
-        <v>768.1934568390157</v>
+        <v>779.0499453390155</v>
       </c>
       <c r="Q35">
-        <v>1088.693456839016</v>
+        <v>1099.549945339015</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1475459148366359</v>
+        <v>0.1475183863225019</v>
       </c>
       <c r="T35">
         <v>1.573551086085718</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4463,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.495195518691134</v>
+        <v>3.622952912641142</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4474,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1170134135982067</v>
+        <v>0.1163320197501524</v>
       </c>
       <c r="C36">
-        <v>11659.03114478265</v>
+        <v>11749.14172462896</v>
       </c>
       <c r="D36">
-        <v>16675.87114478265</v>
+        <v>16765.98172462896</v>
       </c>
       <c r="E36">
         <v>-5253.259999999999</v>
@@ -4239,37 +4507,37 @@
         <v>1434.75</v>
       </c>
       <c r="M36">
-        <v>422.9312108070089</v>
+        <v>408.0172468070089</v>
       </c>
       <c r="N36">
-        <v>1011.818789192991</v>
+        <v>1026.732753192991</v>
       </c>
       <c r="O36">
-        <v>252.9546972982478</v>
+        <v>256.6831882982478</v>
       </c>
       <c r="P36">
-        <v>758.8640918947433</v>
+        <v>770.0495648947433</v>
       </c>
       <c r="Q36">
-        <v>1079.364091894743</v>
+        <v>1090.549564894743</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1488060822237629</v>
+        <v>0.1487782127570139</v>
       </c>
       <c r="T36">
         <v>1.593040200354801</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4545,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.392395650494335</v>
+        <v>3.51639547403405</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4556,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1169226472585948</v>
+        <v>0.116221803666956</v>
       </c>
       <c r="C37">
-        <v>11502.57000728115</v>
+        <v>11595.46916116702</v>
       </c>
       <c r="D37">
-        <v>16688.12000728115</v>
+        <v>16781.01916116702</v>
       </c>
       <c r="E37">
         <v>-5084.549999999999</v>
@@ -4321,37 +4589,37 @@
         <v>1434.75</v>
       </c>
       <c r="M37">
-        <v>435.3703640660386</v>
+        <v>420.0177540660385</v>
       </c>
       <c r="N37">
-        <v>999.3796359339615</v>
+        <v>1014.732245933961</v>
       </c>
       <c r="O37">
-        <v>249.8449089834904</v>
+        <v>253.6830614834903</v>
       </c>
       <c r="P37">
-        <v>749.5347269504712</v>
+        <v>761.0491844504711</v>
       </c>
       <c r="Q37">
-        <v>1070.034726950471</v>
+        <v>1081.549184450471</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1501050239920323</v>
+        <v>0.1500768030818186</v>
       </c>
       <c r="T37">
         <v>1.613128979678317</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4627,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.295470060480212</v>
+        <v>3.415927031918792</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4638,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.116831880918983</v>
+        <v>0.1161115875837596</v>
       </c>
       <c r="C38">
-        <v>11346.12687722485</v>
+        <v>11441.82359612305</v>
       </c>
       <c r="D38">
-        <v>16700.38687722485</v>
+        <v>16796.08359612305</v>
       </c>
       <c r="E38">
         <v>-4915.84</v>
@@ -4403,37 +4671,37 @@
         <v>1434.75</v>
       </c>
       <c r="M38">
-        <v>447.8095173250682</v>
+        <v>432.0182613250682</v>
       </c>
       <c r="N38">
-        <v>986.9404826749318</v>
+        <v>1002.731738674932</v>
       </c>
       <c r="O38">
-        <v>246.7351206687329</v>
+        <v>250.682934668733</v>
       </c>
       <c r="P38">
-        <v>740.2053620061988</v>
+        <v>752.0488040061989</v>
       </c>
       <c r="Q38">
-        <v>1060.705362006199</v>
+        <v>1072.548804006199</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1514445576905601</v>
+        <v>0.1514159743542735</v>
       </c>
       <c r="T38">
         <v>1.633845533355692</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4709,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.203929225466873</v>
+        <v>3.321040169921048</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4720,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1167411145793712</v>
+        <v>0.1160013715005632</v>
       </c>
       <c r="C39">
-        <v>11189.70179435295</v>
+        <v>11288.20510227237</v>
       </c>
       <c r="D39">
-        <v>16712.67179435295</v>
+        <v>16811.17510227237</v>
       </c>
       <c r="E39">
         <v>-4747.13</v>
@@ -4485,37 +4753,37 @@
         <v>1434.75</v>
       </c>
       <c r="M39">
-        <v>460.2486705840979</v>
+        <v>444.0187685840979</v>
       </c>
       <c r="N39">
-        <v>974.5013294159021</v>
+        <v>990.7312314159021</v>
       </c>
       <c r="O39">
-        <v>243.6253323539755</v>
+        <v>247.6828078539755</v>
       </c>
       <c r="P39">
-        <v>730.8759970619266</v>
+        <v>743.0484235619266</v>
       </c>
       <c r="Q39">
-        <v>1051.375997061927</v>
+        <v>1063.548423561926</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1528266162684062</v>
+        <v>0.1527976590004571</v>
       </c>
       <c r="T39">
         <v>1.655219755403778</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4791,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.117336543697498</v>
+        <v>3.231282327490749</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4802,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1166503482397593</v>
+        <v>0.1158911554173668</v>
       </c>
       <c r="C40">
-        <v>11033.29479852163</v>
+        <v>11134.61375265209</v>
       </c>
       <c r="D40">
-        <v>16724.97479852163</v>
+        <v>16826.29375265209</v>
       </c>
       <c r="E40">
         <v>-4578.419999999999</v>
@@ -4567,37 +4835,37 @@
         <v>1434.75</v>
       </c>
       <c r="M40">
-        <v>472.6878238431276</v>
+        <v>456.0192758431276</v>
       </c>
       <c r="N40">
-        <v>962.0621761568724</v>
+        <v>978.7307241568724</v>
       </c>
       <c r="O40">
-        <v>240.5155440392181</v>
+        <v>244.6826810392181</v>
       </c>
       <c r="P40">
-        <v>721.5466321176543</v>
+        <v>734.0480431176543</v>
       </c>
       <c r="Q40">
-        <v>1042.046632117654</v>
+        <v>1054.548043117654</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1542532573810216</v>
+        <v>0.1542239141190982</v>
       </c>
       <c r="T40">
         <v>1.677283468485673</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4873,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.035301371494932</v>
+        <v>3.146248582030466</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4884,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1173200819001475</v>
+        <v>0.1157809393341704</v>
       </c>
       <c r="C41">
-        <v>10774.22911968486</v>
+        <v>10981.04962056231</v>
       </c>
       <c r="D41">
-        <v>16634.61911968486</v>
+        <v>16841.43962056231</v>
       </c>
       <c r="E41">
         <v>-4409.709999999999</v>
@@ -4649,45 +4917,45 @@
         <v>1434.75</v>
       </c>
       <c r="M41">
-        <v>502.2341711021573</v>
+        <v>468.0197831021572</v>
       </c>
       <c r="N41">
-        <v>932.5158288978427</v>
+        <v>966.7302168978428</v>
       </c>
       <c r="O41">
-        <v>233.1289572244607</v>
+        <v>241.6825542244607</v>
       </c>
       <c r="P41">
-        <v>699.386871673382</v>
+        <v>725.0476626733821</v>
       </c>
       <c r="Q41">
-        <v>1019.886871673382</v>
+        <v>1045.547662673382</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1557266736120834</v>
+        <v>0.1556969317006456</v>
       </c>
       <c r="T41">
         <v>1.700070581996483</v>
       </c>
       <c r="U41">
-        <v>0.0763309777667576</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.0572482333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.856735129852731</v>
+        <v>3.065575541465582</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4966,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1172488155605357</v>
+        <v>0.116420723250974</v>
       </c>
       <c r="C42">
-        <v>10615.08742235729</v>
+        <v>10724.79893671117</v>
       </c>
       <c r="D42">
-        <v>16644.18742235729</v>
+        <v>16753.89893671118</v>
       </c>
       <c r="E42">
         <v>-4240.999999999999</v>
@@ -4731,37 +4999,37 @@
         <v>1434.75</v>
       </c>
       <c r="M42">
-        <v>515.111970361187</v>
+        <v>496.891290361187</v>
       </c>
       <c r="N42">
-        <v>919.638029638813</v>
+        <v>937.858709638813</v>
       </c>
       <c r="O42">
-        <v>229.9095074097033</v>
+        <v>234.4646774097033</v>
       </c>
       <c r="P42">
-        <v>689.7285222291098</v>
+        <v>703.3940322291098</v>
       </c>
       <c r="Q42">
-        <v>1010.22852222911</v>
+        <v>1023.89403222911</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1572492037175139</v>
+        <v>0.1572190498682446</v>
       </c>
       <c r="T42">
         <v>1.723617265957653</v>
       </c>
       <c r="U42">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +5037,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.785316751606413</v>
+        <v>2.887452502854477</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +5048,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1171775492209238</v>
+        <v>0.1163292571677776</v>
       </c>
       <c r="C43">
-        <v>10455.95673882054</v>
+        <v>10568.54831089798</v>
       </c>
       <c r="D43">
-        <v>16653.76673882054</v>
+        <v>16766.35831089798</v>
       </c>
       <c r="E43">
         <v>-4072.289999999999</v>
@@ -4813,37 +5081,37 @@
         <v>1434.75</v>
       </c>
       <c r="M43">
-        <v>527.9897696202166</v>
+        <v>509.3135726202166</v>
       </c>
       <c r="N43">
-        <v>906.7602303797834</v>
+        <v>925.4364273797834</v>
       </c>
       <c r="O43">
-        <v>226.6900575949458</v>
+        <v>231.3591068449458</v>
       </c>
       <c r="P43">
-        <v>680.0701727848375</v>
+        <v>694.0773205348376</v>
       </c>
       <c r="Q43">
-        <v>1000.570172784837</v>
+        <v>1014.577320534838</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1588233450129591</v>
+        <v>0.1587927652618638</v>
       </c>
       <c r="T43">
         <v>1.747962142595473</v>
       </c>
       <c r="U43">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +5119,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.717382196689183</v>
+        <v>2.817026832053148</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +5130,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.117106282881312</v>
+        <v>0.1162377910845812</v>
       </c>
       <c r="C44">
-        <v>10296.83708810203</v>
+        <v>10412.31623020505</v>
       </c>
       <c r="D44">
-        <v>16663.35708810203</v>
+        <v>16778.83623020505</v>
       </c>
       <c r="E44">
         <v>-3903.58</v>
@@ -4895,37 +5163,37 @@
         <v>1434.75</v>
       </c>
       <c r="M44">
-        <v>540.8675688792463</v>
+        <v>521.7358548792462</v>
       </c>
       <c r="N44">
-        <v>893.8824311207537</v>
+        <v>913.0141451207538</v>
       </c>
       <c r="O44">
-        <v>223.4706077801884</v>
+        <v>228.2535362801885</v>
       </c>
       <c r="P44">
-        <v>670.4118233405653</v>
+        <v>684.7606088405654</v>
       </c>
       <c r="Q44">
-        <v>990.9118233405653</v>
+        <v>1005.260608840565</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1604517670427299</v>
+        <v>0.160420746703539</v>
       </c>
       <c r="T44">
         <v>1.773146497738046</v>
       </c>
       <c r="U44">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5201,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.652682620577536</v>
+        <v>2.749954764623312</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5212,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1170350165417001</v>
+        <v>0.1161463250013848</v>
       </c>
       <c r="C45">
-        <v>10137.72848927305</v>
+        <v>10256.10273606838</v>
       </c>
       <c r="D45">
-        <v>16672.95848927305</v>
+        <v>16791.33273606838</v>
       </c>
       <c r="E45">
         <v>-3734.87</v>
@@ -4977,37 +5245,37 @@
         <v>1434.75</v>
       </c>
       <c r="M45">
-        <v>553.7453681382759</v>
+        <v>534.1581371382759</v>
       </c>
       <c r="N45">
-        <v>881.0046318617241</v>
+        <v>900.5918628617241</v>
       </c>
       <c r="O45">
-        <v>220.251157965431</v>
+        <v>225.147965715431</v>
       </c>
       <c r="P45">
-        <v>660.753473896293</v>
+        <v>675.443897146293</v>
       </c>
       <c r="Q45">
-        <v>981.253473896293</v>
+        <v>995.943897146293</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1621373266875803</v>
+        <v>0.1621058503010623</v>
       </c>
       <c r="T45">
         <v>1.799214514464568</v>
       </c>
       <c r="U45">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5283,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.590992327075733</v>
+        <v>2.686002328236723</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5294,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1169637502020883</v>
+        <v>0.1160548589181885</v>
       </c>
       <c r="C46">
-        <v>9978.630961448851</v>
+        <v>10099.90787004749</v>
       </c>
       <c r="D46">
-        <v>16682.57096144885</v>
+        <v>16803.84787004749</v>
       </c>
       <c r="E46">
         <v>-3566.16</v>
@@ -5059,37 +5327,37 @@
         <v>1434.75</v>
       </c>
       <c r="M46">
-        <v>566.6231673973057</v>
+        <v>546.5804193973056</v>
       </c>
       <c r="N46">
-        <v>868.1268326026943</v>
+        <v>888.1695806026944</v>
       </c>
       <c r="O46">
-        <v>217.0317081506736</v>
+        <v>222.0423951506736</v>
       </c>
       <c r="P46">
-        <v>651.0951244520207</v>
+        <v>666.1271854520207</v>
       </c>
       <c r="Q46">
-        <v>971.5951244520207</v>
+        <v>986.6271854520207</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1638830848911755</v>
+        <v>0.1638511361699258</v>
       </c>
       <c r="T46">
         <v>1.826213531788466</v>
       </c>
       <c r="U46">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5365,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.532106137824012</v>
+        <v>2.624956820776798</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5376,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1178037338624764</v>
+        <v>0.1159633928349921</v>
       </c>
       <c r="C47">
-        <v>9697.322978173896</v>
+        <v>9943.731673825896</v>
       </c>
       <c r="D47">
-        <v>16569.9729781739</v>
+        <v>16816.3816738259</v>
       </c>
       <c r="E47">
         <v>-3397.45</v>
@@ -5141,45 +5409,45 @@
         <v>1434.75</v>
       </c>
       <c r="M47">
-        <v>599.9992316563353</v>
+        <v>559.0027016563353</v>
       </c>
       <c r="N47">
-        <v>834.7507683436647</v>
+        <v>875.7472983436647</v>
       </c>
       <c r="O47">
-        <v>208.6876920859162</v>
+        <v>218.9368245859162</v>
       </c>
       <c r="P47">
-        <v>626.0630762577485</v>
+        <v>656.8104737577486</v>
       </c>
       <c r="Q47">
-        <v>946.5630762577485</v>
+        <v>977.3104737577486</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.165692325211265</v>
+        <v>0.1656598869794752</v>
       </c>
       <c r="T47">
         <v>1.854194331560506</v>
       </c>
       <c r="U47">
-        <v>0.07903097776675759</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05927323332506819</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.391253062173568</v>
+        <v>2.566624446981758</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5458,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1177527175228646</v>
+        <v>0.1158719267517957</v>
       </c>
       <c r="C48">
-        <v>9535.408236222411</v>
+        <v>9787.574189211573</v>
       </c>
       <c r="D48">
-        <v>16576.76823622241</v>
+        <v>16828.93418921157</v>
       </c>
       <c r="E48">
         <v>-3228.739999999999</v>
@@ -5223,45 +5491,45 @@
         <v>1434.75</v>
       </c>
       <c r="M48">
-        <v>613.332547915365</v>
+        <v>571.424983915365</v>
       </c>
       <c r="N48">
-        <v>821.417452084635</v>
+        <v>863.325016084635</v>
       </c>
       <c r="O48">
-        <v>205.3543630211587</v>
+        <v>215.8312540211587</v>
       </c>
       <c r="P48">
-        <v>616.0630890634762</v>
+        <v>647.4937620634762</v>
       </c>
       <c r="Q48">
-        <v>936.5630890634762</v>
+        <v>967.9937620634762</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1675685744320985</v>
+        <v>0.1675356285597487</v>
       </c>
       <c r="T48">
         <v>1.883211457250028</v>
       </c>
       <c r="U48">
-        <v>0.07903097776675759</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05927323332506819</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.339269299952404</v>
+        <v>2.510828263351719</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5540,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1177017011832528</v>
+        <v>0.1170142106685993</v>
       </c>
       <c r="C49">
-        <v>9373.499069956071</v>
+        <v>9463.432691909458</v>
       </c>
       <c r="D49">
-        <v>16583.56906995607</v>
+        <v>16673.50269190946</v>
       </c>
       <c r="E49">
         <v>-3060.029999999999</v>
@@ -5305,37 +5573,37 @@
         <v>1434.75</v>
       </c>
       <c r="M49">
-        <v>626.6658641743946</v>
+        <v>611.6000611743947</v>
       </c>
       <c r="N49">
-        <v>808.0841358256054</v>
+        <v>823.1499388256053</v>
       </c>
       <c r="O49">
-        <v>202.0210339564013</v>
+        <v>205.7874847064013</v>
       </c>
       <c r="P49">
-        <v>606.063101869204</v>
+        <v>617.362454119204</v>
       </c>
       <c r="Q49">
-        <v>926.563101869204</v>
+        <v>937.862454119204</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1695156255103221</v>
+        <v>0.1694821528411646</v>
       </c>
       <c r="T49">
         <v>1.913323568814628</v>
       </c>
       <c r="U49">
-        <v>0.07903097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05927323332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5611,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.289497612719374</v>
+        <v>2.345895775819565</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5622,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1193426848436409</v>
+        <v>0.1169489945854029</v>
       </c>
       <c r="C50">
-        <v>8988.795115244071</v>
+        <v>9303.519375665759</v>
       </c>
       <c r="D50">
-        <v>16367.57511524407</v>
+        <v>16682.29937566576</v>
       </c>
       <c r="E50">
         <v>-2891.32</v>
@@ -5387,45 +5655,45 @@
         <v>1434.75</v>
       </c>
       <c r="M50">
-        <v>678.0601564334243</v>
+        <v>624.6128284334243</v>
       </c>
       <c r="N50">
-        <v>756.6898435665757</v>
+        <v>810.1371715665757</v>
       </c>
       <c r="O50">
-        <v>189.1724608916439</v>
+        <v>202.5342928916439</v>
       </c>
       <c r="P50">
-        <v>567.5173826749318</v>
+        <v>607.6028786749318</v>
       </c>
       <c r="Q50">
-        <v>888.0173826749318</v>
+        <v>928.1028786749318</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1715375631684773</v>
+        <v>0.1715035434410964</v>
       </c>
       <c r="T50">
         <v>1.944593838516327</v>
       </c>
       <c r="U50">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.115962700930167</v>
+        <v>2.297022947156658</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5704,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1193269185040291</v>
+        <v>0.1168837785022065</v>
       </c>
       <c r="C51">
-        <v>8822.13358193105</v>
+        <v>9143.615346311983</v>
       </c>
       <c r="D51">
-        <v>16369.62358193105</v>
+        <v>16691.10534631198</v>
       </c>
       <c r="E51">
         <v>-2722.610000000001</v>
@@ -5469,45 +5737,45 @@
         <v>1434.75</v>
       </c>
       <c r="M51">
-        <v>692.1864096924538</v>
+        <v>637.6255956924539</v>
       </c>
       <c r="N51">
-        <v>742.5635903075462</v>
+        <v>797.1244043075461</v>
       </c>
       <c r="O51">
-        <v>185.6408975768865</v>
+        <v>199.2811010768865</v>
       </c>
       <c r="P51">
-        <v>556.9226927306596</v>
+        <v>597.8433032306596</v>
       </c>
       <c r="Q51">
-        <v>877.4226927306596</v>
+        <v>918.3433032306596</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1736387924995013</v>
+        <v>0.1736042042606335</v>
       </c>
       <c r="T51">
         <v>1.977090393304367</v>
       </c>
       <c r="U51">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.072779788666287</v>
+        <v>2.25014492782693</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5786,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1193111521644172</v>
+        <v>0.1178685624190101</v>
       </c>
       <c r="C52">
-        <v>8655.472561429604</v>
+        <v>8842.914242623421</v>
       </c>
       <c r="D52">
-        <v>16371.6725614296</v>
+        <v>16559.11424262342</v>
       </c>
       <c r="E52">
         <v>-2553.9</v>
@@ -5551,37 +5819,37 @@
         <v>1434.75</v>
       </c>
       <c r="M52">
-        <v>706.3126629514836</v>
+        <v>674.2577629514836</v>
       </c>
       <c r="N52">
-        <v>728.4373370485164</v>
+        <v>760.4922370485164</v>
       </c>
       <c r="O52">
-        <v>182.1093342621291</v>
+        <v>190.1230592621291</v>
       </c>
       <c r="P52">
-        <v>546.3280027863873</v>
+        <v>570.3691777863872</v>
       </c>
       <c r="Q52">
-        <v>866.8280027863873</v>
+        <v>890.8691777863872</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1758240710037663</v>
+        <v>0.175788891512952</v>
       </c>
       <c r="T52">
         <v>2.010886810283929</v>
       </c>
       <c r="U52">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5857,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.03132419289296</v>
+        <v>2.127895411570126</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5868,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1228526358248054</v>
+        <v>0.1178243463358137</v>
       </c>
       <c r="C53">
-        <v>8039.044902461623</v>
+        <v>8680.085771221356</v>
       </c>
       <c r="D53">
-        <v>15923.95490246162</v>
+        <v>16564.99577122136</v>
       </c>
       <c r="E53">
         <v>-2385.189999999999</v>
@@ -5633,45 +5901,45 @@
         <v>1434.75</v>
       </c>
       <c r="M53">
-        <v>800.4580692105134</v>
+        <v>687.7429182105134</v>
       </c>
       <c r="N53">
-        <v>634.2919307894866</v>
+        <v>747.0070817894866</v>
       </c>
       <c r="O53">
-        <v>158.5729826973717</v>
+        <v>186.7517704473717</v>
       </c>
       <c r="P53">
-        <v>475.7189480921149</v>
+        <v>560.255311342115</v>
       </c>
       <c r="Q53">
-        <v>796.2189480921149</v>
+        <v>880.755311342115</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1780985445490217</v>
+        <v>0.1780627496735284</v>
       </c>
       <c r="T53">
         <v>2.046062672854494</v>
       </c>
       <c r="U53">
-        <v>0.09303097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.792411189526873</v>
+        <v>2.086171972127575</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5950,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1229066194851935</v>
+        <v>0.1177801302526173</v>
       </c>
       <c r="C54">
-        <v>7863.699638597724</v>
+        <v>8517.26147935078</v>
       </c>
       <c r="D54">
-        <v>15917.31963859772</v>
+        <v>16570.88147935078</v>
       </c>
       <c r="E54">
         <v>-2216.48</v>
@@ -5715,45 +5983,45 @@
         <v>1434.75</v>
       </c>
       <c r="M54">
-        <v>816.153325469543</v>
+        <v>701.228073469543</v>
       </c>
       <c r="N54">
-        <v>618.596674530457</v>
+        <v>733.521926530457</v>
       </c>
       <c r="O54">
-        <v>154.6491686326142</v>
+        <v>183.3804816326142</v>
       </c>
       <c r="P54">
-        <v>463.9475058978427</v>
+        <v>550.1414448978428</v>
       </c>
       <c r="Q54">
-        <v>784.4475058978428</v>
+        <v>870.6414448978428</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1804677878253294</v>
+        <v>0.1804313519241288</v>
       </c>
       <c r="T54">
         <v>2.082704196365498</v>
       </c>
       <c r="U54">
-        <v>0.09303097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.757941743574433</v>
+        <v>2.046053280355891</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +6032,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1248288531455817</v>
+        <v>0.1177359141694209</v>
       </c>
       <c r="C55">
-        <v>7462.27447653731</v>
+        <v>8354.441371468354</v>
       </c>
       <c r="D55">
-        <v>15684.60447653731</v>
+        <v>16576.77137146836</v>
       </c>
       <c r="E55">
         <v>-2047.769999999999</v>
@@ -5797,45 +6065,45 @@
         <v>1434.75</v>
       </c>
       <c r="M55">
-        <v>873.8742427285729</v>
+        <v>714.7132287285727</v>
       </c>
       <c r="N55">
-        <v>560.8757572714271</v>
+        <v>720.0367712714273</v>
       </c>
       <c r="O55">
-        <v>140.2189393178568</v>
+        <v>180.0091928178568</v>
       </c>
       <c r="P55">
-        <v>420.6568179535703</v>
+        <v>540.0275784535704</v>
       </c>
       <c r="Q55">
-        <v>741.1568179535703</v>
+        <v>860.5275784535704</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1829378499644587</v>
+        <v>0.1829007457598612</v>
       </c>
       <c r="T55">
         <v>2.120904933642928</v>
       </c>
       <c r="U55">
-        <v>0.0977309777667576</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.0732982333250682</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.641826626586631</v>
+        <v>2.007448501481251</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +6114,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1249180868059699</v>
+        <v>0.1208506980862245</v>
       </c>
       <c r="C56">
-        <v>7282.926569552288</v>
+        <v>7780.811465256269</v>
       </c>
       <c r="D56">
-        <v>15673.96656955229</v>
+        <v>16171.85146525627</v>
       </c>
       <c r="E56">
         <v>-1879.059999999999</v>
@@ -5879,45 +6147,45 @@
         <v>1434.75</v>
       </c>
       <c r="M56">
-        <v>890.3624359876025</v>
+        <v>799.2590359876024</v>
       </c>
       <c r="N56">
-        <v>544.3875640123975</v>
+        <v>635.4909640123976</v>
       </c>
       <c r="O56">
-        <v>136.0968910030994</v>
+        <v>158.8727410030994</v>
       </c>
       <c r="P56">
-        <v>408.2906730092982</v>
+        <v>476.6182230092982</v>
       </c>
       <c r="Q56">
-        <v>728.7906730092982</v>
+        <v>797.1182230092982</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.185515306109637</v>
+        <v>0.1854775045449732</v>
       </c>
       <c r="T56">
         <v>2.160766572541116</v>
       </c>
       <c r="U56">
-        <v>0.0977309777667576</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.0732982333250682</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.61142242979799</v>
+        <v>1.795100130744415</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6196,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.125007320466358</v>
+        <v>0.1208649820030281</v>
       </c>
       <c r="C57">
-        <v>7103.59308286894</v>
+        <v>7610.290126556805</v>
       </c>
       <c r="D57">
-        <v>15663.34308286894</v>
+        <v>16170.04012655681</v>
       </c>
       <c r="E57">
         <v>-1710.349999999999</v>
@@ -5961,45 +6229,45 @@
         <v>1434.75</v>
       </c>
       <c r="M57">
-        <v>906.8506292466323</v>
+        <v>814.0601292466321</v>
       </c>
       <c r="N57">
-        <v>527.8993707533677</v>
+        <v>620.6898707533679</v>
       </c>
       <c r="O57">
-        <v>131.9748426883419</v>
+        <v>155.172467688342</v>
       </c>
       <c r="P57">
-        <v>395.9245280650258</v>
+        <v>465.517403065026</v>
       </c>
       <c r="Q57">
-        <v>716.4245280650258</v>
+        <v>786.017403065026</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1882073158612678</v>
+        <v>0.188168785942757</v>
       </c>
       <c r="T57">
         <v>2.20239983983478</v>
       </c>
       <c r="U57">
-        <v>0.0977309777667576</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.0732982333250682</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.582123840165299</v>
+        <v>1.762461946549062</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6278,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1250965541267462</v>
+        <v>0.1225172659198317</v>
       </c>
       <c r="C58">
-        <v>6924.273987185794</v>
+        <v>7234.757656323172</v>
       </c>
       <c r="D58">
-        <v>15652.73398718579</v>
+        <v>15963.21765632317</v>
       </c>
       <c r="E58">
         <v>-1541.639999999999</v>
@@ -6043,37 +6311,37 @@
         <v>1434.75</v>
       </c>
       <c r="M58">
-        <v>923.3388225056618</v>
+        <v>865.7074865056617</v>
       </c>
       <c r="N58">
-        <v>511.4111774943382</v>
+        <v>569.0425134943383</v>
       </c>
       <c r="O58">
-        <v>127.8527943735845</v>
+        <v>142.2606283735846</v>
       </c>
       <c r="P58">
-        <v>383.5583831207537</v>
+        <v>426.7818851207537</v>
       </c>
       <c r="Q58">
-        <v>704.0583831207537</v>
+        <v>747.2818851207537</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1910216896925182</v>
+        <v>0.1909823983131672</v>
       </c>
       <c r="T58">
         <v>2.245925528369063</v>
       </c>
       <c r="U58">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6349,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.553871628733776</v>
+        <v>1.657314996536785</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6360,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1251857877871344</v>
+        <v>0.1225607998366354</v>
       </c>
       <c r="C59">
-        <v>6744.9692532807</v>
+        <v>7060.669866889773</v>
       </c>
       <c r="D59">
-        <v>15642.1392532807</v>
+        <v>15957.83986688978</v>
       </c>
       <c r="E59">
         <v>-1372.929999999998</v>
@@ -6125,37 +6393,37 @@
         <v>1434.75</v>
       </c>
       <c r="M59">
-        <v>939.8270157646915</v>
+        <v>881.1665487646915</v>
       </c>
       <c r="N59">
-        <v>494.9229842353085</v>
+        <v>553.5834512353085</v>
       </c>
       <c r="O59">
-        <v>123.7307460588271</v>
+        <v>138.3958628088271</v>
       </c>
       <c r="P59">
-        <v>371.1922381764814</v>
+        <v>415.1875884264814</v>
       </c>
       <c r="Q59">
-        <v>691.6922381764814</v>
+        <v>735.6875884264814</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1939669646321988</v>
+        <v>0.1939268763752244</v>
       </c>
       <c r="T59">
         <v>2.29147566753285</v>
       </c>
       <c r="U59">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6431,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.526610722966517</v>
+        <v>1.628239294843158</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6442,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1252750214475225</v>
+        <v>0.1226043337534389</v>
       </c>
       <c r="C60">
-        <v>6565.678852010586</v>
+        <v>6886.585699643356</v>
       </c>
       <c r="D60">
-        <v>15631.55885201058</v>
+        <v>15952.46569964335</v>
       </c>
       <c r="E60">
         <v>-1204.220000000001</v>
@@ -6207,37 +6475,37 @@
         <v>1434.75</v>
       </c>
       <c r="M60">
-        <v>956.315209023721</v>
+        <v>896.6256110237209</v>
       </c>
       <c r="N60">
-        <v>478.434790976279</v>
+        <v>538.1243889762791</v>
       </c>
       <c r="O60">
-        <v>119.6086977440698</v>
+        <v>134.5310972440698</v>
       </c>
       <c r="P60">
-        <v>358.8260932322092</v>
+        <v>403.5932917322093</v>
       </c>
       <c r="Q60">
-        <v>679.3260932322092</v>
+        <v>724.0932917322093</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1970524907594832</v>
+        <v>0.1970115676783319</v>
       </c>
       <c r="T60">
         <v>2.339194860942529</v>
       </c>
       <c r="U60">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6513,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.500289848432612</v>
+        <v>1.600166203552759</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6524,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1325770051079107</v>
+        <v>0.1226478676702425</v>
       </c>
       <c r="C61">
-        <v>5577.138697412183</v>
+        <v>6712.505150925572</v>
       </c>
       <c r="D61">
-        <v>14811.72869741218</v>
+        <v>15947.09515092557</v>
       </c>
       <c r="E61">
         <v>-1035.51</v>
@@ -6289,45 +6557,45 @@
         <v>1434.75</v>
       </c>
       <c r="M61">
-        <v>1135.051809282751</v>
+        <v>912.0846732827507</v>
       </c>
       <c r="N61">
-        <v>299.6981907172492</v>
+        <v>522.6653267172493</v>
       </c>
       <c r="O61">
-        <v>74.9245476793123</v>
+        <v>130.6663316793123</v>
       </c>
       <c r="P61">
-        <v>224.7736430379369</v>
+        <v>391.998995037937</v>
       </c>
       <c r="Q61">
-        <v>545.2736430379368</v>
+        <v>712.498995037937</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.2002885303563913</v>
+        <v>0.2002467317279325</v>
       </c>
       <c r="T61">
         <v>2.389241819884389</v>
       </c>
       <c r="U61">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.0855232333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.264039216770758</v>
+        <v>1.573044742475593</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6606,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1486318340148529</v>
+        <v>0.1226914015870462</v>
       </c>
       <c r="C62">
-        <v>3877.007815922883</v>
+        <v>6538.428217083021</v>
       </c>
       <c r="D62">
-        <v>13280.30781592288</v>
+        <v>15941.72821708302</v>
       </c>
       <c r="E62">
         <v>-866.7999999999993</v>
@@ -6371,45 +6639,45 @@
         <v>1434.75</v>
       </c>
       <c r="M62">
-        <v>1485.29899554178</v>
+        <v>927.5437355417804</v>
       </c>
       <c r="N62">
-        <v>-50.54899554178041</v>
+        <v>507.2062644582196</v>
       </c>
       <c r="O62">
-        <v>-12.6372488854451</v>
+        <v>126.8015661145549</v>
       </c>
       <c r="P62">
-        <v>-37.91174665633531</v>
+        <v>380.4046983436647</v>
       </c>
       <c r="Q62">
-        <v>282.5882533436647</v>
+        <v>700.9046983436647</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2046346061470574</v>
+        <v>0.2036436539800131</v>
       </c>
       <c r="T62">
-        <v>2.456456039655217</v>
+        <v>2.441791126773342</v>
       </c>
       <c r="U62">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V62">
-        <v>0.2414917811677133</v>
+        <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.1112966525933832</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9659671246708532</v>
+        <v>1.546827330101</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6688,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1496411437925205</v>
+        <v>0.1227349355038498</v>
       </c>
       <c r="C63">
-        <v>3622.534411157369</v>
+        <v>6364.35489446722</v>
       </c>
       <c r="D63">
-        <v>13194.54441115737</v>
+        <v>15936.36489446722</v>
       </c>
       <c r="E63">
         <v>-698.0900000000001</v>
@@ -6453,45 +6721,45 @@
         <v>1434.75</v>
       </c>
       <c r="M63">
-        <v>1510.05397880081</v>
+        <v>943.00279780081</v>
       </c>
       <c r="N63">
-        <v>-75.30397880081</v>
+        <v>491.74720219919</v>
       </c>
       <c r="O63">
-        <v>-18.8259947002025</v>
+        <v>122.9368005497975</v>
       </c>
       <c r="P63">
-        <v>-56.4779841006075</v>
+        <v>368.8104016493925</v>
       </c>
       <c r="Q63">
-        <v>264.0220158993925</v>
+        <v>689.3104016493926</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2087072883559564</v>
+        <v>0.2072147773732261</v>
       </c>
       <c r="T63">
-        <v>2.519442091954069</v>
+        <v>2.497035269913011</v>
       </c>
       <c r="U63">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V63">
-        <v>0.2375328995092262</v>
+        <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.1118775431699959</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.9501315980369048</v>
+        <v>1.521469505017377</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6770,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.150650453570188</v>
+        <v>0.1293814694206534</v>
       </c>
       <c r="C64">
-        <v>3369.16160827786</v>
+        <v>5417.067453466199</v>
       </c>
       <c r="D64">
-        <v>13109.88160827786</v>
+        <v>15157.7874534662</v>
       </c>
       <c r="E64">
         <v>-529.3799999999992</v>
@@ -6535,45 +6803,45 @@
         <v>1434.75</v>
       </c>
       <c r="M64">
-        <v>1534.80896205984</v>
+        <v>1106.99414405984</v>
       </c>
       <c r="N64">
-        <v>-100.0589620598398</v>
+        <v>327.7558559401602</v>
       </c>
       <c r="O64">
-        <v>-25.01474051495995</v>
+        <v>81.93896398504006</v>
       </c>
       <c r="P64">
-        <v>-75.04422154487986</v>
+        <v>245.8168919551202</v>
       </c>
       <c r="Q64">
-        <v>245.4557784551201</v>
+        <v>566.3168919551201</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2129943222600605</v>
+        <v>0.2109738546292398</v>
       </c>
       <c r="T64">
-        <v>2.585743199637071</v>
+        <v>2.555186999533714</v>
       </c>
       <c r="U64">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V64">
-        <v>0.2337017237106903</v>
+        <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.1124396953409114</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.9348068948427611</v>
+        <v>1.296077316848429</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6852,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1516597633478556</v>
+        <v>0.129531503337457</v>
       </c>
       <c r="C65">
-        <v>3116.86835631971</v>
+        <v>5231.659474925171</v>
       </c>
       <c r="D65">
-        <v>13026.29835631971</v>
+        <v>15141.08947492517</v>
       </c>
       <c r="E65">
         <v>-360.6700000000001</v>
@@ -6617,45 +6885,45 @@
         <v>1434.75</v>
       </c>
       <c r="M65">
-        <v>1559.563945318869</v>
+        <v>1124.84888831887</v>
       </c>
       <c r="N65">
-        <v>-124.8139453188694</v>
+        <v>309.9011116811305</v>
       </c>
       <c r="O65">
-        <v>-31.20348632971735</v>
+        <v>77.47527792028262</v>
       </c>
       <c r="P65">
-        <v>-93.61045898915205</v>
+        <v>232.4258337608479</v>
       </c>
       <c r="Q65">
-        <v>226.8895410108479</v>
+        <v>552.9258337608478</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2175130877265486</v>
+        <v>0.2149361252504433</v>
       </c>
       <c r="T65">
-        <v>2.655628150978614</v>
+        <v>2.616482065890672</v>
       </c>
       <c r="U65">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V65">
-        <v>0.2299921725406793</v>
+        <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.1129840014111629</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.9199686901627173</v>
+        <v>1.275504661025438</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6934,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1526690731255232</v>
+        <v>0.1296815372542606</v>
       </c>
       <c r="C66">
-        <v>2865.634137766641</v>
+        <v>5046.288245239793</v>
       </c>
       <c r="D66">
-        <v>12943.77413776664</v>
+        <v>15124.42824523979</v>
       </c>
       <c r="E66">
         <v>-191.9599999999991</v>
@@ -6699,45 +6967,45 @@
         <v>1434.75</v>
       </c>
       <c r="M66">
-        <v>1584.318928577899</v>
+        <v>1142.703632577899</v>
       </c>
       <c r="N66">
-        <v>-149.5689285778992</v>
+        <v>292.0463674221007</v>
       </c>
       <c r="O66">
-        <v>-37.3922321444748</v>
+        <v>73.01159185552518</v>
       </c>
       <c r="P66">
-        <v>-112.1766964334244</v>
+        <v>219.0347755665755</v>
       </c>
       <c r="Q66">
-        <v>208.3233035665756</v>
+        <v>539.5347755665755</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2222828957189527</v>
+        <v>0.2191185220172693</v>
       </c>
       <c r="T66">
-        <v>2.729395599616908</v>
+        <v>2.681182413711905</v>
       </c>
       <c r="U66">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V66">
-        <v>0.2263985448447312</v>
+        <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.1135112979167191</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.9055941793789248</v>
+        <v>1.255574900696915</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +7016,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1536783829031907</v>
+        <v>0.1446814395595901</v>
       </c>
       <c r="C67">
-        <v>2615.438951759621</v>
+        <v>3378.586214760779</v>
       </c>
       <c r="D67">
-        <v>12862.28895175962</v>
+        <v>13625.43621476078</v>
       </c>
       <c r="E67">
         <v>-23.25</v>
@@ -6781,37 +7049,37 @@
         <v>1434.75</v>
       </c>
       <c r="M67">
-        <v>1609.073911836929</v>
+        <v>1474.190266836929</v>
       </c>
       <c r="N67">
-        <v>-174.3239118369286</v>
+        <v>-39.44026683692891</v>
       </c>
       <c r="O67">
-        <v>-43.58097795923214</v>
+        <v>-9.860066709232228</v>
       </c>
       <c r="P67">
-        <v>-130.7429338776964</v>
+        <v>-29.58020012769668</v>
       </c>
       <c r="Q67">
-        <v>189.7570661223036</v>
+        <v>290.9197998723033</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2273252641680657</v>
+        <v>0.2244625689006351</v>
       </c>
       <c r="T67">
-        <v>2.807378331034534</v>
+        <v>2.763853119387001</v>
       </c>
       <c r="U67">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V67">
-        <v>0.2229154903086585</v>
+        <v>0.2433115372343433</v>
       </c>
       <c r="W67">
-        <v>0.114022369914412</v>
+        <v>0.101722369914412</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +7087,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8916619612346338</v>
+        <v>0.9732461489373734</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +7098,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1546876926808584</v>
+        <v>0.1455677493372576</v>
       </c>
       <c r="C68">
-        <v>2366.263297935953</v>
+        <v>3130.547215323573</v>
       </c>
       <c r="D68">
-        <v>12781.82329793595</v>
+        <v>13546.10721532357</v>
       </c>
       <c r="E68">
         <v>145.4600000000009</v>
@@ -6863,37 +7131,37 @@
         <v>1434.75</v>
       </c>
       <c r="M68">
-        <v>1633.828895095958</v>
+        <v>1496.870117095959</v>
       </c>
       <c r="N68">
-        <v>-199.0788950959584</v>
+        <v>-62.12011709595868</v>
       </c>
       <c r="O68">
-        <v>-49.7697237739896</v>
+        <v>-15.53002927398967</v>
       </c>
       <c r="P68">
-        <v>-149.3091713219688</v>
+        <v>-46.59008782196901</v>
       </c>
       <c r="Q68">
-        <v>171.1908286780312</v>
+        <v>273.909912178031</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.23266424252595</v>
+        <v>0.229717350338889</v>
       </c>
       <c r="T68">
-        <v>2.889948281947315</v>
+        <v>2.845142917016029</v>
       </c>
       <c r="U68">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V68">
-        <v>0.2195379828797394</v>
+        <v>0.2396249987913988</v>
       </c>
       <c r="W68">
-        <v>0.1145179548818717</v>
+        <v>0.1022179548818718</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7169,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8781519315189574</v>
+        <v>0.958499995165595</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7180,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1556970024585259</v>
+        <v>0.1464540591149252</v>
       </c>
       <c r="C69">
-        <v>2118.088160871293</v>
+        <v>2883.426595742327</v>
       </c>
       <c r="D69">
-        <v>12702.3581608713</v>
+        <v>13467.69659574233</v>
       </c>
       <c r="E69">
         <v>314.1700000000019</v>
@@ -6945,37 +7213,37 @@
         <v>1434.75</v>
       </c>
       <c r="M69">
-        <v>1658.583878354988</v>
+        <v>1519.549967354988</v>
       </c>
       <c r="N69">
-        <v>-223.8338783549882</v>
+        <v>-84.79996735498844</v>
       </c>
       <c r="O69">
-        <v>-55.95846958874705</v>
+        <v>-21.19999183874711</v>
       </c>
       <c r="P69">
-        <v>-167.8754087662412</v>
+        <v>-63.59997551624133</v>
       </c>
       <c r="Q69">
-        <v>152.6245912337588</v>
+        <v>256.9000244837587</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2383267953297666</v>
+        <v>0.2352906033794615</v>
       </c>
       <c r="T69">
-        <v>2.977522472309355</v>
+        <v>2.931359369046819</v>
       </c>
       <c r="U69">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V69">
-        <v>0.2162612965681014</v>
+        <v>0.2360485062721241</v>
       </c>
       <c r="W69">
-        <v>0.1149987462682133</v>
+        <v>0.1026987462682133</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7251,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8650451862724058</v>
+        <v>0.9441940250884965</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7262,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1567063122361935</v>
+        <v>0.1473403688925928</v>
       </c>
       <c r="C70">
-        <v>1870.894995098328</v>
+        <v>2637.208499881577</v>
       </c>
       <c r="D70">
-        <v>12623.87499509833</v>
+        <v>13390.18849988158</v>
       </c>
       <c r="E70">
         <v>482.880000000001</v>
@@ -7027,37 +7295,37 @@
         <v>1434.75</v>
       </c>
       <c r="M70">
-        <v>1683.338861614018</v>
+        <v>1542.229817614018</v>
       </c>
       <c r="N70">
-        <v>-248.5888616140178</v>
+        <v>-107.479817614018</v>
       </c>
       <c r="O70">
-        <v>-62.14721540350445</v>
+        <v>-26.86995440350449</v>
       </c>
       <c r="P70">
-        <v>-186.4416462105133</v>
+        <v>-80.60986321051348</v>
       </c>
       <c r="Q70">
-        <v>134.0583537894867</v>
+        <v>239.8901367894865</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2443432576838219</v>
+        <v>0.2412121847350696</v>
       </c>
       <c r="T70">
-        <v>3.070570049569023</v>
+        <v>3.022964349329532</v>
       </c>
       <c r="U70">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V70">
-        <v>0.2130809833832764</v>
+        <v>0.2325772047092988</v>
       </c>
       <c r="W70">
-        <v>0.1154653967314272</v>
+        <v>0.1031653967314272</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7333,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8523239335331058</v>
+        <v>0.9303088188371952</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7344,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1577156220138611</v>
+        <v>0.1482266786702604</v>
       </c>
       <c r="C71">
-        <v>1624.665710677509</v>
+        <v>2391.877434532464</v>
       </c>
       <c r="D71">
-        <v>12546.35571067751</v>
+        <v>13313.56743453247</v>
       </c>
       <c r="E71">
         <v>651.590000000002</v>
@@ -7109,37 +7377,37 @@
         <v>1434.75</v>
       </c>
       <c r="M71">
-        <v>1708.093844873048</v>
+        <v>1564.909667873048</v>
       </c>
       <c r="N71">
-        <v>-273.3438448730476</v>
+        <v>-130.159667873048</v>
       </c>
       <c r="O71">
-        <v>-68.3359612182619</v>
+        <v>-32.53991696826199</v>
       </c>
       <c r="P71">
-        <v>-205.0078836547857</v>
+        <v>-97.61975090478597</v>
       </c>
       <c r="Q71">
-        <v>115.4921163452143</v>
+        <v>222.880249095214</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.250747878899429</v>
+        <v>0.2475158035974913</v>
       </c>
       <c r="T71">
-        <v>3.169620696329313</v>
+        <v>3.120479328340163</v>
       </c>
       <c r="U71">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V71">
-        <v>0.2099928531893159</v>
+        <v>0.229206520583077</v>
       </c>
       <c r="W71">
-        <v>0.1159185210942581</v>
+        <v>0.1036185210942581</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7415,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8399714127572635</v>
+        <v>0.9168260823323081</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7426,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1587249317915286</v>
+        <v>0.1491129884479279</v>
       </c>
       <c r="C72">
-        <v>1379.382659296134</v>
+        <v>2147.418259088208</v>
       </c>
       <c r="D72">
-        <v>12469.78265929614</v>
+        <v>13237.81825908821</v>
       </c>
       <c r="E72">
         <v>820.3000000000011</v>
@@ -7191,37 +7459,37 @@
         <v>1434.75</v>
       </c>
       <c r="M72">
-        <v>1732.848828132077</v>
+        <v>1587.589518132078</v>
       </c>
       <c r="N72">
-        <v>-298.0988281320772</v>
+        <v>-152.8395181320775</v>
       </c>
       <c r="O72">
-        <v>-74.5247070330193</v>
+        <v>-38.20987953301938</v>
       </c>
       <c r="P72">
-        <v>-223.5741210990579</v>
+        <v>-114.6296385990581</v>
       </c>
       <c r="Q72">
-        <v>96.92587890094211</v>
+        <v>205.8703614009419</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2575794748627433</v>
+        <v>0.2542396637174076</v>
       </c>
       <c r="T72">
-        <v>3.27527471954029</v>
+        <v>3.2244953059515</v>
       </c>
       <c r="U72">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V72">
-        <v>0.2069929552866114</v>
+        <v>0.2259321417176045</v>
       </c>
       <c r="W72">
-        <v>0.1163586990467224</v>
+        <v>0.1040586990467224</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7497,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8279718211464455</v>
+        <v>0.903728566870418</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7508,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1597342415691962</v>
+        <v>0.1499992982255955</v>
       </c>
       <c r="C73">
-        <v>1135.028620873376</v>
+        <v>1903.81617556994</v>
       </c>
       <c r="D73">
-        <v>12394.13862087338</v>
+        <v>13162.92617556994</v>
       </c>
       <c r="E73">
         <v>989.0100000000002</v>
@@ -7273,37 +7541,37 @@
         <v>1434.75</v>
       </c>
       <c r="M73">
-        <v>1757.603811391107</v>
+        <v>1610.269368391107</v>
       </c>
       <c r="N73">
-        <v>-322.8538113911068</v>
+        <v>-175.519368391107</v>
       </c>
       <c r="O73">
-        <v>-80.71345284777669</v>
+        <v>-43.87984209777676</v>
       </c>
       <c r="P73">
-        <v>-242.1403585433301</v>
+        <v>-131.6395262933303</v>
       </c>
       <c r="Q73">
-        <v>78.35964145666992</v>
+        <v>188.8604737066697</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2648822153752516</v>
+        <v>0.2614272383283526</v>
       </c>
       <c r="T73">
-        <v>3.388215227110645</v>
+        <v>3.335684799260172</v>
       </c>
       <c r="U73">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V73">
-        <v>0.2040775615501803</v>
+        <v>0.2227499988765115</v>
       </c>
       <c r="W73">
-        <v>0.116786477620244</v>
+        <v>0.104486477620244</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7579,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.816310246200721</v>
+        <v>0.890999995506046</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7590,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1607435513468638</v>
+        <v>0.1508856080032631</v>
       </c>
       <c r="C74">
-        <v>891.5867906499589</v>
+        <v>1661.056718989294</v>
       </c>
       <c r="D74">
-        <v>12319.40679064996</v>
+        <v>13088.87671898929</v>
       </c>
       <c r="E74">
         <v>1157.719999999999</v>
@@ -7355,37 +7623,37 @@
         <v>1434.75</v>
       </c>
       <c r="M74">
-        <v>1782.358794650136</v>
+        <v>1632.949218650137</v>
       </c>
       <c r="N74">
-        <v>-347.6087946501364</v>
+        <v>-198.1992186501366</v>
       </c>
       <c r="O74">
-        <v>-86.90219866253409</v>
+        <v>-49.54980466253414</v>
       </c>
       <c r="P74">
-        <v>-260.7065959876023</v>
+        <v>-148.6494139876024</v>
       </c>
       <c r="Q74">
-        <v>59.79340401239773</v>
+        <v>171.8505860123976</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.272706580210082</v>
+        <v>0.2691282111257938</v>
       </c>
       <c r="T74">
-        <v>3.509222913793168</v>
+        <v>3.45481639923375</v>
       </c>
       <c r="U74">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V74">
-        <v>0.2012431509730944</v>
+        <v>0.2196562488921155</v>
       </c>
       <c r="W74">
-        <v>0.1172023734556122</v>
+        <v>0.1049023734556122</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7661,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8049726038923777</v>
+        <v>0.8786249955684622</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7672,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2276758001110584</v>
+        <v>0.1517719177809307</v>
       </c>
       <c r="C75">
-        <v>-2796.028780418826</v>
+        <v>1419.125748034408</v>
       </c>
       <c r="D75">
-        <v>8800.501219581174</v>
+        <v>13015.65574803441</v>
       </c>
       <c r="E75">
         <v>1326.43</v>
@@ -7437,45 +7705,45 @@
         <v>1434.75</v>
       </c>
       <c r="M75">
-        <v>2852.727744909167</v>
+        <v>1655.629068909166</v>
       </c>
       <c r="N75">
-        <v>-1417.977744909167</v>
+        <v>-220.8790689091663</v>
       </c>
       <c r="O75">
-        <v>-354.4944362272917</v>
+        <v>-55.21976722729158</v>
       </c>
       <c r="P75">
-        <v>-1063.483308681875</v>
+        <v>-165.6593016818748</v>
       </c>
       <c r="Q75">
-        <v>-742.9833086818749</v>
+        <v>154.8406983181252</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2957251164642592</v>
+        <v>0.2773996263526751</v>
       </c>
       <c r="T75">
-        <v>3.86521600482803</v>
+        <v>3.582772562168334</v>
       </c>
       <c r="U75">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V75">
-        <v>0.1257349218270462</v>
+        <v>0.2166472591812646</v>
       </c>
       <c r="W75">
-        <v>0.2025068748845321</v>
+        <v>0.1053068748845321</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5029396873081851</v>
+        <v>0.8665890367250585</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7754,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2295341098887259</v>
+        <v>0.1526582275585982</v>
       </c>
       <c r="C76">
-        <v>-3033.982012770432</v>
+        <v>1178.009436066848</v>
       </c>
       <c r="D76">
-        <v>8731.257987229568</v>
+        <v>12943.24943606685</v>
       </c>
       <c r="E76">
         <v>1495.139999999999</v>
@@ -7519,45 +7787,45 @@
         <v>1434.75</v>
       </c>
       <c r="M76">
-        <v>2891.806207168196</v>
+        <v>1678.308919168196</v>
       </c>
       <c r="N76">
-        <v>-1457.056207168196</v>
+        <v>-243.5589191681959</v>
       </c>
       <c r="O76">
-        <v>-364.264051792049</v>
+        <v>-60.88972979204897</v>
       </c>
       <c r="P76">
-        <v>-1092.792155376147</v>
+        <v>-182.6691893761469</v>
       </c>
       <c r="Q76">
-        <v>-772.2921553761471</v>
+        <v>137.8308106238531</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.3053376209436537</v>
+        <v>0.2863073042893164</v>
       </c>
       <c r="T76">
-        <v>4.013878158859877</v>
+        <v>3.720571506867115</v>
       </c>
       <c r="U76">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V76">
-        <v>0.1240358012618159</v>
+        <v>0.213719593516653</v>
       </c>
       <c r="W76">
-        <v>0.2029004438424</v>
+        <v>0.1057004438424</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4961432050472636</v>
+        <v>0.8548783740666118</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7836,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2313924196663935</v>
+        <v>0.1535445373362658</v>
       </c>
       <c r="C77">
-        <v>-3270.854125986656</v>
+        <v>937.6942624173498</v>
       </c>
       <c r="D77">
-        <v>8663.095874013345</v>
+        <v>12871.64426241735</v>
       </c>
       <c r="E77">
         <v>1663.85</v>
@@ -7601,45 +7869,45 @@
         <v>1434.75</v>
       </c>
       <c r="M77">
-        <v>2930.884669427226</v>
+        <v>1700.988769427226</v>
       </c>
       <c r="N77">
-        <v>-1496.134669427226</v>
+        <v>-266.2387694272256</v>
       </c>
       <c r="O77">
-        <v>-374.0336673568064</v>
+        <v>-66.55969235680641</v>
       </c>
       <c r="P77">
-        <v>-1122.101002070419</v>
+        <v>-199.6790770704192</v>
       </c>
       <c r="Q77">
-        <v>-801.6010020704193</v>
+        <v>120.8209229295808</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3157191257813999</v>
+        <v>0.2959275964608891</v>
       </c>
       <c r="T77">
-        <v>4.174433285214273</v>
+        <v>3.869394367141801</v>
       </c>
       <c r="U77">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V77">
-        <v>0.122381990578325</v>
+        <v>0.2108699989364309</v>
       </c>
       <c r="W77">
-        <v>0.2032835176280581</v>
+        <v>0.1060835176280581</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4895279623133001</v>
+        <v>0.8434799957457236</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7918,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2332507294440611</v>
+        <v>0.1544308471139334</v>
       </c>
       <c r="C78">
-        <v>-3506.670243779297</v>
+        <v>698.1670039689252</v>
       </c>
       <c r="D78">
-        <v>8595.989756220704</v>
+        <v>12800.82700396893</v>
       </c>
       <c r="E78">
         <v>1832.560000000001</v>
@@ -7683,45 +7951,45 @@
         <v>1434.75</v>
       </c>
       <c r="M78">
-        <v>2969.963131686256</v>
+        <v>1723.668619686256</v>
       </c>
       <c r="N78">
-        <v>-1535.213131686256</v>
+        <v>-288.9186196862556</v>
       </c>
       <c r="O78">
-        <v>-383.8032829215639</v>
+        <v>-72.22965492156391</v>
       </c>
       <c r="P78">
-        <v>-1151.409848764692</v>
+        <v>-216.6889647646917</v>
       </c>
       <c r="Q78">
-        <v>-830.9098487646916</v>
+        <v>103.8110352353083</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3269657560222917</v>
+        <v>0.3063495796467595</v>
       </c>
       <c r="T78">
-        <v>4.348368005431535</v>
+        <v>4.030619132439376</v>
       </c>
       <c r="U78">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V78">
-        <v>0.1207717012286102</v>
+        <v>0.2080953936872673</v>
       </c>
       <c r="W78">
-        <v>0.2036565105246199</v>
+        <v>0.1064565105246199</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4830868049144409</v>
+        <v>0.8323815747490693</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +8000,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2351090392217287</v>
+        <v>0.155317156891601</v>
       </c>
       <c r="C79">
-        <v>-3741.454717390183</v>
+        <v>459.4147270162666</v>
       </c>
       <c r="D79">
-        <v>8529.915282609818</v>
+        <v>12730.78472701627</v>
       </c>
       <c r="E79">
         <v>2001.27</v>
@@ -7765,45 +8033,45 @@
         <v>1434.75</v>
       </c>
       <c r="M79">
-        <v>3009.041593945285</v>
+        <v>1746.348469945285</v>
       </c>
       <c r="N79">
-        <v>-1574.291593945285</v>
+        <v>-311.5984699452852</v>
       </c>
       <c r="O79">
-        <v>-393.5728984863213</v>
+        <v>-77.89961748632129</v>
       </c>
       <c r="P79">
-        <v>-1180.718695458964</v>
+        <v>-233.6988524589639</v>
       </c>
       <c r="Q79">
-        <v>-860.2186954589638</v>
+        <v>86.80114754103613</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3391903541102174</v>
+        <v>0.3176778222400969</v>
       </c>
       <c r="T79">
-        <v>4.537427483928558</v>
+        <v>4.205863442545436</v>
       </c>
       <c r="U79">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V79">
-        <v>0.1192032375762906</v>
+        <v>0.2053928561069132</v>
       </c>
       <c r="W79">
-        <v>0.2040198152939983</v>
+        <v>0.1068198152939983</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4768129503051625</v>
+        <v>0.8215714244276529</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +8082,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2369673489993963</v>
+        <v>0.1562034666692685</v>
       </c>
       <c r="C80">
-        <v>-3975.231155053261</v>
+        <v>221.4247793909617</v>
       </c>
       <c r="D80">
-        <v>8464.84884494674</v>
+        <v>12661.50477939096</v>
       </c>
       <c r="E80">
         <v>2169.980000000001</v>
@@ -7847,45 +8115,45 @@
         <v>1434.75</v>
       </c>
       <c r="M80">
-        <v>3048.120056204315</v>
+        <v>1769.028320204315</v>
       </c>
       <c r="N80">
-        <v>-1613.370056204315</v>
+        <v>-334.2783202043149</v>
       </c>
       <c r="O80">
-        <v>-403.3425140510788</v>
+        <v>-83.56958005107873</v>
       </c>
       <c r="P80">
-        <v>-1210.027542153236</v>
+        <v>-250.7087401532362</v>
       </c>
       <c r="Q80">
-        <v>-889.5275421532363</v>
+        <v>69.79125984676381</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3525262792970454</v>
+        <v>0.3300359050691922</v>
       </c>
       <c r="T80">
-        <v>4.743674187743492</v>
+        <v>4.397039053570228</v>
       </c>
       <c r="U80">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V80">
-        <v>0.1176749909406971</v>
+        <v>0.2027596143619528</v>
       </c>
       <c r="W80">
-        <v>0.2043738045564696</v>
+        <v>0.1071738045564696</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4706999637627886</v>
+        <v>0.8110384574478111</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8164,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2388256587770639</v>
+        <v>0.1570897764469361</v>
       </c>
       <c r="C81">
-        <v>-4208.022450118491</v>
+        <v>-15.81521715753297</v>
       </c>
       <c r="D81">
-        <v>8400.76754988151</v>
+        <v>12592.97478284247</v>
       </c>
       <c r="E81">
         <v>2338.690000000001</v>
@@ -7929,45 +8197,45 @@
         <v>1434.75</v>
       </c>
       <c r="M81">
-        <v>3087.198518463344</v>
+        <v>1791.708170463344</v>
       </c>
       <c r="N81">
-        <v>-1652.448518463344</v>
+        <v>-356.9581704633445</v>
       </c>
       <c r="O81">
-        <v>-413.1121296158361</v>
+        <v>-89.23954261583611</v>
       </c>
       <c r="P81">
-        <v>-1239.336388847508</v>
+        <v>-267.7186278475083</v>
       </c>
       <c r="Q81">
-        <v>-918.8363888475083</v>
+        <v>52.78137215249166</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3671322925969048</v>
+        <v>0.3435709481677252</v>
       </c>
       <c r="T81">
-        <v>4.969563434778897</v>
+        <v>4.606421865645001</v>
       </c>
       <c r="U81">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V81">
-        <v>0.1161854340933465</v>
+        <v>0.200193036964966</v>
       </c>
       <c r="W81">
-        <v>0.2047188320654606</v>
+        <v>0.1075188320654606</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4647417363733861</v>
+        <v>0.8007721478598642</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8246,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2406839685547314</v>
+        <v>0.1825730818020935</v>
       </c>
       <c r="C82">
-        <v>-4439.850807907929</v>
+        <v>-1880.341741005695</v>
       </c>
       <c r="D82">
-        <v>8337.649192092073</v>
+        <v>10897.15825899431</v>
       </c>
       <c r="E82">
         <v>2507.400000000001</v>
@@ -8011,45 +8279,45 @@
         <v>1434.75</v>
       </c>
       <c r="M82">
-        <v>3126.276980722374</v>
+        <v>2194.997780722375</v>
       </c>
       <c r="N82">
-        <v>-1691.526980722374</v>
+        <v>-760.2477807223745</v>
       </c>
       <c r="O82">
-        <v>-422.8817451805936</v>
+        <v>-190.0619451805936</v>
       </c>
       <c r="P82">
-        <v>-1268.645235541781</v>
+        <v>-570.1858355417809</v>
       </c>
       <c r="Q82">
-        <v>-948.1452355417809</v>
+        <v>-249.6858355417809</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.38319890722675</v>
+        <v>0.3686444734635606</v>
       </c>
       <c r="T82">
-        <v>5.218041606517842</v>
+        <v>4.994301327634966</v>
       </c>
       <c r="U82">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V82">
-        <v>0.1147331161671797</v>
+        <v>0.1634113269499324</v>
       </c>
       <c r="W82">
-        <v>0.2050552338867268</v>
+        <v>0.1360552338867268</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4589324646687188</v>
+        <v>0.6536453077997297</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8328,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.242542278332399</v>
+        <v>0.2299019386652058</v>
       </c>
       <c r="C83">
-        <v>-4670.737771370103</v>
+        <v>-4229.209242435858</v>
       </c>
       <c r="D83">
-        <v>8275.472228629898</v>
+        <v>8717.000757564143</v>
       </c>
       <c r="E83">
         <v>2676.110000000001</v>
@@ -8093,37 +8361,37 @@
         <v>1434.75</v>
       </c>
       <c r="M83">
-        <v>3165.355442981404</v>
+        <v>2960.372792981404</v>
       </c>
       <c r="N83">
-        <v>-1730.605442981404</v>
+        <v>-1525.622792981404</v>
       </c>
       <c r="O83">
-        <v>-432.651360745351</v>
+        <v>-381.4056982453509</v>
       </c>
       <c r="P83">
-        <v>-1297.954082236053</v>
+        <v>-1144.217094736053</v>
       </c>
       <c r="Q83">
-        <v>-977.454082236053</v>
+        <v>-823.7170947360528</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.4009567444492106</v>
+        <v>0.3983760093587198</v>
       </c>
       <c r="T83">
-        <v>5.49267537528194</v>
+        <v>5.454238732171583</v>
       </c>
       <c r="U83">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V83">
-        <v>0.1133166579428935</v>
+        <v>0.121162949764433</v>
       </c>
       <c r="W83">
-        <v>0.205383329490184</v>
+        <v>0.190383329490184</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8399,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4532666317715741</v>
+        <v>0.484651799057732</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8410,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2444005881100666</v>
+        <v>0.2316102484428733</v>
       </c>
       <c r="C84">
-        <v>-4900.704245595056</v>
+        <v>-4460.415988555542</v>
       </c>
       <c r="D84">
-        <v>8214.215754404946</v>
+        <v>8654.50401144446</v>
       </c>
       <c r="E84">
         <v>2844.820000000002</v>
@@ -8175,37 +8443,37 @@
         <v>1434.75</v>
       </c>
       <c r="M84">
-        <v>3204.433905240434</v>
+        <v>2996.920605240434</v>
       </c>
       <c r="N84">
-        <v>-1769.683905240434</v>
+        <v>-1562.170605240434</v>
       </c>
       <c r="O84">
-        <v>-442.4209763101085</v>
+        <v>-390.5426513101085</v>
       </c>
       <c r="P84">
-        <v>-1327.262928930325</v>
+        <v>-1171.627953930325</v>
       </c>
       <c r="Q84">
-        <v>-1006.762928930325</v>
+        <v>-851.1279539303255</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.4206876746963889</v>
+        <v>0.4179635654342042</v>
       </c>
       <c r="T84">
-        <v>5.797824007242047</v>
+        <v>5.757251995070004</v>
       </c>
       <c r="U84">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V84">
-        <v>0.1119347474801753</v>
+        <v>0.1196853528160862</v>
       </c>
       <c r="W84">
-        <v>0.2057034227618495</v>
+        <v>0.1907034227618495</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8481,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4477389899207013</v>
+        <v>0.4787414112643449</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8492,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2462588978877342</v>
+        <v>0.2333185582205409</v>
       </c>
       <c r="C85">
-        <v>-5129.770521248545</v>
+        <v>-4690.732970022089</v>
       </c>
       <c r="D85">
-        <v>8153.859478751456</v>
+        <v>8592.897029977912</v>
       </c>
       <c r="E85">
         <v>3013.530000000001</v>
@@ -8257,37 +8525,37 @@
         <v>1434.75</v>
       </c>
       <c r="M85">
-        <v>3243.512367499463</v>
+        <v>3033.468417499463</v>
       </c>
       <c r="N85">
-        <v>-1808.762367499463</v>
+        <v>-1598.718417499463</v>
       </c>
       <c r="O85">
-        <v>-452.1905918748658</v>
+        <v>-399.6796043748658</v>
       </c>
       <c r="P85">
-        <v>-1356.571775624598</v>
+        <v>-1199.038813124597</v>
       </c>
       <c r="Q85">
-        <v>-1036.071775624598</v>
+        <v>-878.5388131245973</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4427398908550001</v>
+        <v>0.4398555398715104</v>
       </c>
       <c r="T85">
-        <v>6.138872478256286</v>
+        <v>6.095913877132946</v>
       </c>
       <c r="U85">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1105861360647515</v>
+        <v>0.1182433606134828</v>
       </c>
       <c r="W85">
-        <v>0.2060158029426315</v>
+        <v>0.1910158029426315</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8563,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.442344544259006</v>
+        <v>0.4729734424539311</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8574,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2481172076654017</v>
+        <v>0.2350268679982085</v>
       </c>
       <c r="C86">
-        <v>-5357.956296980703</v>
+        <v>-4920.179053867319</v>
       </c>
       <c r="D86">
-        <v>8094.383703019296</v>
+        <v>8532.160946132681</v>
       </c>
       <c r="E86">
         <v>3182.24</v>
@@ -8339,37 +8607,37 @@
         <v>1434.75</v>
       </c>
       <c r="M86">
-        <v>3282.590829758493</v>
+        <v>3070.016229758492</v>
       </c>
       <c r="N86">
-        <v>-1847.840829758493</v>
+        <v>-1635.266229758492</v>
       </c>
       <c r="O86">
-        <v>-461.9602074396232</v>
+        <v>-408.8165574396231</v>
       </c>
       <c r="P86">
-        <v>-1385.88062231887</v>
+        <v>-1226.449672318869</v>
       </c>
       <c r="Q86">
-        <v>-1065.38062231887</v>
+        <v>-905.9496723188695</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4675486340334374</v>
+        <v>0.4644840111134795</v>
       </c>
       <c r="T86">
-        <v>6.522552008147301</v>
+        <v>6.476908494453752</v>
       </c>
       <c r="U86">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1092696344449331</v>
+        <v>0.1168357015585604</v>
       </c>
       <c r="W86">
-        <v>0.2063207455000616</v>
+        <v>0.1913207455000616</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8645,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4370785377797323</v>
+        <v>0.4673428062342415</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8656,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2499755174430693</v>
+        <v>0.236735177775876</v>
       </c>
       <c r="C87">
-        <v>-5585.280700861031</v>
+        <v>-5148.772577445126</v>
       </c>
       <c r="D87">
-        <v>8035.769299138969</v>
+        <v>8472.277422554875</v>
       </c>
       <c r="E87">
         <v>3350.950000000001</v>
@@ -8421,37 +8689,37 @@
         <v>1434.75</v>
       </c>
       <c r="M87">
-        <v>3321.669292017523</v>
+        <v>3106.564042017522</v>
       </c>
       <c r="N87">
-        <v>-1886.919292017523</v>
+        <v>-1671.814042017522</v>
       </c>
       <c r="O87">
-        <v>-471.7298230043807</v>
+        <v>-417.9535105043806</v>
       </c>
       <c r="P87">
-        <v>-1415.189469013142</v>
+        <v>-1253.860531513142</v>
       </c>
       <c r="Q87">
-        <v>-1094.689469013142</v>
+        <v>-933.3605315131417</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4956652096356666</v>
+        <v>0.4923962785210449</v>
       </c>
       <c r="T87">
-        <v>6.957388808690455</v>
+        <v>6.908702394084003</v>
       </c>
       <c r="U87">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1079841093338162</v>
+        <v>0.1154611638931656</v>
       </c>
       <c r="W87">
-        <v>0.2066185129384933</v>
+        <v>0.1916185129384933</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8727,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4319364373352648</v>
+        <v>0.4618446555726622</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8738,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2518338272207369</v>
+        <v>0.2384434875535436</v>
       </c>
       <c r="C88">
-        <v>-5811.762310888789</v>
+        <v>-5376.531366889809</v>
       </c>
       <c r="D88">
-        <v>7977.99768911121</v>
+        <v>8413.228633110191</v>
       </c>
       <c r="E88">
         <v>3519.66</v>
@@ -8503,37 +8771,37 @@
         <v>1434.75</v>
       </c>
       <c r="M88">
-        <v>3360.747754276552</v>
+        <v>3143.111854276552</v>
       </c>
       <c r="N88">
-        <v>-1925.997754276552</v>
+        <v>-1708.361854276552</v>
       </c>
       <c r="O88">
-        <v>-481.4994385691381</v>
+        <v>-427.090463569138</v>
       </c>
       <c r="P88">
-        <v>-1444.498315707414</v>
+        <v>-1281.271390707414</v>
       </c>
       <c r="Q88">
-        <v>-1123.998315707414</v>
+        <v>-960.771390707414</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.527798438895357</v>
+        <v>0.5242960127011196</v>
       </c>
       <c r="T88">
-        <v>7.454345152168345</v>
+        <v>7.402181136518575</v>
       </c>
       <c r="U88">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V88">
-        <v>0.106728480155516</v>
+        <v>0.1141185922199892</v>
       </c>
       <c r="W88">
-        <v>0.2069093555527755</v>
+        <v>0.1919093555527754</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8809,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.426913920622064</v>
+        <v>0.4564743688799568</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8820,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2536921369984045</v>
+        <v>0.2401517973312112</v>
       </c>
       <c r="C89">
-        <v>-6037.419174624993</v>
+        <v>-5603.472754807875</v>
       </c>
       <c r="D89">
-        <v>7921.050825375008</v>
+        <v>8354.997245192126</v>
       </c>
       <c r="E89">
         <v>3688.370000000001</v>
@@ -8585,37 +8853,37 @@
         <v>1434.75</v>
       </c>
       <c r="M89">
-        <v>3399.826216535582</v>
+        <v>3179.659666535582</v>
       </c>
       <c r="N89">
-        <v>-1965.076216535582</v>
+        <v>-1744.909666535582</v>
       </c>
       <c r="O89">
-        <v>-491.2690541338956</v>
+        <v>-436.2274166338955</v>
       </c>
       <c r="P89">
-        <v>-1473.807162401687</v>
+        <v>-1308.682249901686</v>
       </c>
       <c r="Q89">
-        <v>-1153.307162401687</v>
+        <v>-988.1822499016864</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5648752418873074</v>
+        <v>0.5611033982935133</v>
       </c>
       <c r="T89">
-        <v>8.027756317719755</v>
+        <v>7.971579685481542</v>
       </c>
       <c r="U89">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1055017160157974</v>
+        <v>0.1128068842634376</v>
       </c>
       <c r="W89">
-        <v>0.2071935121299477</v>
+        <v>0.1921935121299477</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8891,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4220068640631897</v>
+        <v>0.4512275370537504</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8902,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.255550446776072</v>
+        <v>0.2418601071088788</v>
       </c>
       <c r="C90">
-        <v>-6262.268827989532</v>
+        <v>-5829.613597240168</v>
       </c>
       <c r="D90">
-        <v>7864.911172010467</v>
+        <v>8297.566402759832</v>
       </c>
       <c r="E90">
         <v>3857.08</v>
@@ -8667,37 +8935,37 @@
         <v>1434.75</v>
       </c>
       <c r="M90">
-        <v>3438.904678794612</v>
+        <v>3216.207478794611</v>
       </c>
       <c r="N90">
-        <v>-2004.154678794612</v>
+        <v>-1781.457478794611</v>
       </c>
       <c r="O90">
-        <v>-501.0386696986529</v>
+        <v>-445.3643696986528</v>
       </c>
       <c r="P90">
-        <v>-1503.116009095959</v>
+        <v>-1336.093109095958</v>
       </c>
       <c r="Q90">
-        <v>-1182.616009095959</v>
+        <v>-1015.593109095958</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.6081315120445833</v>
+        <v>0.6040453481513061</v>
       </c>
       <c r="T90">
-        <v>8.69673601086307</v>
+        <v>8.635877992605003</v>
       </c>
       <c r="U90">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1043028328792543</v>
+        <v>0.1115249878513531</v>
       </c>
       <c r="W90">
-        <v>0.2074712106030932</v>
+        <v>0.1924712106030932</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8973,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4172113315170171</v>
+        <v>0.4460999514054124</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8984,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2574087565537396</v>
+        <v>0.2435684168865463</v>
       </c>
       <c r="C91">
-        <v>-6486.328313264619</v>
+        <v>-6054.970289929217</v>
       </c>
       <c r="D91">
-        <v>7809.561686735381</v>
+        <v>8240.919710070784</v>
       </c>
       <c r="E91">
         <v>4025.790000000001</v>
@@ -8749,37 +9017,37 @@
         <v>1434.75</v>
       </c>
       <c r="M91">
-        <v>3477.983141053641</v>
+        <v>3252.755291053641</v>
       </c>
       <c r="N91">
-        <v>-2043.233141053641</v>
+        <v>-1818.005291053641</v>
       </c>
       <c r="O91">
-        <v>-510.8082852634103</v>
+        <v>-454.5013227634103</v>
       </c>
       <c r="P91">
-        <v>-1532.424855790231</v>
+        <v>-1363.503968290231</v>
       </c>
       <c r="Q91">
-        <v>-1211.924855790231</v>
+        <v>-1043.003968290231</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6592525585940907</v>
+        <v>0.6547949252559704</v>
       </c>
       <c r="T91">
-        <v>9.487348375486985</v>
+        <v>9.420957810114551</v>
       </c>
       <c r="U91">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1031308909367907</v>
+        <v>0.1102718981002143</v>
       </c>
       <c r="W91">
-        <v>0.2077426686611119</v>
+        <v>0.1927426686611119</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +9055,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.412523563747163</v>
+        <v>0.4410875924008572</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +9066,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2592670663314072</v>
+        <v>0.2452767266642139</v>
       </c>
       <c r="C92">
-        <v>-6709.614196343322</v>
+        <v>-6279.558783924756</v>
       </c>
       <c r="D92">
-        <v>7754.985803656677</v>
+        <v>8185.041216075243</v>
       </c>
       <c r="E92">
         <v>4194.5</v>
@@ -8831,37 +9099,37 @@
         <v>1434.75</v>
       </c>
       <c r="M92">
-        <v>3517.061603312671</v>
+        <v>3289.303103312671</v>
       </c>
       <c r="N92">
-        <v>-2082.311603312671</v>
+        <v>-1854.553103312671</v>
       </c>
       <c r="O92">
-        <v>-520.5779008281677</v>
+        <v>-463.6382758281677</v>
       </c>
       <c r="P92">
-        <v>-1561.733702484503</v>
+        <v>-1390.914827484503</v>
       </c>
       <c r="Q92">
-        <v>-1241.233702484503</v>
+        <v>-1070.414827484503</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.7205978144534999</v>
+        <v>0.7156944177815675</v>
       </c>
       <c r="T92">
-        <v>10.43608321303568</v>
+        <v>10.36305359112601</v>
       </c>
       <c r="U92">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1019849921486042</v>
+        <v>0.1090466547879897</v>
       </c>
       <c r="W92">
-        <v>0.2080080943178413</v>
+        <v>0.1930080943178413</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +9137,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4079399685944167</v>
+        <v>0.4361866191519588</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9148,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2611253761090748</v>
+        <v>0.2469850364418815</v>
       </c>
       <c r="C93">
-        <v>-6932.142583259889</v>
+        <v>-6503.394600558646</v>
       </c>
       <c r="D93">
-        <v>7701.167416740112</v>
+        <v>8129.915399441355</v>
       </c>
       <c r="E93">
         <v>4363.210000000001</v>
@@ -8913,37 +9181,37 @@
         <v>1434.75</v>
       </c>
       <c r="M93">
-        <v>3556.140065571701</v>
+        <v>3325.850915571701</v>
       </c>
       <c r="N93">
-        <v>-2121.390065571701</v>
+        <v>-1891.100915571701</v>
       </c>
       <c r="O93">
-        <v>-530.3475163929252</v>
+        <v>-472.7752288929252</v>
       </c>
       <c r="P93">
-        <v>-1591.042549178776</v>
+        <v>-1418.325686678776</v>
       </c>
       <c r="Q93">
-        <v>-1270.542549178776</v>
+        <v>-1097.825686678776</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7955753493927777</v>
+        <v>0.7901271308684084</v>
       </c>
       <c r="T93">
-        <v>11.59564801448409</v>
+        <v>11.51450399014001</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V93">
-        <v>0.100864277949169</v>
+        <v>0.1078483399002096</v>
       </c>
       <c r="W93">
-        <v>0.2082676864436536</v>
+        <v>0.1932676864436536</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9219,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4034571117966759</v>
+        <v>0.4313933596008384</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9230,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2629836858867424</v>
+        <v>0.2486933462195491</v>
       </c>
       <c r="C94">
-        <v>-7153.929136036526</v>
+        <v>-6726.492845818682</v>
       </c>
       <c r="D94">
-        <v>7648.090863963476</v>
+        <v>8075.52715418132</v>
       </c>
       <c r="E94">
         <v>4531.920000000002</v>
@@ -8995,37 +9263,37 @@
         <v>1434.75</v>
       </c>
       <c r="M94">
-        <v>3595.218527830731</v>
+        <v>3362.39872783073</v>
       </c>
       <c r="N94">
-        <v>-2160.468527830731</v>
+        <v>-1927.64872783073</v>
       </c>
       <c r="O94">
-        <v>-540.1171319576827</v>
+        <v>-481.9121819576826</v>
       </c>
       <c r="P94">
-        <v>-1620.351395873048</v>
+        <v>-1445.736545873048</v>
       </c>
       <c r="Q94">
-        <v>-1299.851395873048</v>
+        <v>-1125.236545873048</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8892972680668754</v>
+        <v>0.8831680222269598</v>
       </c>
       <c r="T94">
-        <v>13.04510401629461</v>
+        <v>12.95381698890751</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V94">
-        <v>0.09976792710189539</v>
+        <v>0.1066760753360769</v>
       </c>
       <c r="W94">
-        <v>0.208521635262383</v>
+        <v>0.193521635262383</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9301,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3990717084075815</v>
+        <v>0.4267043013443075</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9312,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2648419956644099</v>
+        <v>0.2504016559972166</v>
       </c>
       <c r="C95">
-        <v>-7374.989087879341</v>
+        <v>-6948.868224149308</v>
       </c>
       <c r="D95">
-        <v>7595.74091212066</v>
+        <v>8021.861775850693</v>
       </c>
       <c r="E95">
         <v>4700.630000000001</v>
@@ -9077,37 +9345,37 @@
         <v>1434.75</v>
       </c>
       <c r="M95">
-        <v>3634.29699008976</v>
+        <v>3398.94654008976</v>
       </c>
       <c r="N95">
-        <v>-2199.54699008976</v>
+        <v>-1964.19654008976</v>
       </c>
       <c r="O95">
-        <v>-549.88674752244</v>
+        <v>-491.0491350224399</v>
       </c>
       <c r="P95">
-        <v>-1649.66024256732</v>
+        <v>-1473.14740506732</v>
       </c>
       <c r="Q95">
-        <v>-1329.16024256732</v>
+        <v>-1152.64740506732</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.009796877790715</v>
+        <v>1.00279202540224</v>
       </c>
       <c r="T95">
-        <v>14.9086903043367</v>
+        <v>14.80436227303716</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V95">
-        <v>0.0986951536921976</v>
+        <v>0.1055290207625707</v>
       </c>
       <c r="W95">
-        <v>0.2087701228161935</v>
+        <v>0.1937701228161935</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9383,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3947806147687903</v>
+        <v>0.4221160830502827</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9394,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2667003054420775</v>
+        <v>0.2521099657748843</v>
       </c>
       <c r="C96">
-        <v>-7595.337257754478</v>
+        <v>-7170.535051705716</v>
       </c>
       <c r="D96">
-        <v>7544.102742245524</v>
+        <v>7968.904948294286</v>
       </c>
       <c r="E96">
         <v>4869.340000000002</v>
@@ -9159,37 +9427,37 @@
         <v>1434.75</v>
       </c>
       <c r="M96">
-        <v>3673.37545234879</v>
+        <v>3435.49435234879</v>
       </c>
       <c r="N96">
-        <v>-2238.62545234879</v>
+        <v>-2000.74435234879</v>
       </c>
       <c r="O96">
-        <v>-559.6563630871975</v>
+        <v>-500.1860880871975</v>
       </c>
       <c r="P96">
-        <v>-1678.969089261593</v>
+        <v>-1500.558264261593</v>
       </c>
       <c r="Q96">
-        <v>-1358.469089261593</v>
+        <v>-1180.058264261593</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.170463024089168</v>
+        <v>1.162290696302613</v>
       </c>
       <c r="T96">
-        <v>17.39347202172615</v>
+        <v>17.27175598521002</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V96">
-        <v>0.09764520524866357</v>
+        <v>0.104406371605522</v>
       </c>
       <c r="W96">
-        <v>0.2090133234007739</v>
+        <v>0.1940133234007739</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9465,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3905808209946543</v>
+        <v>0.4176254864220881</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9476,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2685586152197451</v>
+        <v>0.2538182755525519</v>
       </c>
       <c r="C97">
-        <v>-7814.988064373665</v>
+        <v>-7391.507269086322</v>
       </c>
       <c r="D97">
-        <v>7493.161935626336</v>
+        <v>7916.642730913679</v>
       </c>
       <c r="E97">
         <v>5038.050000000001</v>
@@ -9241,37 +9509,37 @@
         <v>1434.75</v>
       </c>
       <c r="M97">
-        <v>3712.45391460782</v>
+        <v>3472.042164607819</v>
       </c>
       <c r="N97">
-        <v>-2277.70391460782</v>
+        <v>-2037.292164607819</v>
       </c>
       <c r="O97">
-        <v>-569.4259786519549</v>
+        <v>-509.3230411519548</v>
       </c>
       <c r="P97">
-        <v>-1708.277935955865</v>
+        <v>-1527.969123455865</v>
       </c>
       <c r="Q97">
-        <v>-1387.777935955865</v>
+        <v>-1207.469123455865</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.395395628907002</v>
+        <v>1.385588835563137</v>
       </c>
       <c r="T97">
-        <v>20.8721664260714</v>
+        <v>20.72610718225204</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.09661736098288817</v>
+        <v>0.1033073571675692</v>
       </c>
       <c r="W97">
-        <v>0.2092514039730475</v>
+        <v>0.1942514039730475</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9547,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3864694439315527</v>
+        <v>0.4132294286702767</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9558,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2704169249974127</v>
+        <v>0.2555265853302194</v>
       </c>
       <c r="C98">
-        <v>-8033.955539616978</v>
+        <v>-7611.798453567564</v>
       </c>
       <c r="D98">
-        <v>7442.904460383022</v>
+        <v>7865.061546432436</v>
       </c>
       <c r="E98">
         <v>5206.76</v>
@@ -9323,37 +9591,37 @@
         <v>1434.75</v>
       </c>
       <c r="M98">
-        <v>3751.532376866849</v>
+        <v>3508.589976866849</v>
       </c>
       <c r="N98">
-        <v>-2316.782376866849</v>
+        <v>-2073.839976866849</v>
       </c>
       <c r="O98">
-        <v>-579.1955942167123</v>
+        <v>-518.4599942167122</v>
       </c>
       <c r="P98">
-        <v>-1737.586782650137</v>
+        <v>-1555.379982650137</v>
       </c>
       <c r="Q98">
-        <v>-1417.086782650137</v>
+        <v>-1234.879982650137</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.732794536133748</v>
+        <v>1.720536044453917</v>
       </c>
       <c r="T98">
-        <v>26.09020803258919</v>
+        <v>25.90763397781499</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.09561093013931643</v>
+        <v>0.1022312388637403</v>
       </c>
       <c r="W98">
-        <v>0.2094845245333986</v>
+        <v>0.1944845245333986</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9629,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3824437205572657</v>
+        <v>0.4089249554549613</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9640,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2722752347750803</v>
+        <v>0.2572348951078869</v>
       </c>
       <c r="C99">
-        <v>-8252.253341419044</v>
+        <v>-7831.421830863485</v>
       </c>
       <c r="D99">
-        <v>7393.316658580954</v>
+        <v>7814.148169136515</v>
       </c>
       <c r="E99">
         <v>5375.469999999999</v>
@@ -9405,37 +9673,37 @@
         <v>1434.75</v>
       </c>
       <c r="M99">
-        <v>3790.610839125879</v>
+        <v>3545.137789125878</v>
       </c>
       <c r="N99">
-        <v>-2355.860839125879</v>
+        <v>-2110.387789125878</v>
       </c>
       <c r="O99">
-        <v>-588.9652097814696</v>
+        <v>-527.5969472814696</v>
       </c>
       <c r="P99">
-        <v>-1766.895629344409</v>
+        <v>-1582.790841844409</v>
       </c>
       <c r="Q99">
-        <v>-1446.395629344409</v>
+        <v>-1262.290841844409</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.295126048178331</v>
+        <v>2.278781392605222</v>
       </c>
       <c r="T99">
-        <v>34.78694404345225</v>
+        <v>34.54351197041998</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.09462525044715853</v>
+        <v>0.101177308566176</v>
       </c>
       <c r="W99">
-        <v>0.209712838484258</v>
+        <v>0.194712838484258</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9711,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3785010017886341</v>
+        <v>0.404709234264704</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9722,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2741335445527478</v>
+        <v>0.2589432048855546</v>
       </c>
       <c r="C100">
-        <v>-8469.894766143494</v>
+        <v>-8050.390286431468</v>
       </c>
       <c r="D100">
-        <v>7344.385233856504</v>
+        <v>7763.88971356853</v>
       </c>
       <c r="E100">
         <v>5544.179999999998</v>
@@ -9487,37 +9755,37 @@
         <v>1434.75</v>
       </c>
       <c r="M100">
-        <v>3829.689301384908</v>
+        <v>3581.685601384908</v>
       </c>
       <c r="N100">
-        <v>-2394.939301384908</v>
+        <v>-2146.935601384908</v>
       </c>
       <c r="O100">
-        <v>-598.734825346227</v>
+        <v>-536.733900346227</v>
       </c>
       <c r="P100">
-        <v>-1796.204476038681</v>
+        <v>-1610.201701038681</v>
       </c>
       <c r="Q100">
-        <v>-1475.704476038681</v>
+        <v>-1289.701701038681</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.419789072267496</v>
+        <v>3.395272088907834</v>
       </c>
       <c r="T100">
-        <v>52.18041606517837</v>
+        <v>51.81526795562998</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.09365968666708549</v>
+        <v>0.1001448870501946</v>
       </c>
       <c r="W100">
-        <v>0.2099364929667324</v>
+        <v>0.1949364929667324</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9793,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.374638746668342</v>
+        <v>0.4005795482007785</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9804,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2759918543304154</v>
+        <v>0.2606515146632221</v>
       </c>
       <c r="C101">
-        <v>-8686.892760469293</v>
+        <v>-8268.716376344521</v>
       </c>
       <c r="D101">
-        <v>7296.097239530708</v>
+        <v>7714.273623655481</v>
       </c>
       <c r="E101">
         <v>5712.890000000001</v>
@@ -9569,37 +9837,37 @@
         <v>1434.75</v>
       </c>
       <c r="M101">
-        <v>3868.767763643938</v>
+        <v>3618.233413643938</v>
       </c>
       <c r="N101">
-        <v>-2434.017763643938</v>
+        <v>-2183.483413643938</v>
       </c>
       <c r="O101">
-        <v>-608.5044409109846</v>
+        <v>-545.8708534109845</v>
       </c>
       <c r="P101">
-        <v>-1825.513322732954</v>
+        <v>-1637.612560232953</v>
       </c>
       <c r="Q101">
-        <v>-1505.013322732954</v>
+        <v>-1317.112560232953</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.793778144534993</v>
+        <v>6.744744177815669</v>
       </c>
       <c r="T101">
-        <v>104.3608321303567</v>
+        <v>103.63053591126</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V101">
-        <v>0.09271362922600379</v>
+        <v>0.09913332253453608</v>
       </c>
       <c r="W101">
-        <v>0.2101556291768337</v>
+        <v>0.1951556291768337</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9875,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3708545169040152</v>
+        <v>0.3965332901381443</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/spain/spain_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_drugs_biotechnology.xlsx
@@ -1546,7 +1546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1683,22 +1683,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1200793665788297</v>
+        <v>0.1199316504956333</v>
       </c>
       <c r="C2">
-        <v>16989.57004404403</v>
+        <v>16839.84481116528</v>
       </c>
       <c r="D2">
-        <v>16270.27004404403</v>
+        <v>16289.25481116528</v>
       </c>
       <c r="E2">
-        <v>-10989.4</v>
+        <v>-10820.69</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>168.71</v>
       </c>
       <c r="G2">
         <v>719.3</v>
@@ -1719,28 +1719,28 @@
         <v>1434.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.15695725902967</v>
       </c>
       <c r="N2">
-        <v>1434.75</v>
+        <v>1423.59304274097</v>
       </c>
       <c r="O2">
-        <v>358.6875</v>
+        <v>355.8982606852426</v>
       </c>
       <c r="P2">
-        <v>1076.0625</v>
+        <v>1067.694782055728</v>
       </c>
       <c r="Q2">
-        <v>1396.5625</v>
+        <v>1388.194782055728</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1200793665788297</v>
+        <v>0.1206420890529117</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.157783315011959</v>
       </c>
       <c r="U2">
         <v>0.0661309777667576</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.5968895183149</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1199316504956333</v>
+        <v>0.1197839344124369</v>
       </c>
       <c r="C3">
-        <v>16839.84481116528</v>
+        <v>16690.16393433302</v>
       </c>
       <c r="D3">
-        <v>16289.25481116528</v>
+        <v>16308.28393433302</v>
       </c>
       <c r="E3">
-        <v>-10820.69</v>
+        <v>-10651.98</v>
       </c>
       <c r="F3">
-        <v>168.71</v>
+        <v>337.42</v>
       </c>
       <c r="G3">
         <v>719.3</v>
@@ -1801,28 +1801,28 @@
         <v>1434.75</v>
       </c>
       <c r="M3">
-        <v>11.15695725902967</v>
+        <v>22.31391451805935</v>
       </c>
       <c r="N3">
-        <v>1423.59304274097</v>
+        <v>1412.436085481941</v>
       </c>
       <c r="O3">
-        <v>355.8982606852426</v>
+        <v>353.1090213704852</v>
       </c>
       <c r="P3">
-        <v>1067.694782055728</v>
+        <v>1059.327064111455</v>
       </c>
       <c r="Q3">
-        <v>1388.194782055728</v>
+        <v>1379.827064111455</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1206420890529117</v>
+        <v>0.1212162956591179</v>
       </c>
       <c r="T3">
-        <v>1.157783315011959</v>
+        <v>1.166666108590384</v>
       </c>
       <c r="U3">
         <v>0.0661309777667576</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.5968895183149</v>
+        <v>64.29844475915743</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1197839344124369</v>
+        <v>0.1196362183292405</v>
       </c>
       <c r="C4">
-        <v>16690.16393433302</v>
+        <v>16540.52756917939</v>
       </c>
       <c r="D4">
-        <v>16308.28393433302</v>
+        <v>16327.3575691794</v>
       </c>
       <c r="E4">
-        <v>-10651.98</v>
+        <v>-10483.27</v>
       </c>
       <c r="F4">
-        <v>337.42</v>
+        <v>506.13</v>
       </c>
       <c r="G4">
         <v>719.3</v>
@@ -1883,28 +1883,28 @@
         <v>1434.75</v>
       </c>
       <c r="M4">
-        <v>22.31391451805935</v>
+        <v>33.47087177708902</v>
       </c>
       <c r="N4">
-        <v>1412.436085481941</v>
+        <v>1401.279128222911</v>
       </c>
       <c r="O4">
-        <v>353.1090213704852</v>
+        <v>350.3197820557277</v>
       </c>
       <c r="P4">
-        <v>1059.327064111455</v>
+        <v>1050.959346167183</v>
       </c>
       <c r="Q4">
-        <v>1379.827064111455</v>
+        <v>1371.459346167183</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1212162956591179</v>
+        <v>0.1218023415767922</v>
       </c>
       <c r="T4">
-        <v>1.166666108590384</v>
+        <v>1.17573205255187</v>
       </c>
       <c r="U4">
         <v>0.0661309777667576</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.29844475915743</v>
+        <v>42.86562983943828</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1196362183292405</v>
+        <v>0.1194885022460441</v>
       </c>
       <c r="C5">
-        <v>16540.52756917939</v>
+        <v>16390.93587206547</v>
       </c>
       <c r="D5">
-        <v>16327.3575691794</v>
+        <v>16346.47587206548</v>
       </c>
       <c r="E5">
-        <v>-10483.27</v>
+        <v>-10314.56</v>
       </c>
       <c r="F5">
-        <v>506.13</v>
+        <v>674.84</v>
       </c>
       <c r="G5">
         <v>719.3</v>
@@ -1965,28 +1965,28 @@
         <v>1434.75</v>
       </c>
       <c r="M5">
-        <v>33.47087177708902</v>
+        <v>44.6278290361187</v>
       </c>
       <c r="N5">
-        <v>1401.279128222911</v>
+        <v>1390.122170963881</v>
       </c>
       <c r="O5">
-        <v>350.3197820557277</v>
+        <v>347.5305427409703</v>
       </c>
       <c r="P5">
-        <v>1050.959346167183</v>
+        <v>1042.591628222911</v>
       </c>
       <c r="Q5">
-        <v>1371.459346167183</v>
+        <v>1363.091628222911</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1218023415767922</v>
+        <v>0.1224005967844181</v>
       </c>
       <c r="T5">
-        <v>1.17573205255187</v>
+        <v>1.184986870345887</v>
       </c>
       <c r="U5">
         <v>0.0661309777667576</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.86562983943828</v>
+        <v>32.14922237957872</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1194885022460441</v>
+        <v>0.1193407861628478</v>
       </c>
       <c r="C6">
-        <v>16390.93587206547</v>
+        <v>16241.38900008556</v>
       </c>
       <c r="D6">
-        <v>16346.47587206548</v>
+        <v>16365.63900008556</v>
       </c>
       <c r="E6">
-        <v>-10314.56</v>
+        <v>-10145.85</v>
       </c>
       <c r="F6">
-        <v>674.84</v>
+        <v>843.5500000000001</v>
       </c>
       <c r="G6">
         <v>719.3</v>
@@ -2047,28 +2047,28 @@
         <v>1434.75</v>
       </c>
       <c r="M6">
-        <v>44.6278290361187</v>
+        <v>55.78478629514837</v>
       </c>
       <c r="N6">
-        <v>1390.122170963881</v>
+        <v>1378.965213704852</v>
       </c>
       <c r="O6">
-        <v>347.5305427409703</v>
+        <v>344.7413034262129</v>
       </c>
       <c r="P6">
-        <v>1042.591628222911</v>
+        <v>1034.223910278639</v>
       </c>
       <c r="Q6">
-        <v>1363.091628222911</v>
+        <v>1354.723910278639</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1224005967844181</v>
+        <v>0.1230114468385204</v>
       </c>
       <c r="T6">
-        <v>1.184986870345887</v>
+        <v>1.194436526409251</v>
       </c>
       <c r="U6">
         <v>0.0661309777667576</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.14922237957872</v>
+        <v>25.71937790366297</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1193407861628478</v>
+        <v>0.1191930700796514</v>
       </c>
       <c r="C7">
-        <v>16241.38900008556</v>
+        <v>16091.88711107146</v>
       </c>
       <c r="D7">
-        <v>16365.63900008556</v>
+        <v>16384.84711107146</v>
       </c>
       <c r="E7">
-        <v>-10145.85</v>
+        <v>-9977.139999999999</v>
       </c>
       <c r="F7">
-        <v>843.5500000000001</v>
+        <v>1012.26</v>
       </c>
       <c r="G7">
         <v>719.3</v>
@@ -2129,28 +2129,28 @@
         <v>1434.75</v>
       </c>
       <c r="M7">
-        <v>55.78478629514837</v>
+        <v>66.94174355417805</v>
       </c>
       <c r="N7">
-        <v>1378.965213704852</v>
+        <v>1367.808256445822</v>
       </c>
       <c r="O7">
-        <v>344.7413034262129</v>
+        <v>341.9520641114555</v>
       </c>
       <c r="P7">
-        <v>1034.223910278639</v>
+        <v>1025.856192334367</v>
       </c>
       <c r="Q7">
-        <v>1354.723910278639</v>
+        <v>1346.356192334367</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1230114468385204</v>
+        <v>0.1236352937022843</v>
       </c>
       <c r="T7">
-        <v>1.194436526409251</v>
+        <v>1.204087238984602</v>
       </c>
       <c r="U7">
         <v>0.0661309777667576</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.71937790366297</v>
+        <v>21.43281491971915</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1191930700796514</v>
+        <v>0.119045353996455</v>
       </c>
       <c r="C8">
-        <v>16091.88711107146</v>
+        <v>15942.43036359684</v>
       </c>
       <c r="D8">
-        <v>16384.84711107146</v>
+        <v>16404.10036359684</v>
       </c>
       <c r="E8">
-        <v>-9977.139999999999</v>
+        <v>-9808.43</v>
       </c>
       <c r="F8">
-        <v>1012.26</v>
+        <v>1180.97</v>
       </c>
       <c r="G8">
         <v>719.3</v>
@@ -2211,28 +2211,28 @@
         <v>1434.75</v>
       </c>
       <c r="M8">
-        <v>66.94174355417805</v>
+        <v>78.0987008132077</v>
       </c>
       <c r="N8">
-        <v>1367.808256445822</v>
+        <v>1356.651299186792</v>
       </c>
       <c r="O8">
-        <v>341.9520641114555</v>
+        <v>339.1628247966981</v>
       </c>
       <c r="P8">
-        <v>1025.856192334367</v>
+        <v>1017.488474390094</v>
       </c>
       <c r="Q8">
-        <v>1346.356192334367</v>
+        <v>1337.988474390094</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1236352937022843</v>
+        <v>0.1242725566276346</v>
       </c>
       <c r="T8">
-        <v>1.204087238984602</v>
+        <v>1.213945493765874</v>
       </c>
       <c r="U8">
         <v>0.0661309777667576</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.43281491971915</v>
+        <v>18.37098421690213</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.119045353996455</v>
+        <v>0.1188976379132586</v>
       </c>
       <c r="C9">
-        <v>15942.43036359684</v>
+        <v>15793.01891698157</v>
       </c>
       <c r="D9">
-        <v>16404.10036359684</v>
+        <v>16423.39891698157</v>
       </c>
       <c r="E9">
-        <v>-9808.43</v>
+        <v>-9639.719999999999</v>
       </c>
       <c r="F9">
-        <v>1180.97</v>
+        <v>1349.68</v>
       </c>
       <c r="G9">
         <v>719.3</v>
@@ -2293,28 +2293,28 @@
         <v>1434.75</v>
       </c>
       <c r="M9">
-        <v>78.09870081320771</v>
+        <v>89.2556580722374</v>
       </c>
       <c r="N9">
-        <v>1356.651299186792</v>
+        <v>1345.494341927763</v>
       </c>
       <c r="O9">
-        <v>339.1628247966981</v>
+        <v>336.3735854819407</v>
       </c>
       <c r="P9">
-        <v>1017.488474390094</v>
+        <v>1009.120756445822</v>
       </c>
       <c r="Q9">
-        <v>1337.988474390094</v>
+        <v>1329.620756445822</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1242725566276346</v>
+        <v>0.1249236730948403</v>
       </c>
       <c r="T9">
-        <v>1.213945493765874</v>
+        <v>1.224018058433696</v>
       </c>
       <c r="U9">
         <v>0.0661309777667576</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.37098421690213</v>
+        <v>16.07461118978936</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1188976379132586</v>
+        <v>0.1187499218300622</v>
       </c>
       <c r="C10">
-        <v>15793.01891698157</v>
+        <v>15643.65293129614</v>
       </c>
       <c r="D10">
-        <v>16423.39891698157</v>
+        <v>16442.74293129614</v>
       </c>
       <c r="E10">
-        <v>-9639.719999999999</v>
+        <v>-9471.01</v>
       </c>
       <c r="F10">
-        <v>1349.68</v>
+        <v>1518.39</v>
       </c>
       <c r="G10">
         <v>719.3</v>
@@ -2375,28 +2375,28 @@
         <v>1434.75</v>
       </c>
       <c r="M10">
-        <v>89.2556580722374</v>
+        <v>100.4126153312671</v>
       </c>
       <c r="N10">
-        <v>1345.494341927763</v>
+        <v>1334.337384668733</v>
       </c>
       <c r="O10">
-        <v>336.3735854819407</v>
+        <v>333.5843461671832</v>
       </c>
       <c r="P10">
-        <v>1009.120756445822</v>
+        <v>1000.75303850155</v>
       </c>
       <c r="Q10">
-        <v>1329.620756445822</v>
+        <v>1321.25303850155</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1249236730948403</v>
+        <v>0.1255890998140726</v>
       </c>
       <c r="T10">
-        <v>1.224018058433696</v>
+        <v>1.234311998149162</v>
       </c>
       <c r="U10">
         <v>0.0661309777667576</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.07461118978936</v>
+        <v>14.28854327981276</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1187499218300622</v>
+        <v>0.1186022057468658</v>
       </c>
       <c r="C11">
-        <v>15643.65293129614</v>
+        <v>15494.33256736606</v>
       </c>
       <c r="D11">
-        <v>16442.74293129614</v>
+        <v>16462.13256736606</v>
       </c>
       <c r="E11">
-        <v>-9471.01</v>
+        <v>-9302.299999999999</v>
       </c>
       <c r="F11">
-        <v>1518.39</v>
+        <v>1687.1</v>
       </c>
       <c r="G11">
         <v>719.3</v>
@@ -2457,28 +2457,28 @@
         <v>1434.75</v>
       </c>
       <c r="M11">
-        <v>100.4126153312671</v>
+        <v>111.5695725902967</v>
       </c>
       <c r="N11">
-        <v>1334.337384668733</v>
+        <v>1323.180427409703</v>
       </c>
       <c r="O11">
-        <v>333.5843461671832</v>
+        <v>330.7951068524258</v>
       </c>
       <c r="P11">
-        <v>1000.75303850155</v>
+        <v>992.3853205572775</v>
       </c>
       <c r="Q11">
-        <v>1321.25303850155</v>
+        <v>1312.885320557278</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1255890998140726</v>
+        <v>0.1262693137937322</v>
       </c>
       <c r="T11">
-        <v>1.234311998149162</v>
+        <v>1.244834692080527</v>
       </c>
       <c r="U11">
         <v>0.0661309777667576</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.28854327981276</v>
+        <v>12.85968895183149</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1186022057468658</v>
+        <v>0.1184544896636694</v>
       </c>
       <c r="C12">
-        <v>15494.33256736606</v>
+        <v>15345.05798677635</v>
       </c>
       <c r="D12">
-        <v>16462.13256736606</v>
+        <v>16481.56798677635</v>
       </c>
       <c r="E12">
-        <v>-9302.299999999999</v>
+        <v>-9133.59</v>
       </c>
       <c r="F12">
-        <v>1687.1</v>
+        <v>1855.81</v>
       </c>
       <c r="G12">
         <v>719.3</v>
@@ -2539,28 +2539,28 @@
         <v>1434.75</v>
       </c>
       <c r="M12">
-        <v>111.5695725902967</v>
+        <v>122.7265298493264</v>
       </c>
       <c r="N12">
-        <v>1323.180427409703</v>
+        <v>1312.023470150674</v>
       </c>
       <c r="O12">
-        <v>330.7951068524258</v>
+        <v>328.0058675376684</v>
       </c>
       <c r="P12">
-        <v>992.3853205572775</v>
+        <v>984.0176026130052</v>
       </c>
       <c r="Q12">
-        <v>1312.885320557278</v>
+        <v>1304.517602613005</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1262693137937322</v>
+        <v>0.1269648134807999</v>
       </c>
       <c r="T12">
-        <v>1.244834692080527</v>
+        <v>1.255593851044058</v>
       </c>
       <c r="U12">
         <v>0.0661309777667576</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.85968895183149</v>
+        <v>11.69062631984681</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1184544896636694</v>
+        <v>0.118306773580473</v>
       </c>
       <c r="C13">
-        <v>15345.05798677635</v>
+        <v>15195.829351876</v>
       </c>
       <c r="D13">
-        <v>16481.56798677635</v>
+        <v>16501.049351876</v>
       </c>
       <c r="E13">
-        <v>-9133.59</v>
+        <v>-8964.879999999999</v>
       </c>
       <c r="F13">
-        <v>1855.81</v>
+        <v>2024.52</v>
       </c>
       <c r="G13">
         <v>719.3</v>
@@ -2621,28 +2621,28 @@
         <v>1434.75</v>
       </c>
       <c r="M13">
-        <v>122.7265298493264</v>
+        <v>133.8834871083561</v>
       </c>
       <c r="N13">
-        <v>1312.023470150674</v>
+        <v>1300.866512891644</v>
       </c>
       <c r="O13">
-        <v>328.0058675376684</v>
+        <v>325.216628222911</v>
       </c>
       <c r="P13">
-        <v>984.0176026130052</v>
+        <v>975.649884668733</v>
       </c>
       <c r="Q13">
-        <v>1304.517602613005</v>
+        <v>1296.149884668733</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1269648134807999</v>
+        <v>0.1276761199789373</v>
       </c>
       <c r="T13">
-        <v>1.255593851044058</v>
+        <v>1.26659753634767</v>
       </c>
       <c r="U13">
         <v>0.0661309777667576</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.69062631984681</v>
+        <v>10.71640745985957</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.118306773580473</v>
+        <v>0.1181590574972766</v>
       </c>
       <c r="C14">
-        <v>15195.829351876</v>
+        <v>15046.64682578249</v>
       </c>
       <c r="D14">
-        <v>16501.049351876</v>
+        <v>16520.57682578249</v>
       </c>
       <c r="E14">
-        <v>-8964.879999999999</v>
+        <v>-8796.17</v>
       </c>
       <c r="F14">
-        <v>2024.52</v>
+        <v>2193.23</v>
       </c>
       <c r="G14">
         <v>719.3</v>
@@ -2703,28 +2703,28 @@
         <v>1434.75</v>
       </c>
       <c r="M14">
-        <v>133.8834871083561</v>
+        <v>145.0404443673858</v>
       </c>
       <c r="N14">
-        <v>1300.866512891644</v>
+        <v>1289.709555632614</v>
       </c>
       <c r="O14">
-        <v>325.216628222911</v>
+        <v>322.4273889081535</v>
       </c>
       <c r="P14">
-        <v>975.649884668733</v>
+        <v>967.2821667244607</v>
       </c>
       <c r="Q14">
-        <v>1296.149884668733</v>
+        <v>1287.782166724461</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1276761199789373</v>
+        <v>0.1284037783505951</v>
       </c>
       <c r="T14">
-        <v>1.26659753634767</v>
+        <v>1.277854179934122</v>
       </c>
       <c r="U14">
         <v>0.0661309777667576</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.71640745985957</v>
+        <v>9.892068424485759</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1181590574972766</v>
+        <v>0.1180113414140802</v>
       </c>
       <c r="C15">
-        <v>15046.64682578249</v>
+        <v>14897.51057238636</v>
       </c>
       <c r="D15">
-        <v>16520.57682578249</v>
+        <v>16540.15057238636</v>
       </c>
       <c r="E15">
-        <v>-8796.17</v>
+        <v>-8627.459999999999</v>
       </c>
       <c r="F15">
-        <v>2193.23</v>
+        <v>2361.94</v>
       </c>
       <c r="G15">
         <v>719.3</v>
@@ -2785,28 +2785,28 @@
         <v>1434.75</v>
       </c>
       <c r="M15">
-        <v>145.0404443673858</v>
+        <v>156.1974016264154</v>
       </c>
       <c r="N15">
-        <v>1289.709555632614</v>
+        <v>1278.552598373584</v>
       </c>
       <c r="O15">
-        <v>322.4273889081535</v>
+        <v>319.6381495933961</v>
       </c>
       <c r="P15">
-        <v>967.2821667244607</v>
+        <v>958.9144487801884</v>
       </c>
       <c r="Q15">
-        <v>1287.782166724461</v>
+        <v>1279.414448780188</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1284037783505951</v>
+        <v>0.1291483590099659</v>
       </c>
       <c r="T15">
-        <v>1.277854179934122</v>
+        <v>1.289372605929562</v>
       </c>
       <c r="U15">
         <v>0.0661309777667576</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.892068424485759</v>
+        <v>9.185492108451061</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1180113414140802</v>
+        <v>0.1180323753308838</v>
       </c>
       <c r="C16">
-        <v>14897.51057238636</v>
+        <v>14726.01055237468</v>
       </c>
       <c r="D16">
-        <v>16540.15057238636</v>
+        <v>16537.36055237468</v>
       </c>
       <c r="E16">
-        <v>-8627.459999999999</v>
+        <v>-8458.75</v>
       </c>
       <c r="F16">
-        <v>2361.94</v>
+        <v>2530.650000000001</v>
       </c>
       <c r="G16">
         <v>719.3</v>
@@ -2867,45 +2867,45 @@
         <v>1434.75</v>
       </c>
       <c r="M16">
-        <v>156.1974016264154</v>
+        <v>171.1503338854451</v>
       </c>
       <c r="N16">
-        <v>1278.552598373584</v>
+        <v>1263.599666114555</v>
       </c>
       <c r="O16">
-        <v>319.6381495933961</v>
+        <v>315.8999165286387</v>
       </c>
       <c r="P16">
-        <v>958.9144487801884</v>
+        <v>947.6997495859162</v>
       </c>
       <c r="Q16">
-        <v>1279.414448780188</v>
+        <v>1268.199749585916</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1291483590099659</v>
+        <v>0.129910459214263</v>
       </c>
       <c r="T16">
-        <v>1.289372605929562</v>
+        <v>1.30116205371313</v>
       </c>
       <c r="U16">
-        <v>0.0661309777667576</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.0495982333250682</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.185492108451061</v>
+        <v>8.38298101691295</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1180323753308838</v>
+        <v>0.1178959092476874</v>
       </c>
       <c r="C17">
-        <v>14726.01055237468</v>
+        <v>14575.41871601075</v>
       </c>
       <c r="D17">
-        <v>16537.36055237468</v>
+        <v>16555.47871601075</v>
       </c>
       <c r="E17">
-        <v>-8458.75</v>
+        <v>-8290.039999999999</v>
       </c>
       <c r="F17">
-        <v>2530.65</v>
+        <v>2699.36</v>
       </c>
       <c r="G17">
         <v>719.3</v>
@@ -2949,28 +2949,28 @@
         <v>1434.75</v>
       </c>
       <c r="M17">
-        <v>171.1503338854451</v>
+        <v>182.5603561444748</v>
       </c>
       <c r="N17">
-        <v>1263.599666114555</v>
+        <v>1252.189643855525</v>
       </c>
       <c r="O17">
-        <v>315.8999165286388</v>
+        <v>313.0474109638813</v>
       </c>
       <c r="P17">
-        <v>947.6997495859163</v>
+        <v>939.142232891644</v>
       </c>
       <c r="Q17">
-        <v>1268.199749585916</v>
+        <v>1259.642232891644</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.129910459214263</v>
+        <v>0.1306907046615197</v>
       </c>
       <c r="T17">
-        <v>1.30116205371313</v>
+        <v>1.313232202634403</v>
       </c>
       <c r="U17">
         <v>0.06763097776675758</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.382981016912954</v>
+        <v>7.859044703355894</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1178959092476874</v>
+        <v>0.117759443164491</v>
       </c>
       <c r="C18">
-        <v>14575.41871601075</v>
+        <v>14424.86662334037</v>
       </c>
       <c r="D18">
-        <v>16555.47871601075</v>
+        <v>16573.63662334037</v>
       </c>
       <c r="E18">
-        <v>-8290.039999999999</v>
+        <v>-8121.33</v>
       </c>
       <c r="F18">
-        <v>2699.36</v>
+        <v>2868.07</v>
       </c>
       <c r="G18">
         <v>719.3</v>
@@ -3031,28 +3031,28 @@
         <v>1434.75</v>
       </c>
       <c r="M18">
-        <v>182.5603561444748</v>
+        <v>193.9703784035044</v>
       </c>
       <c r="N18">
-        <v>1252.189643855525</v>
+        <v>1240.779621596496</v>
       </c>
       <c r="O18">
-        <v>313.0474109638813</v>
+        <v>310.1949053991239</v>
       </c>
       <c r="P18">
-        <v>939.142232891644</v>
+        <v>930.5847161973718</v>
       </c>
       <c r="Q18">
-        <v>1259.642232891644</v>
+        <v>1251.084716197372</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1306907046615197</v>
+        <v>0.1314897512038909</v>
       </c>
       <c r="T18">
-        <v>1.313232202634403</v>
+        <v>1.325593198517633</v>
       </c>
       <c r="U18">
         <v>0.06763097776675758</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.859044703355894</v>
+        <v>7.396747956099665</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.117759443164491</v>
+        <v>0.1176229770812946</v>
       </c>
       <c r="C19">
-        <v>14424.86662334037</v>
+        <v>14274.35440527875</v>
       </c>
       <c r="D19">
-        <v>16573.63662334037</v>
+        <v>16591.83440527875</v>
       </c>
       <c r="E19">
-        <v>-8121.33</v>
+        <v>-7952.619999999999</v>
       </c>
       <c r="F19">
-        <v>2868.07</v>
+        <v>3036.78</v>
       </c>
       <c r="G19">
         <v>719.3</v>
@@ -3113,28 +3113,28 @@
         <v>1434.75</v>
       </c>
       <c r="M19">
-        <v>193.9703784035044</v>
+        <v>205.3804006625341</v>
       </c>
       <c r="N19">
-        <v>1240.779621596496</v>
+        <v>1229.369599337466</v>
       </c>
       <c r="O19">
-        <v>310.1949053991239</v>
+        <v>307.3423998343665</v>
       </c>
       <c r="P19">
-        <v>930.5847161973718</v>
+        <v>922.0271995030994</v>
       </c>
       <c r="Q19">
-        <v>1251.084716197372</v>
+        <v>1242.527199503099</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1314897512038909</v>
+        <v>0.13230828668632</v>
       </c>
       <c r="T19">
-        <v>1.325593198517633</v>
+        <v>1.338255682105332</v>
       </c>
       <c r="U19">
         <v>0.06763097776675758</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.396747956099665</v>
+        <v>6.985817514094128</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1176229770812947</v>
+        <v>0.1177287609980983</v>
       </c>
       <c r="C20">
-        <v>14274.35440527874</v>
+        <v>14091.53461750456</v>
       </c>
       <c r="D20">
-        <v>16591.83440527874</v>
+        <v>16577.72461750456</v>
       </c>
       <c r="E20">
-        <v>-7952.62</v>
+        <v>-7783.91</v>
       </c>
       <c r="F20">
-        <v>3036.78</v>
+        <v>3205.49</v>
       </c>
       <c r="G20">
         <v>719.3</v>
@@ -3195,45 +3195,45 @@
         <v>1434.75</v>
       </c>
       <c r="M20">
-        <v>205.3804006625341</v>
+        <v>222.2397559215638</v>
       </c>
       <c r="N20">
-        <v>1229.369599337466</v>
+        <v>1212.510244078436</v>
       </c>
       <c r="O20">
-        <v>307.3423998343665</v>
+        <v>303.1275610196091</v>
       </c>
       <c r="P20">
-        <v>922.0271995030994</v>
+        <v>909.3826830588272</v>
       </c>
       <c r="Q20">
-        <v>1242.527199503099</v>
+        <v>1229.882683058827</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.13230828668632</v>
+        <v>0.1331470329214016</v>
       </c>
       <c r="T20">
-        <v>1.338255682105332</v>
+        <v>1.351230819608778</v>
       </c>
       <c r="U20">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05072323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.985817514094129</v>
+        <v>6.455865621569408</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1177287609980983</v>
+        <v>0.1176050449149019</v>
       </c>
       <c r="C21">
-        <v>14091.53461750456</v>
+        <v>13939.3286346085</v>
       </c>
       <c r="D21">
-        <v>16577.72461750456</v>
+        <v>16594.2286346085</v>
       </c>
       <c r="E21">
-        <v>-7783.91</v>
+        <v>-7615.199999999999</v>
       </c>
       <c r="F21">
-        <v>3205.49</v>
+        <v>3374.2</v>
       </c>
       <c r="G21">
         <v>719.3</v>
@@ -3277,28 +3277,28 @@
         <v>1434.75</v>
       </c>
       <c r="M21">
-        <v>222.2397559215638</v>
+        <v>233.9365851805935</v>
       </c>
       <c r="N21">
-        <v>1212.510244078436</v>
+        <v>1200.813414819406</v>
       </c>
       <c r="O21">
-        <v>303.1275610196091</v>
+        <v>300.2033537048516</v>
       </c>
       <c r="P21">
-        <v>909.3826830588272</v>
+        <v>900.6100611145548</v>
       </c>
       <c r="Q21">
-        <v>1229.882683058827</v>
+        <v>1221.110061114555</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1331470329214016</v>
+        <v>0.1340067478123603</v>
       </c>
       <c r="T21">
-        <v>1.351230819608778</v>
+        <v>1.364530335549809</v>
       </c>
       <c r="U21">
         <v>0.06933097776675759</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.455865621569408</v>
+        <v>6.133072340490937</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1176050449149019</v>
+        <v>0.1174813288317055</v>
       </c>
       <c r="C22">
-        <v>13939.3286346085</v>
+        <v>13787.15554573483</v>
       </c>
       <c r="D22">
-        <v>16594.2286346085</v>
+        <v>16610.76554573483</v>
       </c>
       <c r="E22">
-        <v>-7615.199999999999</v>
+        <v>-7446.49</v>
       </c>
       <c r="F22">
-        <v>3374.2</v>
+        <v>3542.91</v>
       </c>
       <c r="G22">
         <v>719.3</v>
@@ -3359,28 +3359,28 @@
         <v>1434.75</v>
       </c>
       <c r="M22">
-        <v>233.9365851805935</v>
+        <v>245.6334144396232</v>
       </c>
       <c r="N22">
-        <v>1200.813414819406</v>
+        <v>1189.116585560377</v>
       </c>
       <c r="O22">
-        <v>300.2033537048516</v>
+        <v>297.2791463900942</v>
       </c>
       <c r="P22">
-        <v>900.6100611145548</v>
+        <v>891.8374391702826</v>
       </c>
       <c r="Q22">
-        <v>1221.110061114555</v>
+        <v>1212.337439170283</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1340067478123603</v>
+        <v>0.1348882276372673</v>
       </c>
       <c r="T22">
-        <v>1.364530335549809</v>
+        <v>1.378166548096942</v>
       </c>
       <c r="U22">
         <v>0.06933097776675759</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.133072340490937</v>
+        <v>5.841021276658036</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1174813288317055</v>
+        <v>0.1173576127485091</v>
       </c>
       <c r="C23">
-        <v>13787.15554573483</v>
+        <v>13635.01544932285</v>
       </c>
       <c r="D23">
-        <v>16610.76554573483</v>
+        <v>16627.33544932285</v>
       </c>
       <c r="E23">
-        <v>-7446.49</v>
+        <v>-7277.78</v>
       </c>
       <c r="F23">
-        <v>3542.91</v>
+        <v>3711.62</v>
       </c>
       <c r="G23">
         <v>719.3</v>
@@ -3441,28 +3441,28 @@
         <v>1434.75</v>
       </c>
       <c r="M23">
-        <v>245.6334144396231</v>
+        <v>257.3302436986528</v>
       </c>
       <c r="N23">
-        <v>1189.116585560377</v>
+        <v>1177.419756301347</v>
       </c>
       <c r="O23">
-        <v>297.2791463900942</v>
+        <v>294.3549390753368</v>
       </c>
       <c r="P23">
-        <v>891.8374391702828</v>
+        <v>883.0648172260104</v>
       </c>
       <c r="Q23">
-        <v>1212.337439170283</v>
+        <v>1203.56481722601</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1348882276372673</v>
+        <v>0.1357923095089668</v>
       </c>
       <c r="T23">
-        <v>1.378166548096942</v>
+        <v>1.392152407119643</v>
       </c>
       <c r="U23">
         <v>0.06933097776675759</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.841021276658036</v>
+        <v>5.575520309537216</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1173576127485091</v>
+        <v>0.1173718966653127</v>
       </c>
       <c r="C24">
-        <v>13635.01544932285</v>
+        <v>13464.39064620704</v>
       </c>
       <c r="D24">
-        <v>16627.33544932285</v>
+        <v>16625.42064620704</v>
       </c>
       <c r="E24">
-        <v>-7277.78</v>
+        <v>-7109.07</v>
       </c>
       <c r="F24">
-        <v>3711.62</v>
+        <v>3880.33</v>
       </c>
       <c r="G24">
         <v>719.3</v>
@@ -3523,45 +3523,45 @@
         <v>1434.75</v>
       </c>
       <c r="M24">
-        <v>257.3302436986528</v>
+        <v>272.1313369576825</v>
       </c>
       <c r="N24">
-        <v>1177.419756301347</v>
+        <v>1162.618663042318</v>
       </c>
       <c r="O24">
-        <v>294.3549390753368</v>
+        <v>290.6546657605794</v>
       </c>
       <c r="P24">
-        <v>883.0648172260104</v>
+        <v>871.9639972817382</v>
       </c>
       <c r="Q24">
-        <v>1203.56481722601</v>
+        <v>1192.463997281738</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1357923095089668</v>
+        <v>0.1367198740266844</v>
       </c>
       <c r="T24">
-        <v>1.392152407119643</v>
+        <v>1.406501535207869</v>
       </c>
       <c r="U24">
-        <v>0.06933097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05199823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.575520309537216</v>
+        <v>5.272270426625322</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1173718966653127</v>
+        <v>0.1172541805821163</v>
       </c>
       <c r="C25">
-        <v>13464.39064620704</v>
+        <v>13311.47402181889</v>
       </c>
       <c r="D25">
-        <v>16625.42064620704</v>
+        <v>16641.21402181889</v>
       </c>
       <c r="E25">
-        <v>-7109.07</v>
+        <v>-6940.359999999999</v>
       </c>
       <c r="F25">
-        <v>3880.33</v>
+        <v>4049.04</v>
       </c>
       <c r="G25">
         <v>719.3</v>
@@ -3605,28 +3605,28 @@
         <v>1434.75</v>
       </c>
       <c r="M25">
-        <v>272.1313369576825</v>
+        <v>283.9631342167121</v>
       </c>
       <c r="N25">
-        <v>1162.618663042318</v>
+        <v>1150.786865783288</v>
       </c>
       <c r="O25">
-        <v>290.6546657605794</v>
+        <v>287.6967164458219</v>
       </c>
       <c r="P25">
-        <v>871.9639972817382</v>
+        <v>863.0901493374658</v>
       </c>
       <c r="Q25">
-        <v>1192.463997281738</v>
+        <v>1183.590149337466</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1367198740266844</v>
+        <v>0.1376718481369736</v>
       </c>
       <c r="T25">
-        <v>1.406501535207869</v>
+        <v>1.421228271929995</v>
       </c>
       <c r="U25">
         <v>0.07013097776675759</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.272270426625322</v>
+        <v>5.0525924921826</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1172541805821163</v>
+        <v>0.1171364644989199</v>
       </c>
       <c r="C26">
-        <v>13311.47402181889</v>
+        <v>13158.58743190522</v>
       </c>
       <c r="D26">
-        <v>16641.21402181889</v>
+        <v>16657.03743190522</v>
       </c>
       <c r="E26">
-        <v>-6940.36</v>
+        <v>-6771.65</v>
       </c>
       <c r="F26">
-        <v>4049.04</v>
+        <v>4217.75</v>
       </c>
       <c r="G26">
         <v>719.3</v>
@@ -3687,28 +3687,28 @@
         <v>1434.75</v>
       </c>
       <c r="M26">
-        <v>283.9631342167121</v>
+        <v>295.7949314757418</v>
       </c>
       <c r="N26">
-        <v>1150.786865783288</v>
+        <v>1138.955068524258</v>
       </c>
       <c r="O26">
-        <v>287.6967164458219</v>
+        <v>284.7387671310645</v>
       </c>
       <c r="P26">
-        <v>863.0901493374658</v>
+        <v>854.2163013931936</v>
       </c>
       <c r="Q26">
-        <v>1183.590149337466</v>
+        <v>1174.716301393194</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1376718481369736</v>
+        <v>0.1386492082235371</v>
       </c>
       <c r="T26">
-        <v>1.421228271929995</v>
+        <v>1.436347721631378</v>
       </c>
       <c r="U26">
         <v>0.07013097776675759</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.0525924921826</v>
+        <v>4.850488792495296</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1171364644989199</v>
+        <v>0.1170187484157235</v>
       </c>
       <c r="C27">
-        <v>13158.58743190522</v>
+        <v>13005.73096222303</v>
       </c>
       <c r="D27">
-        <v>16657.03743190522</v>
+        <v>16672.89096222303</v>
       </c>
       <c r="E27">
-        <v>-6771.65</v>
+        <v>-6602.94</v>
       </c>
       <c r="F27">
-        <v>4217.75</v>
+        <v>4386.46</v>
       </c>
       <c r="G27">
         <v>719.3</v>
@@ -3769,28 +3769,28 @@
         <v>1434.75</v>
       </c>
       <c r="M27">
-        <v>295.7949314757418</v>
+        <v>307.6267287347715</v>
       </c>
       <c r="N27">
-        <v>1138.955068524258</v>
+        <v>1127.123271265229</v>
       </c>
       <c r="O27">
-        <v>284.7387671310645</v>
+        <v>281.7808178163071</v>
       </c>
       <c r="P27">
-        <v>854.2163013931936</v>
+        <v>845.3424534489214</v>
       </c>
       <c r="Q27">
-        <v>1174.716301393194</v>
+        <v>1165.842453448921</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1386492082235371</v>
+        <v>0.1396529834475754</v>
       </c>
       <c r="T27">
-        <v>1.436347721631378</v>
+        <v>1.451875805108474</v>
       </c>
       <c r="U27">
         <v>0.07013097776675759</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.850488792495296</v>
+        <v>4.663931531245479</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1170187484157235</v>
+        <v>0.1169010323325271</v>
       </c>
       <c r="C28">
-        <v>13005.73096222303</v>
+        <v>12852.90469885608</v>
       </c>
       <c r="D28">
-        <v>16672.89096222303</v>
+        <v>16688.77469885608</v>
       </c>
       <c r="E28">
-        <v>-6602.94</v>
+        <v>-6434.23</v>
       </c>
       <c r="F28">
-        <v>4386.46</v>
+        <v>4555.17</v>
       </c>
       <c r="G28">
         <v>719.3</v>
@@ -3851,28 +3851,28 @@
         <v>1434.75</v>
       </c>
       <c r="M28">
-        <v>307.6267287347715</v>
+        <v>319.4585259938012</v>
       </c>
       <c r="N28">
-        <v>1127.123271265229</v>
+        <v>1115.291474006199</v>
       </c>
       <c r="O28">
-        <v>281.7808178163071</v>
+        <v>278.8228685015497</v>
       </c>
       <c r="P28">
-        <v>845.3424534489214</v>
+        <v>836.4686055046491</v>
       </c>
       <c r="Q28">
-        <v>1165.842453448921</v>
+        <v>1156.968605504649</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1396529834475754</v>
+        <v>0.1406842593626832</v>
       </c>
       <c r="T28">
-        <v>1.451875805108474</v>
+        <v>1.467829315530148</v>
       </c>
       <c r="U28">
         <v>0.07013097776675759</v>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.663931531245479</v>
+        <v>4.491193326384534</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1169010323325271</v>
+        <v>0.1167833162493307</v>
       </c>
       <c r="C29">
-        <v>12852.90469885608</v>
+        <v>12700.10872821652</v>
       </c>
       <c r="D29">
-        <v>16688.77469885608</v>
+        <v>16704.68872821652</v>
       </c>
       <c r="E29">
-        <v>-6434.23</v>
+        <v>-6265.52</v>
       </c>
       <c r="F29">
-        <v>4555.17</v>
+        <v>4723.88</v>
       </c>
       <c r="G29">
         <v>719.3</v>
@@ -3933,28 +3933,28 @@
         <v>1434.75</v>
       </c>
       <c r="M29">
-        <v>319.4585259938012</v>
+        <v>331.2903232528308</v>
       </c>
       <c r="N29">
-        <v>1115.291474006199</v>
+        <v>1103.459676747169</v>
       </c>
       <c r="O29">
-        <v>278.8228685015497</v>
+        <v>275.8649191867923</v>
       </c>
       <c r="P29">
-        <v>836.4686055046491</v>
+        <v>827.5947575603768</v>
       </c>
       <c r="Q29">
-        <v>1156.968605504649</v>
+        <v>1148.094757560377</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1406842593626832</v>
+        <v>0.1417441818309884</v>
       </c>
       <c r="T29">
-        <v>1.467829315530148</v>
+        <v>1.48422597901909</v>
       </c>
       <c r="U29">
         <v>0.07013097776675759</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.491193326384534</v>
+        <v>4.330793564727944</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1167833162493307</v>
+        <v>0.1168831001661343</v>
       </c>
       <c r="C30">
-        <v>12700.10872821652</v>
+        <v>12517.90698925039</v>
       </c>
       <c r="D30">
-        <v>16704.68872821652</v>
+        <v>16691.19698925039</v>
       </c>
       <c r="E30">
-        <v>-6265.52</v>
+        <v>-6096.809999999999</v>
       </c>
       <c r="F30">
-        <v>4723.88</v>
+        <v>4892.59</v>
       </c>
       <c r="G30">
         <v>719.3</v>
@@ -4015,45 +4015,45 @@
         <v>1434.75</v>
       </c>
       <c r="M30">
-        <v>331.2903232528308</v>
+        <v>348.0147105118605</v>
       </c>
       <c r="N30">
-        <v>1103.459676747169</v>
+        <v>1086.735289488139</v>
       </c>
       <c r="O30">
-        <v>275.8649191867923</v>
+        <v>271.6838223720349</v>
       </c>
       <c r="P30">
-        <v>827.5947575603768</v>
+        <v>815.0514671161045</v>
       </c>
       <c r="Q30">
-        <v>1148.094757560377</v>
+        <v>1135.551467116105</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1417441818309884</v>
+        <v>0.1428339612702318</v>
       </c>
       <c r="T30">
-        <v>1.48422597901909</v>
+        <v>1.501084520352792</v>
       </c>
       <c r="U30">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.05259823332506819</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.330793564727944</v>
+        <v>4.122670555764058</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1168831001661343</v>
+        <v>0.1167728840829379</v>
       </c>
       <c r="C31">
-        <v>12517.90698925039</v>
+        <v>12364.10051624733</v>
       </c>
       <c r="D31">
-        <v>16691.19698925039</v>
+        <v>16706.10051624733</v>
       </c>
       <c r="E31">
-        <v>-6096.81</v>
+        <v>-5928.099999999999</v>
       </c>
       <c r="F31">
-        <v>4892.589999999999</v>
+        <v>5061.3</v>
       </c>
       <c r="G31">
         <v>719.3</v>
@@ -4097,28 +4097,28 @@
         <v>1434.75</v>
       </c>
       <c r="M31">
-        <v>348.0147105118605</v>
+        <v>360.0152177708902</v>
       </c>
       <c r="N31">
-        <v>1086.73528948814</v>
+        <v>1074.73478222911</v>
       </c>
       <c r="O31">
-        <v>271.6838223720349</v>
+        <v>268.6836955572775</v>
       </c>
       <c r="P31">
-        <v>815.0514671161047</v>
+        <v>806.0510866718324</v>
       </c>
       <c r="Q31">
-        <v>1135.551467116105</v>
+        <v>1126.551086671832</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1428339612702318</v>
+        <v>0.1439548772648821</v>
       </c>
       <c r="T31">
-        <v>1.501084520352792</v>
+        <v>1.518424734296028</v>
       </c>
       <c r="U31">
         <v>0.07113097776675759</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.12267055576406</v>
+        <v>3.985248203905257</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1167728840829379</v>
+        <v>0.1166626679997415</v>
       </c>
       <c r="C32">
-        <v>12364.10051624733</v>
+        <v>12210.32068167173</v>
       </c>
       <c r="D32">
-        <v>16706.10051624733</v>
+        <v>16721.03068167173</v>
       </c>
       <c r="E32">
-        <v>-5928.099999999999</v>
+        <v>-5759.389999999999</v>
       </c>
       <c r="F32">
-        <v>5061.3</v>
+        <v>5230.01</v>
       </c>
       <c r="G32">
         <v>719.3</v>
@@ -4179,28 +4179,28 @@
         <v>1434.75</v>
       </c>
       <c r="M32">
-        <v>360.0152177708902</v>
+        <v>372.0157250299198</v>
       </c>
       <c r="N32">
-        <v>1074.73478222911</v>
+        <v>1062.73427497008</v>
       </c>
       <c r="O32">
-        <v>268.6836955572775</v>
+        <v>265.68356874252</v>
       </c>
       <c r="P32">
-        <v>806.0510866718324</v>
+        <v>797.0507062275601</v>
       </c>
       <c r="Q32">
-        <v>1126.551086671832</v>
+        <v>1117.55070622756</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1439548772648821</v>
+        <v>0.145108283578218</v>
       </c>
       <c r="T32">
-        <v>1.518424734296028</v>
+        <v>1.536267563136169</v>
       </c>
       <c r="U32">
         <v>0.07113097776675759</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.985248203905257</v>
+        <v>3.856691810230894</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1166626679997415</v>
+        <v>0.1165524519165451</v>
       </c>
       <c r="C33">
-        <v>12210.32068167173</v>
+        <v>12056.56755700741</v>
       </c>
       <c r="D33">
-        <v>16721.03068167173</v>
+        <v>16735.98755700741</v>
       </c>
       <c r="E33">
-        <v>-5759.389999999999</v>
+        <v>-5590.679999999999</v>
       </c>
       <c r="F33">
-        <v>5230.01</v>
+        <v>5398.72</v>
       </c>
       <c r="G33">
         <v>719.3</v>
@@ -4261,28 +4261,28 @@
         <v>1434.75</v>
       </c>
       <c r="M33">
-        <v>372.0157250299198</v>
+        <v>384.0162322889495</v>
       </c>
       <c r="N33">
-        <v>1062.73427497008</v>
+        <v>1050.73376771105</v>
       </c>
       <c r="O33">
-        <v>265.68356874252</v>
+        <v>262.6834419277626</v>
       </c>
       <c r="P33">
-        <v>797.0507062275601</v>
+        <v>788.0503257832878</v>
       </c>
       <c r="Q33">
-        <v>1117.55070622756</v>
+        <v>1108.550325783288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.145108283578218</v>
+        <v>0.146295613606652</v>
       </c>
       <c r="T33">
-        <v>1.536267563136169</v>
+        <v>1.554635181059844</v>
       </c>
       <c r="U33">
         <v>0.07113097776675759</v>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.856691810230894</v>
+        <v>3.736170191161178</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1165524519165451</v>
+        <v>0.1164422358333488</v>
       </c>
       <c r="C34">
-        <v>12056.56755700741</v>
+        <v>11902.84121399417</v>
       </c>
       <c r="D34">
-        <v>16735.98755700741</v>
+        <v>16750.97121399417</v>
       </c>
       <c r="E34">
-        <v>-5590.679999999999</v>
+        <v>-5421.969999999999</v>
       </c>
       <c r="F34">
-        <v>5398.72</v>
+        <v>5567.43</v>
       </c>
       <c r="G34">
         <v>719.3</v>
@@ -4343,28 +4343,28 @@
         <v>1434.75</v>
       </c>
       <c r="M34">
-        <v>384.0162322889495</v>
+        <v>396.0167395479792</v>
       </c>
       <c r="N34">
-        <v>1050.73376771105</v>
+        <v>1038.733260452021</v>
       </c>
       <c r="O34">
-        <v>262.6834419277626</v>
+        <v>259.6833151130052</v>
       </c>
       <c r="P34">
-        <v>788.0503257832878</v>
+        <v>779.0499453390155</v>
       </c>
       <c r="Q34">
-        <v>1108.550325783288</v>
+        <v>1099.549945339015</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.146295613606652</v>
+        <v>0.1475183863225019</v>
       </c>
       <c r="T34">
-        <v>1.554635181059844</v>
+        <v>1.573551086085718</v>
       </c>
       <c r="U34">
         <v>0.07113097776675759</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.736170191161178</v>
+        <v>3.622952912641142</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1164422358333488</v>
+        <v>0.1163320197501524</v>
       </c>
       <c r="C35">
-        <v>11902.84121399417</v>
+        <v>11749.14172462896</v>
       </c>
       <c r="D35">
-        <v>16750.97121399417</v>
+        <v>16765.98172462896</v>
       </c>
       <c r="E35">
-        <v>-5421.969999999999</v>
+        <v>-5253.259999999999</v>
       </c>
       <c r="F35">
-        <v>5567.43</v>
+        <v>5736.14</v>
       </c>
       <c r="G35">
         <v>719.3</v>
@@ -4425,28 +4425,28 @@
         <v>1434.75</v>
       </c>
       <c r="M35">
-        <v>396.0167395479792</v>
+        <v>408.0172468070089</v>
       </c>
       <c r="N35">
-        <v>1038.733260452021</v>
+        <v>1026.732753192991</v>
       </c>
       <c r="O35">
-        <v>259.6833151130052</v>
+        <v>256.6831882982478</v>
       </c>
       <c r="P35">
-        <v>779.0499453390155</v>
+        <v>770.0495648947433</v>
       </c>
       <c r="Q35">
-        <v>1099.549945339015</v>
+        <v>1090.549564894743</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1475183863225019</v>
+        <v>0.1487782127570139</v>
       </c>
       <c r="T35">
-        <v>1.573551086085718</v>
+        <v>1.593040200354801</v>
       </c>
       <c r="U35">
         <v>0.07113097776675759</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.622952912641142</v>
+        <v>3.51639547403405</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1163320197501524</v>
+        <v>0.116221803666956</v>
       </c>
       <c r="C36">
-        <v>11749.14172462896</v>
+        <v>11595.46916116702</v>
       </c>
       <c r="D36">
-        <v>16765.98172462896</v>
+        <v>16781.01916116702</v>
       </c>
       <c r="E36">
-        <v>-5253.259999999999</v>
+        <v>-5084.549999999999</v>
       </c>
       <c r="F36">
-        <v>5736.14</v>
+        <v>5904.85</v>
       </c>
       <c r="G36">
         <v>719.3</v>
@@ -4507,28 +4507,28 @@
         <v>1434.75</v>
       </c>
       <c r="M36">
-        <v>408.0172468070089</v>
+        <v>420.0177540660385</v>
       </c>
       <c r="N36">
-        <v>1026.732753192991</v>
+        <v>1014.732245933961</v>
       </c>
       <c r="O36">
-        <v>256.6831882982478</v>
+        <v>253.6830614834903</v>
       </c>
       <c r="P36">
-        <v>770.0495648947433</v>
+        <v>761.0491844504711</v>
       </c>
       <c r="Q36">
-        <v>1090.549564894743</v>
+        <v>1081.549184450471</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1487782127570139</v>
+        <v>0.1500768030818186</v>
       </c>
       <c r="T36">
-        <v>1.593040200354801</v>
+        <v>1.613128979678317</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.51639547403405</v>
+        <v>3.415927031918792</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.116221803666956</v>
+        <v>0.1161115875837596</v>
       </c>
       <c r="C37">
-        <v>11595.46916116702</v>
+        <v>11441.82359612305</v>
       </c>
       <c r="D37">
-        <v>16781.01916116702</v>
+        <v>16796.08359612305</v>
       </c>
       <c r="E37">
-        <v>-5084.549999999999</v>
+        <v>-4915.839999999999</v>
       </c>
       <c r="F37">
-        <v>5904.85</v>
+        <v>6073.56</v>
       </c>
       <c r="G37">
         <v>719.3</v>
@@ -4589,28 +4589,28 @@
         <v>1434.75</v>
       </c>
       <c r="M37">
-        <v>420.0177540660385</v>
+        <v>432.0182613250682</v>
       </c>
       <c r="N37">
-        <v>1014.732245933961</v>
+        <v>1002.731738674932</v>
       </c>
       <c r="O37">
-        <v>253.6830614834903</v>
+        <v>250.6829346687329</v>
       </c>
       <c r="P37">
-        <v>761.0491844504711</v>
+        <v>752.0488040061988</v>
       </c>
       <c r="Q37">
-        <v>1081.549184450471</v>
+        <v>1072.548804006199</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1500768030818186</v>
+        <v>0.1514159743542735</v>
       </c>
       <c r="T37">
-        <v>1.613128979678317</v>
+        <v>1.633845533355692</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.415927031918792</v>
+        <v>3.321040169921047</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1161115875837596</v>
+        <v>0.1160013715005632</v>
       </c>
       <c r="C38">
-        <v>11441.82359612305</v>
+        <v>11288.20510227237</v>
       </c>
       <c r="D38">
-        <v>16796.08359612305</v>
+        <v>16811.17510227237</v>
       </c>
       <c r="E38">
-        <v>-4915.84</v>
+        <v>-4747.13</v>
       </c>
       <c r="F38">
-        <v>6073.559999999999</v>
+        <v>6242.27</v>
       </c>
       <c r="G38">
         <v>719.3</v>
@@ -4671,28 +4671,28 @@
         <v>1434.75</v>
       </c>
       <c r="M38">
-        <v>432.0182613250682</v>
+        <v>444.0187685840979</v>
       </c>
       <c r="N38">
-        <v>1002.731738674932</v>
+        <v>990.7312314159021</v>
       </c>
       <c r="O38">
-        <v>250.682934668733</v>
+        <v>247.6828078539755</v>
       </c>
       <c r="P38">
-        <v>752.0488040061989</v>
+        <v>743.0484235619266</v>
       </c>
       <c r="Q38">
-        <v>1072.548804006199</v>
+        <v>1063.548423561926</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1514159743542735</v>
+        <v>0.1527976590004571</v>
       </c>
       <c r="T38">
-        <v>1.633845533355692</v>
+        <v>1.655219755403778</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.321040169921048</v>
+        <v>3.231282327490749</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1160013715005632</v>
+        <v>0.1158911554173668</v>
       </c>
       <c r="C39">
-        <v>11288.20510227237</v>
+        <v>11134.61375265209</v>
       </c>
       <c r="D39">
-        <v>16811.17510227237</v>
+        <v>16826.29375265209</v>
       </c>
       <c r="E39">
-        <v>-4747.13</v>
+        <v>-4578.419999999999</v>
       </c>
       <c r="F39">
-        <v>6242.27</v>
+        <v>6410.98</v>
       </c>
       <c r="G39">
         <v>719.3</v>
@@ -4753,28 +4753,28 @@
         <v>1434.75</v>
       </c>
       <c r="M39">
-        <v>444.0187685840979</v>
+        <v>456.0192758431276</v>
       </c>
       <c r="N39">
-        <v>990.7312314159021</v>
+        <v>978.7307241568724</v>
       </c>
       <c r="O39">
-        <v>247.6828078539755</v>
+        <v>244.6826810392181</v>
       </c>
       <c r="P39">
-        <v>743.0484235619266</v>
+        <v>734.0480431176543</v>
       </c>
       <c r="Q39">
-        <v>1063.548423561926</v>
+        <v>1054.548043117654</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1527976590004571</v>
+        <v>0.1542239141190982</v>
       </c>
       <c r="T39">
-        <v>1.655219755403778</v>
+        <v>1.677283468485673</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.231282327490749</v>
+        <v>3.146248582030466</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1158911554173668</v>
+        <v>0.1157809393341704</v>
       </c>
       <c r="C40">
-        <v>11134.61375265209</v>
+        <v>10981.04962056231</v>
       </c>
       <c r="D40">
-        <v>16826.29375265209</v>
+        <v>16841.43962056231</v>
       </c>
       <c r="E40">
-        <v>-4578.419999999999</v>
+        <v>-4409.709999999999</v>
       </c>
       <c r="F40">
-        <v>6410.98</v>
+        <v>6579.690000000001</v>
       </c>
       <c r="G40">
         <v>719.3</v>
@@ -4835,28 +4835,28 @@
         <v>1434.75</v>
       </c>
       <c r="M40">
-        <v>456.0192758431276</v>
+        <v>468.0197831021572</v>
       </c>
       <c r="N40">
-        <v>978.7307241568724</v>
+        <v>966.7302168978428</v>
       </c>
       <c r="O40">
-        <v>244.6826810392181</v>
+        <v>241.6825542244607</v>
       </c>
       <c r="P40">
-        <v>734.0480431176543</v>
+        <v>725.0476626733821</v>
       </c>
       <c r="Q40">
-        <v>1054.548043117654</v>
+        <v>1045.547662673382</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1542239141190982</v>
+        <v>0.1556969317006456</v>
       </c>
       <c r="T40">
-        <v>1.677283468485673</v>
+        <v>1.700070581996483</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.146248582030466</v>
+        <v>3.065575541465582</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1157809393341704</v>
+        <v>0.116420723250974</v>
       </c>
       <c r="C41">
-        <v>10981.04962056231</v>
+        <v>10724.79893671117</v>
       </c>
       <c r="D41">
-        <v>16841.43962056231</v>
+        <v>16753.89893671118</v>
       </c>
       <c r="E41">
-        <v>-4409.709999999999</v>
+        <v>-4240.999999999999</v>
       </c>
       <c r="F41">
-        <v>6579.690000000001</v>
+        <v>6748.400000000001</v>
       </c>
       <c r="G41">
         <v>719.3</v>
@@ -4917,45 +4917,45 @@
         <v>1434.75</v>
       </c>
       <c r="M41">
-        <v>468.0197831021572</v>
+        <v>496.891290361187</v>
       </c>
       <c r="N41">
-        <v>966.7302168978428</v>
+        <v>937.858709638813</v>
       </c>
       <c r="O41">
-        <v>241.6825542244607</v>
+        <v>234.4646774097033</v>
       </c>
       <c r="P41">
-        <v>725.0476626733821</v>
+        <v>703.3940322291098</v>
       </c>
       <c r="Q41">
-        <v>1045.547662673382</v>
+        <v>1023.89403222911</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1556969317006456</v>
+        <v>0.1572190498682446</v>
       </c>
       <c r="T41">
-        <v>1.700070581996483</v>
+        <v>1.723617265957653</v>
       </c>
       <c r="U41">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05334823332506819</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.065575541465582</v>
+        <v>2.887452502854477</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.116420723250974</v>
+        <v>0.1163292571677776</v>
       </c>
       <c r="C42">
-        <v>10724.79893671117</v>
+        <v>10568.54831089798</v>
       </c>
       <c r="D42">
-        <v>16753.89893671118</v>
+        <v>16766.35831089798</v>
       </c>
       <c r="E42">
-        <v>-4240.999999999999</v>
+        <v>-4072.289999999999</v>
       </c>
       <c r="F42">
-        <v>6748.400000000001</v>
+        <v>6917.110000000001</v>
       </c>
       <c r="G42">
         <v>719.3</v>
@@ -4999,28 +4999,28 @@
         <v>1434.75</v>
       </c>
       <c r="M42">
-        <v>496.891290361187</v>
+        <v>509.3135726202166</v>
       </c>
       <c r="N42">
-        <v>937.858709638813</v>
+        <v>925.4364273797834</v>
       </c>
       <c r="O42">
-        <v>234.4646774097033</v>
+        <v>231.3591068449458</v>
       </c>
       <c r="P42">
-        <v>703.3940322291098</v>
+        <v>694.0773205348376</v>
       </c>
       <c r="Q42">
-        <v>1023.89403222911</v>
+        <v>1014.577320534838</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1572190498682446</v>
+        <v>0.1587927652618638</v>
       </c>
       <c r="T42">
-        <v>1.723617265957653</v>
+        <v>1.747962142595473</v>
       </c>
       <c r="U42">
         <v>0.07363097776675759</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.887452502854477</v>
+        <v>2.817026832053148</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1163292571677776</v>
+        <v>0.1162377910845812</v>
       </c>
       <c r="C43">
-        <v>10568.54831089798</v>
+        <v>10412.31623020505</v>
       </c>
       <c r="D43">
-        <v>16766.35831089798</v>
+        <v>16778.83623020505</v>
       </c>
       <c r="E43">
-        <v>-4072.289999999999</v>
+        <v>-3903.579999999999</v>
       </c>
       <c r="F43">
-        <v>6917.110000000001</v>
+        <v>7085.820000000001</v>
       </c>
       <c r="G43">
         <v>719.3</v>
@@ -5081,28 +5081,28 @@
         <v>1434.75</v>
       </c>
       <c r="M43">
-        <v>509.3135726202166</v>
+        <v>521.7358548792463</v>
       </c>
       <c r="N43">
-        <v>925.4364273797834</v>
+        <v>913.0141451207537</v>
       </c>
       <c r="O43">
-        <v>231.3591068449458</v>
+        <v>228.2535362801884</v>
       </c>
       <c r="P43">
-        <v>694.0773205348376</v>
+        <v>684.7606088405653</v>
       </c>
       <c r="Q43">
-        <v>1014.577320534838</v>
+        <v>1005.260608840565</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1587927652618638</v>
+        <v>0.160420746703539</v>
       </c>
       <c r="T43">
-        <v>1.747962142595473</v>
+        <v>1.773146497738046</v>
       </c>
       <c r="U43">
         <v>0.07363097776675759</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.817026832053148</v>
+        <v>2.749954764623312</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1162377910845812</v>
+        <v>0.1161463250013848</v>
       </c>
       <c r="C44">
-        <v>10412.31623020505</v>
+        <v>10256.10273606838</v>
       </c>
       <c r="D44">
-        <v>16778.83623020505</v>
+        <v>16791.33273606838</v>
       </c>
       <c r="E44">
-        <v>-3903.58</v>
+        <v>-3734.87</v>
       </c>
       <c r="F44">
-        <v>7085.82</v>
+        <v>7254.53</v>
       </c>
       <c r="G44">
         <v>719.3</v>
@@ -5163,28 +5163,28 @@
         <v>1434.75</v>
       </c>
       <c r="M44">
-        <v>521.7358548792462</v>
+        <v>534.1581371382759</v>
       </c>
       <c r="N44">
-        <v>913.0141451207538</v>
+        <v>900.5918628617241</v>
       </c>
       <c r="O44">
-        <v>228.2535362801885</v>
+        <v>225.147965715431</v>
       </c>
       <c r="P44">
-        <v>684.7606088405654</v>
+        <v>675.443897146293</v>
       </c>
       <c r="Q44">
-        <v>1005.260608840565</v>
+        <v>995.943897146293</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.160420746703539</v>
+        <v>0.1621058503010623</v>
       </c>
       <c r="T44">
-        <v>1.773146497738046</v>
+        <v>1.799214514464568</v>
       </c>
       <c r="U44">
         <v>0.07363097776675759</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.749954764623312</v>
+        <v>2.686002328236723</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1161463250013848</v>
+        <v>0.1160548589181885</v>
       </c>
       <c r="C45">
-        <v>10256.10273606838</v>
+        <v>10099.90787004749</v>
       </c>
       <c r="D45">
-        <v>16791.33273606838</v>
+        <v>16803.84787004749</v>
       </c>
       <c r="E45">
-        <v>-3734.87</v>
+        <v>-3566.16</v>
       </c>
       <c r="F45">
-        <v>7254.53</v>
+        <v>7423.24</v>
       </c>
       <c r="G45">
         <v>719.3</v>
@@ -5245,28 +5245,28 @@
         <v>1434.75</v>
       </c>
       <c r="M45">
-        <v>534.1581371382759</v>
+        <v>546.5804193973056</v>
       </c>
       <c r="N45">
-        <v>900.5918628617241</v>
+        <v>888.1695806026944</v>
       </c>
       <c r="O45">
-        <v>225.147965715431</v>
+        <v>222.0423951506736</v>
       </c>
       <c r="P45">
-        <v>675.443897146293</v>
+        <v>666.1271854520207</v>
       </c>
       <c r="Q45">
-        <v>995.943897146293</v>
+        <v>986.6271854520207</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1621058503010623</v>
+        <v>0.1638511361699258</v>
       </c>
       <c r="T45">
-        <v>1.799214514464568</v>
+        <v>1.826213531788466</v>
       </c>
       <c r="U45">
         <v>0.07363097776675759</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.686002328236723</v>
+        <v>2.624956820776798</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1160548589181885</v>
+        <v>0.1159633928349921</v>
       </c>
       <c r="C46">
-        <v>10099.90787004749</v>
+        <v>9943.731673825896</v>
       </c>
       <c r="D46">
-        <v>16803.84787004749</v>
+        <v>16816.3816738259</v>
       </c>
       <c r="E46">
-        <v>-3566.16</v>
+        <v>-3397.45</v>
       </c>
       <c r="F46">
-        <v>7423.24</v>
+        <v>7591.95</v>
       </c>
       <c r="G46">
         <v>719.3</v>
@@ -5327,28 +5327,28 @@
         <v>1434.75</v>
       </c>
       <c r="M46">
-        <v>546.5804193973056</v>
+        <v>559.0027016563353</v>
       </c>
       <c r="N46">
-        <v>888.1695806026944</v>
+        <v>875.7472983436647</v>
       </c>
       <c r="O46">
-        <v>222.0423951506736</v>
+        <v>218.9368245859162</v>
       </c>
       <c r="P46">
-        <v>666.1271854520207</v>
+        <v>656.8104737577486</v>
       </c>
       <c r="Q46">
-        <v>986.6271854520207</v>
+        <v>977.3104737577486</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1638511361699258</v>
+        <v>0.1656598869794752</v>
       </c>
       <c r="T46">
-        <v>1.826213531788466</v>
+        <v>1.854194331560506</v>
       </c>
       <c r="U46">
         <v>0.07363097776675759</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.624956820776798</v>
+        <v>2.566624446981758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1159633928349921</v>
+        <v>0.1158719267517957</v>
       </c>
       <c r="C47">
-        <v>9943.731673825896</v>
+        <v>9787.574189211573</v>
       </c>
       <c r="D47">
-        <v>16816.3816738259</v>
+        <v>16828.93418921157</v>
       </c>
       <c r="E47">
-        <v>-3397.45</v>
+        <v>-3228.739999999999</v>
       </c>
       <c r="F47">
-        <v>7591.95</v>
+        <v>7760.660000000001</v>
       </c>
       <c r="G47">
         <v>719.3</v>
@@ -5409,28 +5409,28 @@
         <v>1434.75</v>
       </c>
       <c r="M47">
-        <v>559.0027016563353</v>
+        <v>571.424983915365</v>
       </c>
       <c r="N47">
-        <v>875.7472983436647</v>
+        <v>863.325016084635</v>
       </c>
       <c r="O47">
-        <v>218.9368245859162</v>
+        <v>215.8312540211587</v>
       </c>
       <c r="P47">
-        <v>656.8104737577486</v>
+        <v>647.4937620634762</v>
       </c>
       <c r="Q47">
-        <v>977.3104737577486</v>
+        <v>967.9937620634762</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1656598869794752</v>
+        <v>0.1675356285597487</v>
       </c>
       <c r="T47">
-        <v>1.854194331560506</v>
+        <v>1.883211457250028</v>
       </c>
       <c r="U47">
         <v>0.07363097776675759</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.566624446981758</v>
+        <v>2.510828263351719</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1158719267517957</v>
+        <v>0.1170142106685993</v>
       </c>
       <c r="C48">
-        <v>9787.574189211573</v>
+        <v>9463.432691909458</v>
       </c>
       <c r="D48">
-        <v>16828.93418921157</v>
+        <v>16673.50269190946</v>
       </c>
       <c r="E48">
-        <v>-3228.739999999999</v>
+        <v>-3060.029999999999</v>
       </c>
       <c r="F48">
-        <v>7760.660000000001</v>
+        <v>7929.370000000001</v>
       </c>
       <c r="G48">
         <v>719.3</v>
@@ -5491,45 +5491,45 @@
         <v>1434.75</v>
       </c>
       <c r="M48">
-        <v>571.424983915365</v>
+        <v>611.6000611743947</v>
       </c>
       <c r="N48">
-        <v>863.325016084635</v>
+        <v>823.1499388256053</v>
       </c>
       <c r="O48">
-        <v>215.8312540211587</v>
+        <v>205.7874847064013</v>
       </c>
       <c r="P48">
-        <v>647.4937620634762</v>
+        <v>617.362454119204</v>
       </c>
       <c r="Q48">
-        <v>967.9937620634762</v>
+        <v>937.862454119204</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1675356285597487</v>
+        <v>0.1694821528411646</v>
       </c>
       <c r="T48">
-        <v>1.883211457250028</v>
+        <v>1.913323568814628</v>
       </c>
       <c r="U48">
-        <v>0.07363097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05522323332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.510828263351719</v>
+        <v>2.345895775819565</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1170142106685993</v>
+        <v>0.1169489945854029</v>
       </c>
       <c r="C49">
-        <v>9463.432691909458</v>
+        <v>9303.519375665757</v>
       </c>
       <c r="D49">
-        <v>16673.50269190946</v>
+        <v>16682.29937566576</v>
       </c>
       <c r="E49">
-        <v>-3060.029999999999</v>
+        <v>-2891.319999999999</v>
       </c>
       <c r="F49">
-        <v>7929.370000000001</v>
+        <v>8098.080000000001</v>
       </c>
       <c r="G49">
         <v>719.3</v>
@@ -5573,28 +5573,28 @@
         <v>1434.75</v>
       </c>
       <c r="M49">
-        <v>611.6000611743947</v>
+        <v>624.6128284334244</v>
       </c>
       <c r="N49">
-        <v>823.1499388256053</v>
+        <v>810.1371715665756</v>
       </c>
       <c r="O49">
-        <v>205.7874847064013</v>
+        <v>202.5342928916439</v>
       </c>
       <c r="P49">
-        <v>617.362454119204</v>
+        <v>607.6028786749317</v>
       </c>
       <c r="Q49">
-        <v>937.862454119204</v>
+        <v>928.1028786749317</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1694821528411646</v>
+        <v>0.1715035434410964</v>
       </c>
       <c r="T49">
-        <v>1.913323568814628</v>
+        <v>1.944593838516327</v>
       </c>
       <c r="U49">
         <v>0.07713097776675759</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.345895775819565</v>
+        <v>2.297022947156657</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1169489945854029</v>
+        <v>0.1168837785022065</v>
       </c>
       <c r="C50">
-        <v>9303.519375665759</v>
+        <v>9143.615346311983</v>
       </c>
       <c r="D50">
-        <v>16682.29937566576</v>
+        <v>16691.10534631198</v>
       </c>
       <c r="E50">
-        <v>-2891.32</v>
+        <v>-2722.610000000001</v>
       </c>
       <c r="F50">
-        <v>8098.08</v>
+        <v>8266.789999999999</v>
       </c>
       <c r="G50">
         <v>719.3</v>
@@ -5655,28 +5655,28 @@
         <v>1434.75</v>
       </c>
       <c r="M50">
-        <v>624.6128284334243</v>
+        <v>637.6255956924539</v>
       </c>
       <c r="N50">
-        <v>810.1371715665757</v>
+        <v>797.1244043075461</v>
       </c>
       <c r="O50">
-        <v>202.5342928916439</v>
+        <v>199.2811010768865</v>
       </c>
       <c r="P50">
-        <v>607.6028786749318</v>
+        <v>597.8433032306596</v>
       </c>
       <c r="Q50">
-        <v>928.1028786749318</v>
+        <v>918.3433032306596</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1715035434410964</v>
+        <v>0.1736042042606335</v>
       </c>
       <c r="T50">
-        <v>1.944593838516327</v>
+        <v>1.977090393304367</v>
       </c>
       <c r="U50">
         <v>0.07713097776675759</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.297022947156658</v>
+        <v>2.25014492782693</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1168837785022065</v>
+        <v>0.1178685624190101</v>
       </c>
       <c r="C51">
-        <v>9143.615346311983</v>
+        <v>8842.914242623421</v>
       </c>
       <c r="D51">
-        <v>16691.10534631198</v>
+        <v>16559.11424262342</v>
       </c>
       <c r="E51">
-        <v>-2722.610000000001</v>
+        <v>-2553.9</v>
       </c>
       <c r="F51">
-        <v>8266.789999999999</v>
+        <v>8435.5</v>
       </c>
       <c r="G51">
         <v>719.3</v>
@@ -5737,45 +5737,45 @@
         <v>1434.75</v>
       </c>
       <c r="M51">
-        <v>637.6255956924539</v>
+        <v>674.2577629514836</v>
       </c>
       <c r="N51">
-        <v>797.1244043075461</v>
+        <v>760.4922370485164</v>
       </c>
       <c r="O51">
-        <v>199.2811010768865</v>
+        <v>190.1230592621291</v>
       </c>
       <c r="P51">
-        <v>597.8433032306596</v>
+        <v>570.3691777863872</v>
       </c>
       <c r="Q51">
-        <v>918.3433032306596</v>
+        <v>890.8691777863872</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1736042042606335</v>
+        <v>0.175788891512952</v>
       </c>
       <c r="T51">
-        <v>1.977090393304367</v>
+        <v>2.010886810283929</v>
       </c>
       <c r="U51">
-        <v>0.07713097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05784823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.25014492782693</v>
+        <v>2.127895411570126</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1178685624190101</v>
+        <v>0.1178243463358137</v>
       </c>
       <c r="C52">
-        <v>8842.914242623421</v>
+        <v>8680.085771221356</v>
       </c>
       <c r="D52">
-        <v>16559.11424262342</v>
+        <v>16564.99577122136</v>
       </c>
       <c r="E52">
-        <v>-2553.9</v>
+        <v>-2385.189999999999</v>
       </c>
       <c r="F52">
-        <v>8435.5</v>
+        <v>8604.210000000001</v>
       </c>
       <c r="G52">
         <v>719.3</v>
@@ -5819,28 +5819,28 @@
         <v>1434.75</v>
       </c>
       <c r="M52">
-        <v>674.2577629514836</v>
+        <v>687.7429182105134</v>
       </c>
       <c r="N52">
-        <v>760.4922370485164</v>
+        <v>747.0070817894866</v>
       </c>
       <c r="O52">
-        <v>190.1230592621291</v>
+        <v>186.7517704473717</v>
       </c>
       <c r="P52">
-        <v>570.3691777863872</v>
+        <v>560.255311342115</v>
       </c>
       <c r="Q52">
-        <v>890.8691777863872</v>
+        <v>880.755311342115</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.175788891512952</v>
+        <v>0.1780627496735284</v>
       </c>
       <c r="T52">
-        <v>2.010886810283929</v>
+        <v>2.046062672854494</v>
       </c>
       <c r="U52">
         <v>0.07993097776675759</v>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.127895411570126</v>
+        <v>2.086171972127575</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1178243463358137</v>
+        <v>0.1177801302526173</v>
       </c>
       <c r="C53">
-        <v>8680.085771221356</v>
+        <v>8517.26147935078</v>
       </c>
       <c r="D53">
-        <v>16564.99577122136</v>
+        <v>16570.88147935078</v>
       </c>
       <c r="E53">
-        <v>-2385.189999999999</v>
+        <v>-2216.48</v>
       </c>
       <c r="F53">
-        <v>8604.210000000001</v>
+        <v>8772.92</v>
       </c>
       <c r="G53">
         <v>719.3</v>
@@ -5901,28 +5901,28 @@
         <v>1434.75</v>
       </c>
       <c r="M53">
-        <v>687.7429182105134</v>
+        <v>701.228073469543</v>
       </c>
       <c r="N53">
-        <v>747.0070817894866</v>
+        <v>733.521926530457</v>
       </c>
       <c r="O53">
-        <v>186.7517704473717</v>
+        <v>183.3804816326142</v>
       </c>
       <c r="P53">
-        <v>560.255311342115</v>
+        <v>550.1414448978428</v>
       </c>
       <c r="Q53">
-        <v>880.755311342115</v>
+        <v>870.6414448978428</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1780627496735284</v>
+        <v>0.1804313519241288</v>
       </c>
       <c r="T53">
-        <v>2.046062672854494</v>
+        <v>2.082704196365498</v>
       </c>
       <c r="U53">
         <v>0.07993097776675759</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.086171972127575</v>
+        <v>2.046053280355891</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1177801302526173</v>
+        <v>0.1177359141694209</v>
       </c>
       <c r="C54">
-        <v>8517.26147935078</v>
+        <v>8354.441371468354</v>
       </c>
       <c r="D54">
-        <v>16570.88147935078</v>
+        <v>16576.77137146836</v>
       </c>
       <c r="E54">
-        <v>-2216.48</v>
+        <v>-2047.769999999999</v>
       </c>
       <c r="F54">
-        <v>8772.92</v>
+        <v>8941.630000000001</v>
       </c>
       <c r="G54">
         <v>719.3</v>
@@ -5983,28 +5983,28 @@
         <v>1434.75</v>
       </c>
       <c r="M54">
-        <v>701.228073469543</v>
+        <v>714.7132287285727</v>
       </c>
       <c r="N54">
-        <v>733.521926530457</v>
+        <v>720.0367712714273</v>
       </c>
       <c r="O54">
-        <v>183.3804816326142</v>
+        <v>180.0091928178568</v>
       </c>
       <c r="P54">
-        <v>550.1414448978428</v>
+        <v>540.0275784535704</v>
       </c>
       <c r="Q54">
-        <v>870.6414448978428</v>
+        <v>860.5275784535704</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1804313519241288</v>
+        <v>0.1829007457598612</v>
       </c>
       <c r="T54">
-        <v>2.082704196365498</v>
+        <v>2.120904933642928</v>
       </c>
       <c r="U54">
         <v>0.07993097776675759</v>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.046053280355891</v>
+        <v>2.007448501481251</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1177359141694209</v>
+        <v>0.1208506980862245</v>
       </c>
       <c r="C55">
-        <v>8354.441371468354</v>
+        <v>7780.811465256269</v>
       </c>
       <c r="D55">
-        <v>16576.77137146836</v>
+        <v>16171.85146525627</v>
       </c>
       <c r="E55">
-        <v>-2047.769999999999</v>
+        <v>-1879.059999999999</v>
       </c>
       <c r="F55">
-        <v>8941.630000000001</v>
+        <v>9110.34</v>
       </c>
       <c r="G55">
         <v>719.3</v>
@@ -6065,45 +6065,45 @@
         <v>1434.75</v>
       </c>
       <c r="M55">
-        <v>714.7132287285727</v>
+        <v>799.2590359876024</v>
       </c>
       <c r="N55">
-        <v>720.0367712714273</v>
+        <v>635.4909640123976</v>
       </c>
       <c r="O55">
-        <v>180.0091928178568</v>
+        <v>158.8727410030994</v>
       </c>
       <c r="P55">
-        <v>540.0275784535704</v>
+        <v>476.6182230092982</v>
       </c>
       <c r="Q55">
-        <v>860.5275784535704</v>
+        <v>797.1182230092982</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1829007457598612</v>
+        <v>0.1854775045449732</v>
       </c>
       <c r="T55">
-        <v>2.120904933642928</v>
+        <v>2.160766572541116</v>
       </c>
       <c r="U55">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05994823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.007448501481251</v>
+        <v>1.795100130744415</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1208506980862245</v>
+        <v>0.1208649820030281</v>
       </c>
       <c r="C56">
-        <v>7780.811465256269</v>
+        <v>7610.290126556805</v>
       </c>
       <c r="D56">
-        <v>16171.85146525627</v>
+        <v>16170.04012655681</v>
       </c>
       <c r="E56">
-        <v>-1879.059999999999</v>
+        <v>-1710.349999999999</v>
       </c>
       <c r="F56">
-        <v>9110.34</v>
+        <v>9279.050000000001</v>
       </c>
       <c r="G56">
         <v>719.3</v>
@@ -6147,28 +6147,28 @@
         <v>1434.75</v>
       </c>
       <c r="M56">
-        <v>799.2590359876024</v>
+        <v>814.0601292466321</v>
       </c>
       <c r="N56">
-        <v>635.4909640123976</v>
+        <v>620.6898707533679</v>
       </c>
       <c r="O56">
-        <v>158.8727410030994</v>
+        <v>155.172467688342</v>
       </c>
       <c r="P56">
-        <v>476.6182230092982</v>
+        <v>465.517403065026</v>
       </c>
       <c r="Q56">
-        <v>797.1182230092982</v>
+        <v>786.017403065026</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1854775045449732</v>
+        <v>0.188168785942757</v>
       </c>
       <c r="T56">
-        <v>2.160766572541116</v>
+        <v>2.20239983983478</v>
       </c>
       <c r="U56">
         <v>0.08773097776675759</v>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.795100130744415</v>
+        <v>1.762461946549062</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1208649820030281</v>
+        <v>0.1225172659198317</v>
       </c>
       <c r="C57">
-        <v>7610.290126556805</v>
+        <v>7234.757656323172</v>
       </c>
       <c r="D57">
-        <v>16170.04012655681</v>
+        <v>15963.21765632317</v>
       </c>
       <c r="E57">
-        <v>-1710.349999999999</v>
+        <v>-1541.639999999999</v>
       </c>
       <c r="F57">
-        <v>9279.050000000001</v>
+        <v>9447.76</v>
       </c>
       <c r="G57">
         <v>719.3</v>
@@ -6229,45 +6229,45 @@
         <v>1434.75</v>
       </c>
       <c r="M57">
-        <v>814.0601292466321</v>
+        <v>865.7074865056617</v>
       </c>
       <c r="N57">
-        <v>620.6898707533679</v>
+        <v>569.0425134943383</v>
       </c>
       <c r="O57">
-        <v>155.172467688342</v>
+        <v>142.2606283735846</v>
       </c>
       <c r="P57">
-        <v>465.517403065026</v>
+        <v>426.7818851207537</v>
       </c>
       <c r="Q57">
-        <v>786.017403065026</v>
+        <v>747.2818851207537</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.188168785942757</v>
+        <v>0.1909823983131672</v>
       </c>
       <c r="T57">
-        <v>2.20239983983478</v>
+        <v>2.245925528369063</v>
       </c>
       <c r="U57">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.06579823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.762461946549062</v>
+        <v>1.657314996536785</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1225172659198317</v>
+        <v>0.1225607998366354</v>
       </c>
       <c r="C58">
-        <v>7234.757656323172</v>
+        <v>7060.669866889773</v>
       </c>
       <c r="D58">
-        <v>15963.21765632317</v>
+        <v>15957.83986688978</v>
       </c>
       <c r="E58">
-        <v>-1541.639999999999</v>
+        <v>-1372.929999999998</v>
       </c>
       <c r="F58">
-        <v>9447.76</v>
+        <v>9616.470000000001</v>
       </c>
       <c r="G58">
         <v>719.3</v>
@@ -6311,28 +6311,28 @@
         <v>1434.75</v>
       </c>
       <c r="M58">
-        <v>865.7074865056617</v>
+        <v>881.1665487646915</v>
       </c>
       <c r="N58">
-        <v>569.0425134943383</v>
+        <v>553.5834512353085</v>
       </c>
       <c r="O58">
-        <v>142.2606283735846</v>
+        <v>138.3958628088271</v>
       </c>
       <c r="P58">
-        <v>426.7818851207537</v>
+        <v>415.1875884264814</v>
       </c>
       <c r="Q58">
-        <v>747.2818851207537</v>
+        <v>735.6875884264814</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1909823983131672</v>
+        <v>0.1939268763752244</v>
       </c>
       <c r="T58">
-        <v>2.245925528369063</v>
+        <v>2.29147566753285</v>
       </c>
       <c r="U58">
         <v>0.09163097776675759</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.657314996536785</v>
+        <v>1.628239294843158</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1225607998366354</v>
+        <v>0.122604333753439</v>
       </c>
       <c r="C59">
-        <v>7060.669866889773</v>
+        <v>6886.58569964335</v>
       </c>
       <c r="D59">
-        <v>15957.83986688978</v>
+        <v>15952.46569964335</v>
       </c>
       <c r="E59">
-        <v>-1372.929999999998</v>
+        <v>-1204.219999999999</v>
       </c>
       <c r="F59">
-        <v>9616.470000000001</v>
+        <v>9785.18</v>
       </c>
       <c r="G59">
         <v>719.3</v>
@@ -6393,28 +6393,28 @@
         <v>1434.75</v>
       </c>
       <c r="M59">
-        <v>881.1665487646915</v>
+        <v>896.625611023721</v>
       </c>
       <c r="N59">
-        <v>553.5834512353085</v>
+        <v>538.124388976279</v>
       </c>
       <c r="O59">
-        <v>138.3958628088271</v>
+        <v>134.5310972440697</v>
       </c>
       <c r="P59">
-        <v>415.1875884264814</v>
+        <v>403.5932917322092</v>
       </c>
       <c r="Q59">
-        <v>735.6875884264814</v>
+        <v>724.0932917322092</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1939268763752244</v>
+        <v>0.1970115676783319</v>
       </c>
       <c r="T59">
-        <v>2.29147566753285</v>
+        <v>2.33919486094253</v>
       </c>
       <c r="U59">
         <v>0.09163097776675759</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.628239294843158</v>
+        <v>1.600166203552758</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1226043337534389</v>
+        <v>0.1226478676702425</v>
       </c>
       <c r="C60">
-        <v>6886.585699643356</v>
+        <v>6712.505150925572</v>
       </c>
       <c r="D60">
-        <v>15952.46569964335</v>
+        <v>15947.09515092557</v>
       </c>
       <c r="E60">
-        <v>-1204.220000000001</v>
+        <v>-1035.51</v>
       </c>
       <c r="F60">
-        <v>9785.179999999998</v>
+        <v>9953.889999999999</v>
       </c>
       <c r="G60">
         <v>719.3</v>
@@ -6475,28 +6475,28 @@
         <v>1434.75</v>
       </c>
       <c r="M60">
-        <v>896.6256110237209</v>
+        <v>912.0846732827507</v>
       </c>
       <c r="N60">
-        <v>538.1243889762791</v>
+        <v>522.6653267172493</v>
       </c>
       <c r="O60">
-        <v>134.5310972440698</v>
+        <v>130.6663316793123</v>
       </c>
       <c r="P60">
-        <v>403.5932917322093</v>
+        <v>391.998995037937</v>
       </c>
       <c r="Q60">
-        <v>724.0932917322093</v>
+        <v>712.498995037937</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1970115676783319</v>
+        <v>0.2002467317279325</v>
       </c>
       <c r="T60">
-        <v>2.339194860942529</v>
+        <v>2.389241819884389</v>
       </c>
       <c r="U60">
         <v>0.09163097776675759</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.600166203552759</v>
+        <v>1.573044742475593</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1226478676702425</v>
+        <v>0.1226914015870462</v>
       </c>
       <c r="C61">
-        <v>6712.505150925572</v>
+        <v>6538.428217083021</v>
       </c>
       <c r="D61">
-        <v>15947.09515092557</v>
+        <v>15941.72821708302</v>
       </c>
       <c r="E61">
-        <v>-1035.51</v>
+        <v>-866.7999999999993</v>
       </c>
       <c r="F61">
-        <v>9953.889999999999</v>
+        <v>10122.6</v>
       </c>
       <c r="G61">
         <v>719.3</v>
@@ -6557,28 +6557,28 @@
         <v>1434.75</v>
       </c>
       <c r="M61">
-        <v>912.0846732827507</v>
+        <v>927.5437355417804</v>
       </c>
       <c r="N61">
-        <v>522.6653267172493</v>
+        <v>507.2062644582196</v>
       </c>
       <c r="O61">
-        <v>130.6663316793123</v>
+        <v>126.8015661145549</v>
       </c>
       <c r="P61">
-        <v>391.998995037937</v>
+        <v>380.4046983436647</v>
       </c>
       <c r="Q61">
-        <v>712.498995037937</v>
+        <v>700.9046983436647</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2002467317279325</v>
+        <v>0.2036436539800131</v>
       </c>
       <c r="T61">
-        <v>2.389241819884389</v>
+        <v>2.441791126773342</v>
       </c>
       <c r="U61">
         <v>0.09163097776675759</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.573044742475593</v>
+        <v>1.546827330101</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1226914015870462</v>
+        <v>0.1227349355038498</v>
       </c>
       <c r="C62">
-        <v>6538.428217083021</v>
+        <v>6364.35489446722</v>
       </c>
       <c r="D62">
-        <v>15941.72821708302</v>
+        <v>15936.36489446722</v>
       </c>
       <c r="E62">
-        <v>-866.7999999999993</v>
+        <v>-698.0900000000001</v>
       </c>
       <c r="F62">
-        <v>10122.6</v>
+        <v>10291.31</v>
       </c>
       <c r="G62">
         <v>719.3</v>
@@ -6639,28 +6639,28 @@
         <v>1434.75</v>
       </c>
       <c r="M62">
-        <v>927.5437355417804</v>
+        <v>943.00279780081</v>
       </c>
       <c r="N62">
-        <v>507.2062644582196</v>
+        <v>491.74720219919</v>
       </c>
       <c r="O62">
-        <v>126.8015661145549</v>
+        <v>122.9368005497975</v>
       </c>
       <c r="P62">
-        <v>380.4046983436647</v>
+        <v>368.8104016493925</v>
       </c>
       <c r="Q62">
-        <v>700.9046983436647</v>
+        <v>689.3104016493926</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2036436539800131</v>
+        <v>0.2072147773732261</v>
       </c>
       <c r="T62">
-        <v>2.441791126773342</v>
+        <v>2.497035269913011</v>
       </c>
       <c r="U62">
         <v>0.09163097776675759</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.546827330101</v>
+        <v>1.521469505017377</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1227349355038498</v>
+        <v>0.1293814694206534</v>
       </c>
       <c r="C63">
-        <v>6364.35489446722</v>
+        <v>5417.067453466199</v>
       </c>
       <c r="D63">
-        <v>15936.36489446722</v>
+        <v>15157.7874534662</v>
       </c>
       <c r="E63">
-        <v>-698.0900000000001</v>
+        <v>-529.3799999999992</v>
       </c>
       <c r="F63">
-        <v>10291.31</v>
+        <v>10460.02</v>
       </c>
       <c r="G63">
         <v>719.3</v>
@@ -6721,45 +6721,45 @@
         <v>1434.75</v>
       </c>
       <c r="M63">
-        <v>943.00279780081</v>
+        <v>1106.99414405984</v>
       </c>
       <c r="N63">
-        <v>491.74720219919</v>
+        <v>327.7558559401602</v>
       </c>
       <c r="O63">
-        <v>122.9368005497975</v>
+        <v>81.93896398504006</v>
       </c>
       <c r="P63">
-        <v>368.8104016493925</v>
+        <v>245.8168919551202</v>
       </c>
       <c r="Q63">
-        <v>689.3104016493926</v>
+        <v>566.3168919551201</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2072147773732261</v>
+        <v>0.2109738546292398</v>
       </c>
       <c r="T63">
-        <v>2.497035269913011</v>
+        <v>2.555186999533714</v>
       </c>
       <c r="U63">
-        <v>0.09163097776675759</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.06872323332506819</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.521469505017377</v>
+        <v>1.296077316848429</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1293814694206534</v>
+        <v>0.129531503337457</v>
       </c>
       <c r="C64">
-        <v>5417.067453466199</v>
+        <v>5231.659474925171</v>
       </c>
       <c r="D64">
-        <v>15157.7874534662</v>
+        <v>15141.08947492517</v>
       </c>
       <c r="E64">
-        <v>-529.3799999999992</v>
+        <v>-360.6700000000001</v>
       </c>
       <c r="F64">
-        <v>10460.02</v>
+        <v>10628.73</v>
       </c>
       <c r="G64">
         <v>719.3</v>
@@ -6803,28 +6803,28 @@
         <v>1434.75</v>
       </c>
       <c r="M64">
-        <v>1106.99414405984</v>
+        <v>1124.84888831887</v>
       </c>
       <c r="N64">
-        <v>327.7558559401602</v>
+        <v>309.9011116811305</v>
       </c>
       <c r="O64">
-        <v>81.93896398504006</v>
+        <v>77.47527792028262</v>
       </c>
       <c r="P64">
-        <v>245.8168919551202</v>
+        <v>232.4258337608479</v>
       </c>
       <c r="Q64">
-        <v>566.3168919551201</v>
+        <v>552.9258337608478</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2109738546292398</v>
+        <v>0.2149361252504433</v>
       </c>
       <c r="T64">
-        <v>2.555186999533714</v>
+        <v>2.616482065890672</v>
       </c>
       <c r="U64">
         <v>0.1058309777667576</v>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.296077316848429</v>
+        <v>1.275504661025438</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.129531503337457</v>
+        <v>0.1296815372542606</v>
       </c>
       <c r="C65">
-        <v>5231.659474925171</v>
+        <v>5046.288245239793</v>
       </c>
       <c r="D65">
-        <v>15141.08947492517</v>
+        <v>15124.42824523979</v>
       </c>
       <c r="E65">
-        <v>-360.6700000000001</v>
+        <v>-191.9599999999991</v>
       </c>
       <c r="F65">
-        <v>10628.73</v>
+        <v>10797.44</v>
       </c>
       <c r="G65">
         <v>719.3</v>
@@ -6885,28 +6885,28 @@
         <v>1434.75</v>
       </c>
       <c r="M65">
-        <v>1124.84888831887</v>
+        <v>1142.703632577899</v>
       </c>
       <c r="N65">
-        <v>309.9011116811305</v>
+        <v>292.0463674221007</v>
       </c>
       <c r="O65">
-        <v>77.47527792028262</v>
+        <v>73.01159185552518</v>
       </c>
       <c r="P65">
-        <v>232.4258337608479</v>
+        <v>219.0347755665755</v>
       </c>
       <c r="Q65">
-        <v>552.9258337608478</v>
+        <v>539.5347755665755</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2149361252504433</v>
+        <v>0.2191185220172693</v>
       </c>
       <c r="T65">
-        <v>2.616482065890672</v>
+        <v>2.681182413711905</v>
       </c>
       <c r="U65">
         <v>0.1058309777667576</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.275504661025438</v>
+        <v>1.255574900696915</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1296815372542606</v>
+        <v>0.1446814395595901</v>
       </c>
       <c r="C66">
-        <v>5046.288245239793</v>
+        <v>3378.586214760779</v>
       </c>
       <c r="D66">
-        <v>15124.42824523979</v>
+        <v>13625.43621476078</v>
       </c>
       <c r="E66">
-        <v>-191.9599999999991</v>
+        <v>-23.25</v>
       </c>
       <c r="F66">
-        <v>10797.44</v>
+        <v>10966.15</v>
       </c>
       <c r="G66">
         <v>719.3</v>
@@ -6967,45 +6967,45 @@
         <v>1434.75</v>
       </c>
       <c r="M66">
-        <v>1142.703632577899</v>
+        <v>1474.190266836929</v>
       </c>
       <c r="N66">
-        <v>292.0463674221007</v>
+        <v>-39.44026683692891</v>
       </c>
       <c r="O66">
-        <v>73.01159185552518</v>
+        <v>-9.860066709232228</v>
       </c>
       <c r="P66">
-        <v>219.0347755665755</v>
+        <v>-29.58020012769668</v>
       </c>
       <c r="Q66">
-        <v>539.5347755665755</v>
+        <v>290.9197998723033</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2191185220172693</v>
+        <v>0.2244625689006351</v>
       </c>
       <c r="T66">
-        <v>2.681182413711905</v>
+        <v>2.763853119387001</v>
       </c>
       <c r="U66">
-        <v>0.1058309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V66">
-        <v>0.25</v>
+        <v>0.2433115372343433</v>
       </c>
       <c r="W66">
-        <v>0.0793732333250682</v>
+        <v>0.101722369914412</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.255574900696915</v>
+        <v>0.9732461489373734</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1446814395595901</v>
+        <v>0.1455677493372576</v>
       </c>
       <c r="C67">
-        <v>3378.586214760779</v>
+        <v>3130.547215323573</v>
       </c>
       <c r="D67">
-        <v>13625.43621476078</v>
+        <v>13546.10721532357</v>
       </c>
       <c r="E67">
-        <v>-23.25</v>
+        <v>145.4600000000009</v>
       </c>
       <c r="F67">
-        <v>10966.15</v>
+        <v>11134.86</v>
       </c>
       <c r="G67">
         <v>719.3</v>
@@ -7049,37 +7049,37 @@
         <v>1434.75</v>
       </c>
       <c r="M67">
-        <v>1474.190266836929</v>
+        <v>1496.870117095959</v>
       </c>
       <c r="N67">
-        <v>-39.44026683692891</v>
+        <v>-62.12011709595868</v>
       </c>
       <c r="O67">
-        <v>-9.860066709232228</v>
+        <v>-15.53002927398967</v>
       </c>
       <c r="P67">
-        <v>-29.58020012769668</v>
+        <v>-46.59008782196901</v>
       </c>
       <c r="Q67">
-        <v>290.9197998723033</v>
+        <v>273.909912178031</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2244625689006351</v>
+        <v>0.229717350338889</v>
       </c>
       <c r="T67">
-        <v>2.763853119387001</v>
+        <v>2.845142917016029</v>
       </c>
       <c r="U67">
         <v>0.1344309777667576</v>
       </c>
       <c r="V67">
-        <v>0.2433115372343433</v>
+        <v>0.2396249987913988</v>
       </c>
       <c r="W67">
-        <v>0.101722369914412</v>
+        <v>0.1022179548818718</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9732461489373734</v>
+        <v>0.958499995165595</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1455677493372576</v>
+        <v>0.1464540591149252</v>
       </c>
       <c r="C68">
-        <v>3130.547215323573</v>
+        <v>2883.426595742327</v>
       </c>
       <c r="D68">
-        <v>13546.10721532357</v>
+        <v>13467.69659574233</v>
       </c>
       <c r="E68">
-        <v>145.4600000000009</v>
+        <v>314.1700000000019</v>
       </c>
       <c r="F68">
-        <v>11134.86</v>
+        <v>11303.57</v>
       </c>
       <c r="G68">
         <v>719.3</v>
@@ -7131,37 +7131,37 @@
         <v>1434.75</v>
       </c>
       <c r="M68">
-        <v>1496.870117095959</v>
+        <v>1519.549967354988</v>
       </c>
       <c r="N68">
-        <v>-62.12011709595868</v>
+        <v>-84.79996735498844</v>
       </c>
       <c r="O68">
-        <v>-15.53002927398967</v>
+        <v>-21.19999183874711</v>
       </c>
       <c r="P68">
-        <v>-46.59008782196901</v>
+        <v>-63.59997551624133</v>
       </c>
       <c r="Q68">
-        <v>273.909912178031</v>
+        <v>256.9000244837587</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.229717350338889</v>
+        <v>0.2352906033794615</v>
       </c>
       <c r="T68">
-        <v>2.845142917016029</v>
+        <v>2.931359369046819</v>
       </c>
       <c r="U68">
         <v>0.1344309777667576</v>
       </c>
       <c r="V68">
-        <v>0.2396249987913988</v>
+        <v>0.2360485062721241</v>
       </c>
       <c r="W68">
-        <v>0.1022179548818718</v>
+        <v>0.1026987462682133</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.958499995165595</v>
+        <v>0.9441940250884965</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1464540591149252</v>
+        <v>0.1473403688925928</v>
       </c>
       <c r="C69">
-        <v>2883.426595742327</v>
+        <v>2637.208499881577</v>
       </c>
       <c r="D69">
-        <v>13467.69659574233</v>
+        <v>13390.18849988158</v>
       </c>
       <c r="E69">
-        <v>314.1700000000019</v>
+        <v>482.880000000001</v>
       </c>
       <c r="F69">
-        <v>11303.57</v>
+        <v>11472.28</v>
       </c>
       <c r="G69">
         <v>719.3</v>
@@ -7213,37 +7213,37 @@
         <v>1434.75</v>
       </c>
       <c r="M69">
-        <v>1519.549967354988</v>
+        <v>1542.229817614018</v>
       </c>
       <c r="N69">
-        <v>-84.79996735498844</v>
+        <v>-107.479817614018</v>
       </c>
       <c r="O69">
-        <v>-21.19999183874711</v>
+        <v>-26.86995440350449</v>
       </c>
       <c r="P69">
-        <v>-63.59997551624133</v>
+        <v>-80.60986321051348</v>
       </c>
       <c r="Q69">
-        <v>256.9000244837587</v>
+        <v>239.8901367894865</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2352906033794615</v>
+        <v>0.2412121847350696</v>
       </c>
       <c r="T69">
-        <v>2.931359369046819</v>
+        <v>3.022964349329532</v>
       </c>
       <c r="U69">
         <v>0.1344309777667576</v>
       </c>
       <c r="V69">
-        <v>0.2360485062721241</v>
+        <v>0.2325772047092988</v>
       </c>
       <c r="W69">
-        <v>0.1026987462682133</v>
+        <v>0.1031653967314272</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9441940250884965</v>
+        <v>0.9303088188371952</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1473403688925928</v>
+        <v>0.1482266786702604</v>
       </c>
       <c r="C70">
-        <v>2637.208499881577</v>
+        <v>2391.877434532464</v>
       </c>
       <c r="D70">
-        <v>13390.18849988158</v>
+        <v>13313.56743453247</v>
       </c>
       <c r="E70">
-        <v>482.880000000001</v>
+        <v>651.590000000002</v>
       </c>
       <c r="F70">
-        <v>11472.28</v>
+        <v>11640.99</v>
       </c>
       <c r="G70">
         <v>719.3</v>
@@ -7295,37 +7295,37 @@
         <v>1434.75</v>
       </c>
       <c r="M70">
-        <v>1542.229817614018</v>
+        <v>1564.909667873048</v>
       </c>
       <c r="N70">
-        <v>-107.479817614018</v>
+        <v>-130.159667873048</v>
       </c>
       <c r="O70">
-        <v>-26.86995440350449</v>
+        <v>-32.53991696826199</v>
       </c>
       <c r="P70">
-        <v>-80.60986321051348</v>
+        <v>-97.61975090478597</v>
       </c>
       <c r="Q70">
-        <v>239.8901367894865</v>
+        <v>222.880249095214</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2412121847350696</v>
+        <v>0.2475158035974913</v>
       </c>
       <c r="T70">
-        <v>3.022964349329532</v>
+        <v>3.120479328340163</v>
       </c>
       <c r="U70">
         <v>0.1344309777667576</v>
       </c>
       <c r="V70">
-        <v>0.2325772047092988</v>
+        <v>0.229206520583077</v>
       </c>
       <c r="W70">
-        <v>0.1031653967314272</v>
+        <v>0.1036185210942581</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9303088188371952</v>
+        <v>0.9168260823323081</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1482266786702604</v>
+        <v>0.1491129884479279</v>
       </c>
       <c r="C71">
-        <v>2391.877434532464</v>
+        <v>2147.418259088208</v>
       </c>
       <c r="D71">
-        <v>13313.56743453247</v>
+        <v>13237.81825908821</v>
       </c>
       <c r="E71">
-        <v>651.590000000002</v>
+        <v>820.3000000000011</v>
       </c>
       <c r="F71">
-        <v>11640.99</v>
+        <v>11809.7</v>
       </c>
       <c r="G71">
         <v>719.3</v>
@@ -7377,37 +7377,37 @@
         <v>1434.75</v>
       </c>
       <c r="M71">
-        <v>1564.909667873048</v>
+        <v>1587.589518132078</v>
       </c>
       <c r="N71">
-        <v>-130.159667873048</v>
+        <v>-152.8395181320775</v>
       </c>
       <c r="O71">
-        <v>-32.53991696826199</v>
+        <v>-38.20987953301938</v>
       </c>
       <c r="P71">
-        <v>-97.61975090478597</v>
+        <v>-114.6296385990581</v>
       </c>
       <c r="Q71">
-        <v>222.880249095214</v>
+        <v>205.8703614009419</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2475158035974913</v>
+        <v>0.2542396637174076</v>
       </c>
       <c r="T71">
-        <v>3.120479328340163</v>
+        <v>3.2244953059515</v>
       </c>
       <c r="U71">
         <v>0.1344309777667576</v>
       </c>
       <c r="V71">
-        <v>0.229206520583077</v>
+        <v>0.2259321417176045</v>
       </c>
       <c r="W71">
-        <v>0.1036185210942581</v>
+        <v>0.1040586990467224</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9168260823323081</v>
+        <v>0.903728566870418</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1491129884479279</v>
+        <v>0.1499992982255955</v>
       </c>
       <c r="C72">
-        <v>2147.418259088208</v>
+        <v>1903.816175569937</v>
       </c>
       <c r="D72">
-        <v>13237.81825908821</v>
+        <v>13162.92617556994</v>
       </c>
       <c r="E72">
-        <v>820.3000000000011</v>
+        <v>989.010000000002</v>
       </c>
       <c r="F72">
-        <v>11809.7</v>
+        <v>11978.41</v>
       </c>
       <c r="G72">
         <v>719.3</v>
@@ -7459,37 +7459,37 @@
         <v>1434.75</v>
       </c>
       <c r="M72">
-        <v>1587.589518132078</v>
+        <v>1610.269368391107</v>
       </c>
       <c r="N72">
-        <v>-152.8395181320775</v>
+        <v>-175.5193683911073</v>
       </c>
       <c r="O72">
-        <v>-38.20987953301938</v>
+        <v>-43.87984209777682</v>
       </c>
       <c r="P72">
-        <v>-114.6296385990581</v>
+        <v>-131.6395262933304</v>
       </c>
       <c r="Q72">
-        <v>205.8703614009419</v>
+        <v>188.8604737066696</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2542396637174076</v>
+        <v>0.2614272383283527</v>
       </c>
       <c r="T72">
-        <v>3.2244953059515</v>
+        <v>3.335684799260174</v>
       </c>
       <c r="U72">
         <v>0.1344309777667576</v>
       </c>
       <c r="V72">
-        <v>0.2259321417176045</v>
+        <v>0.2227499988765115</v>
       </c>
       <c r="W72">
-        <v>0.1040586990467224</v>
+        <v>0.104486477620244</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.903728566870418</v>
+        <v>0.8909999955060459</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1499992982255955</v>
+        <v>0.1508856080032631</v>
       </c>
       <c r="C73">
-        <v>1903.81617556994</v>
+        <v>1661.056718989294</v>
       </c>
       <c r="D73">
-        <v>13162.92617556994</v>
+        <v>13088.87671898929</v>
       </c>
       <c r="E73">
-        <v>989.0100000000002</v>
+        <v>1157.719999999999</v>
       </c>
       <c r="F73">
-        <v>11978.41</v>
+        <v>12147.12</v>
       </c>
       <c r="G73">
         <v>719.3</v>
@@ -7541,37 +7541,37 @@
         <v>1434.75</v>
       </c>
       <c r="M73">
-        <v>1610.269368391107</v>
+        <v>1632.949218650137</v>
       </c>
       <c r="N73">
-        <v>-175.519368391107</v>
+        <v>-198.1992186501366</v>
       </c>
       <c r="O73">
-        <v>-43.87984209777676</v>
+        <v>-49.54980466253414</v>
       </c>
       <c r="P73">
-        <v>-131.6395262933303</v>
+        <v>-148.6494139876024</v>
       </c>
       <c r="Q73">
-        <v>188.8604737066697</v>
+        <v>171.8505860123976</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2614272383283526</v>
+        <v>0.2691282111257938</v>
       </c>
       <c r="T73">
-        <v>3.335684799260172</v>
+        <v>3.45481639923375</v>
       </c>
       <c r="U73">
         <v>0.1344309777667576</v>
       </c>
       <c r="V73">
-        <v>0.2227499988765115</v>
+        <v>0.2196562488921155</v>
       </c>
       <c r="W73">
-        <v>0.104486477620244</v>
+        <v>0.1049023734556122</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.890999995506046</v>
+        <v>0.8786249955684622</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1508856080032631</v>
+        <v>0.1517719177809307</v>
       </c>
       <c r="C74">
-        <v>1661.056718989294</v>
+        <v>1419.125748034408</v>
       </c>
       <c r="D74">
-        <v>13088.87671898929</v>
+        <v>13015.65574803441</v>
       </c>
       <c r="E74">
-        <v>1157.719999999999</v>
+        <v>1326.43</v>
       </c>
       <c r="F74">
-        <v>12147.12</v>
+        <v>12315.83</v>
       </c>
       <c r="G74">
         <v>719.3</v>
@@ -7623,37 +7623,37 @@
         <v>1434.75</v>
       </c>
       <c r="M74">
-        <v>1632.949218650137</v>
+        <v>1655.629068909166</v>
       </c>
       <c r="N74">
-        <v>-198.1992186501366</v>
+        <v>-220.8790689091663</v>
       </c>
       <c r="O74">
-        <v>-49.54980466253414</v>
+        <v>-55.21976722729158</v>
       </c>
       <c r="P74">
-        <v>-148.6494139876024</v>
+        <v>-165.6593016818748</v>
       </c>
       <c r="Q74">
-        <v>171.8505860123976</v>
+        <v>154.8406983181252</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2691282111257938</v>
+        <v>0.2773996263526751</v>
       </c>
       <c r="T74">
-        <v>3.45481639923375</v>
+        <v>3.582772562168334</v>
       </c>
       <c r="U74">
         <v>0.1344309777667576</v>
       </c>
       <c r="V74">
-        <v>0.2196562488921155</v>
+        <v>0.2166472591812646</v>
       </c>
       <c r="W74">
-        <v>0.1049023734556122</v>
+        <v>0.1053068748845321</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8786249955684622</v>
+        <v>0.8665890367250585</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1517719177809307</v>
+        <v>0.1526582275585982</v>
       </c>
       <c r="C75">
-        <v>1419.125748034408</v>
+        <v>1178.009436066848</v>
       </c>
       <c r="D75">
-        <v>13015.65574803441</v>
+        <v>12943.24943606685</v>
       </c>
       <c r="E75">
-        <v>1326.43</v>
+        <v>1495.139999999999</v>
       </c>
       <c r="F75">
-        <v>12315.83</v>
+        <v>12484.54</v>
       </c>
       <c r="G75">
         <v>719.3</v>
@@ -7705,37 +7705,37 @@
         <v>1434.75</v>
       </c>
       <c r="M75">
-        <v>1655.629068909166</v>
+        <v>1678.308919168196</v>
       </c>
       <c r="N75">
-        <v>-220.8790689091663</v>
+        <v>-243.5589191681959</v>
       </c>
       <c r="O75">
-        <v>-55.21976722729158</v>
+        <v>-60.88972979204897</v>
       </c>
       <c r="P75">
-        <v>-165.6593016818748</v>
+        <v>-182.6691893761469</v>
       </c>
       <c r="Q75">
-        <v>154.8406983181252</v>
+        <v>137.8308106238531</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2773996263526751</v>
+        <v>0.2863073042893164</v>
       </c>
       <c r="T75">
-        <v>3.582772562168334</v>
+        <v>3.720571506867115</v>
       </c>
       <c r="U75">
         <v>0.1344309777667576</v>
       </c>
       <c r="V75">
-        <v>0.2166472591812646</v>
+        <v>0.213719593516653</v>
       </c>
       <c r="W75">
-        <v>0.1053068748845321</v>
+        <v>0.1057004438424</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8665890367250585</v>
+        <v>0.8548783740666118</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1526582275585982</v>
+        <v>0.1535445373362658</v>
       </c>
       <c r="C76">
-        <v>1178.009436066848</v>
+        <v>937.6942624173498</v>
       </c>
       <c r="D76">
-        <v>12943.24943606685</v>
+        <v>12871.64426241735</v>
       </c>
       <c r="E76">
-        <v>1495.139999999999</v>
+        <v>1663.85</v>
       </c>
       <c r="F76">
-        <v>12484.54</v>
+        <v>12653.25</v>
       </c>
       <c r="G76">
         <v>719.3</v>
@@ -7787,37 +7787,37 @@
         <v>1434.75</v>
       </c>
       <c r="M76">
-        <v>1678.308919168196</v>
+        <v>1700.988769427226</v>
       </c>
       <c r="N76">
-        <v>-243.5589191681959</v>
+        <v>-266.2387694272256</v>
       </c>
       <c r="O76">
-        <v>-60.88972979204897</v>
+        <v>-66.55969235680641</v>
       </c>
       <c r="P76">
-        <v>-182.6691893761469</v>
+        <v>-199.6790770704192</v>
       </c>
       <c r="Q76">
-        <v>137.8308106238531</v>
+        <v>120.8209229295808</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2863073042893164</v>
+        <v>0.2959275964608891</v>
       </c>
       <c r="T76">
-        <v>3.720571506867115</v>
+        <v>3.869394367141801</v>
       </c>
       <c r="U76">
         <v>0.1344309777667576</v>
       </c>
       <c r="V76">
-        <v>0.213719593516653</v>
+        <v>0.2108699989364309</v>
       </c>
       <c r="W76">
-        <v>0.1057004438424</v>
+        <v>0.1060835176280581</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8548783740666118</v>
+        <v>0.8434799957457236</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1535445373362658</v>
+        <v>0.1544308471139334</v>
       </c>
       <c r="C77">
-        <v>937.6942624173498</v>
+        <v>698.1670039689252</v>
       </c>
       <c r="D77">
-        <v>12871.64426241735</v>
+        <v>12800.82700396893</v>
       </c>
       <c r="E77">
-        <v>1663.85</v>
+        <v>1832.560000000001</v>
       </c>
       <c r="F77">
-        <v>12653.25</v>
+        <v>12821.96</v>
       </c>
       <c r="G77">
         <v>719.3</v>
@@ -7869,37 +7869,37 @@
         <v>1434.75</v>
       </c>
       <c r="M77">
-        <v>1700.988769427226</v>
+        <v>1723.668619686256</v>
       </c>
       <c r="N77">
-        <v>-266.2387694272256</v>
+        <v>-288.9186196862556</v>
       </c>
       <c r="O77">
-        <v>-66.55969235680641</v>
+        <v>-72.22965492156391</v>
       </c>
       <c r="P77">
-        <v>-199.6790770704192</v>
+        <v>-216.6889647646917</v>
       </c>
       <c r="Q77">
-        <v>120.8209229295808</v>
+        <v>103.8110352353083</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2959275964608891</v>
+        <v>0.3063495796467595</v>
       </c>
       <c r="T77">
-        <v>3.869394367141801</v>
+        <v>4.030619132439376</v>
       </c>
       <c r="U77">
         <v>0.1344309777667576</v>
       </c>
       <c r="V77">
-        <v>0.2108699989364309</v>
+        <v>0.2080953936872673</v>
       </c>
       <c r="W77">
-        <v>0.1060835176280581</v>
+        <v>0.1064565105246199</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8434799957457236</v>
+        <v>0.8323815747490693</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1544308471139334</v>
+        <v>0.155317156891601</v>
       </c>
       <c r="C78">
-        <v>698.1670039689252</v>
+        <v>459.4147270162666</v>
       </c>
       <c r="D78">
-        <v>12800.82700396893</v>
+        <v>12730.78472701627</v>
       </c>
       <c r="E78">
-        <v>1832.560000000001</v>
+        <v>2001.27</v>
       </c>
       <c r="F78">
-        <v>12821.96</v>
+        <v>12990.67</v>
       </c>
       <c r="G78">
         <v>719.3</v>
@@ -7951,37 +7951,37 @@
         <v>1434.75</v>
       </c>
       <c r="M78">
-        <v>1723.668619686256</v>
+        <v>1746.348469945285</v>
       </c>
       <c r="N78">
-        <v>-288.9186196862556</v>
+        <v>-311.5984699452852</v>
       </c>
       <c r="O78">
-        <v>-72.22965492156391</v>
+        <v>-77.89961748632129</v>
       </c>
       <c r="P78">
-        <v>-216.6889647646917</v>
+        <v>-233.6988524589639</v>
       </c>
       <c r="Q78">
-        <v>103.8110352353083</v>
+        <v>86.80114754103613</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3063495796467595</v>
+        <v>0.3176778222400969</v>
       </c>
       <c r="T78">
-        <v>4.030619132439376</v>
+        <v>4.205863442545436</v>
       </c>
       <c r="U78">
         <v>0.1344309777667576</v>
       </c>
       <c r="V78">
-        <v>0.2080953936872673</v>
+        <v>0.2053928561069132</v>
       </c>
       <c r="W78">
-        <v>0.1064565105246199</v>
+        <v>0.1068198152939983</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8323815747490693</v>
+        <v>0.8215714244276529</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.155317156891601</v>
+        <v>0.1562034666692685</v>
       </c>
       <c r="C79">
-        <v>459.4147270162666</v>
+        <v>221.4247793909617</v>
       </c>
       <c r="D79">
-        <v>12730.78472701627</v>
+        <v>12661.50477939096</v>
       </c>
       <c r="E79">
-        <v>2001.27</v>
+        <v>2169.980000000001</v>
       </c>
       <c r="F79">
-        <v>12990.67</v>
+        <v>13159.38</v>
       </c>
       <c r="G79">
         <v>719.3</v>
@@ -8033,37 +8033,37 @@
         <v>1434.75</v>
       </c>
       <c r="M79">
-        <v>1746.348469945285</v>
+        <v>1769.028320204315</v>
       </c>
       <c r="N79">
-        <v>-311.5984699452852</v>
+        <v>-334.2783202043149</v>
       </c>
       <c r="O79">
-        <v>-77.89961748632129</v>
+        <v>-83.56958005107873</v>
       </c>
       <c r="P79">
-        <v>-233.6988524589639</v>
+        <v>-250.7087401532362</v>
       </c>
       <c r="Q79">
-        <v>86.80114754103613</v>
+        <v>69.79125984676381</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3176778222400969</v>
+        <v>0.3300359050691922</v>
       </c>
       <c r="T79">
-        <v>4.205863442545436</v>
+        <v>4.397039053570228</v>
       </c>
       <c r="U79">
         <v>0.1344309777667576</v>
       </c>
       <c r="V79">
-        <v>0.2053928561069132</v>
+        <v>0.2027596143619528</v>
       </c>
       <c r="W79">
-        <v>0.1068198152939983</v>
+        <v>0.1071738045564696</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8215714244276529</v>
+        <v>0.8110384574478111</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1562034666692685</v>
+        <v>0.1570897764469361</v>
       </c>
       <c r="C80">
-        <v>221.4247793909617</v>
+        <v>-15.81521715753297</v>
       </c>
       <c r="D80">
-        <v>12661.50477939096</v>
+        <v>12592.97478284247</v>
       </c>
       <c r="E80">
-        <v>2169.980000000001</v>
+        <v>2338.690000000001</v>
       </c>
       <c r="F80">
-        <v>13159.38</v>
+        <v>13328.09</v>
       </c>
       <c r="G80">
         <v>719.3</v>
@@ -8115,37 +8115,37 @@
         <v>1434.75</v>
       </c>
       <c r="M80">
-        <v>1769.028320204315</v>
+        <v>1791.708170463344</v>
       </c>
       <c r="N80">
-        <v>-334.2783202043149</v>
+        <v>-356.9581704633445</v>
       </c>
       <c r="O80">
-        <v>-83.56958005107873</v>
+        <v>-89.23954261583611</v>
       </c>
       <c r="P80">
-        <v>-250.7087401532362</v>
+        <v>-267.7186278475083</v>
       </c>
       <c r="Q80">
-        <v>69.79125984676381</v>
+        <v>52.78137215249166</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3300359050691922</v>
+        <v>0.3435709481677252</v>
       </c>
       <c r="T80">
-        <v>4.397039053570228</v>
+        <v>4.606421865645001</v>
       </c>
       <c r="U80">
         <v>0.1344309777667576</v>
       </c>
       <c r="V80">
-        <v>0.2027596143619528</v>
+        <v>0.200193036964966</v>
       </c>
       <c r="W80">
-        <v>0.1071738045564696</v>
+        <v>0.1075188320654606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8110384574478111</v>
+        <v>0.8007721478598642</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1570897764469361</v>
+        <v>0.1825730818020935</v>
       </c>
       <c r="C81">
-        <v>-15.81521715753297</v>
+        <v>-1880.341741005695</v>
       </c>
       <c r="D81">
-        <v>12592.97478284247</v>
+        <v>10897.15825899431</v>
       </c>
       <c r="E81">
-        <v>2338.690000000001</v>
+        <v>2507.400000000001</v>
       </c>
       <c r="F81">
-        <v>13328.09</v>
+        <v>13496.8</v>
       </c>
       <c r="G81">
         <v>719.3</v>
@@ -8197,45 +8197,45 @@
         <v>1434.75</v>
       </c>
       <c r="M81">
-        <v>1791.708170463344</v>
+        <v>2194.997780722375</v>
       </c>
       <c r="N81">
-        <v>-356.9581704633445</v>
+        <v>-760.2477807223745</v>
       </c>
       <c r="O81">
-        <v>-89.23954261583611</v>
+        <v>-190.0619451805936</v>
       </c>
       <c r="P81">
-        <v>-267.7186278475083</v>
+        <v>-570.1858355417809</v>
       </c>
       <c r="Q81">
-        <v>52.78137215249166</v>
+        <v>-249.6858355417809</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3435709481677252</v>
+        <v>0.3686444734635606</v>
       </c>
       <c r="T81">
-        <v>4.606421865645001</v>
+        <v>4.994301327634966</v>
       </c>
       <c r="U81">
-        <v>0.1344309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V81">
-        <v>0.200193036964966</v>
+        <v>0.1634113269499324</v>
       </c>
       <c r="W81">
-        <v>0.1075188320654606</v>
+        <v>0.1360552338867268</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8007721478598642</v>
+        <v>0.6536453077997297</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1825730818020935</v>
+        <v>0.2299019386652058</v>
       </c>
       <c r="C82">
-        <v>-1880.341741005695</v>
+        <v>-4229.209242435858</v>
       </c>
       <c r="D82">
-        <v>10897.15825899431</v>
+        <v>8717.000757564143</v>
       </c>
       <c r="E82">
-        <v>2507.400000000001</v>
+        <v>2676.110000000001</v>
       </c>
       <c r="F82">
-        <v>13496.8</v>
+        <v>13665.51</v>
       </c>
       <c r="G82">
         <v>719.3</v>
@@ -8279,45 +8279,45 @@
         <v>1434.75</v>
       </c>
       <c r="M82">
-        <v>2194.997780722375</v>
+        <v>2960.372792981404</v>
       </c>
       <c r="N82">
-        <v>-760.2477807223745</v>
+        <v>-1525.622792981404</v>
       </c>
       <c r="O82">
-        <v>-190.0619451805936</v>
+        <v>-381.4056982453509</v>
       </c>
       <c r="P82">
-        <v>-570.1858355417809</v>
+        <v>-1144.217094736053</v>
       </c>
       <c r="Q82">
-        <v>-249.6858355417809</v>
+        <v>-823.7170947360528</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3686444734635606</v>
+        <v>0.3983760093587198</v>
       </c>
       <c r="T82">
-        <v>4.994301327634966</v>
+        <v>5.454238732171583</v>
       </c>
       <c r="U82">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V82">
-        <v>0.1634113269499324</v>
+        <v>0.121162949764433</v>
       </c>
       <c r="W82">
-        <v>0.1360552338867268</v>
+        <v>0.190383329490184</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.6536453077997297</v>
+        <v>0.484651799057732</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2299019386652058</v>
+        <v>0.2316102484428733</v>
       </c>
       <c r="C83">
-        <v>-4229.209242435858</v>
+        <v>-4460.415988555542</v>
       </c>
       <c r="D83">
-        <v>8717.000757564143</v>
+        <v>8654.50401144446</v>
       </c>
       <c r="E83">
-        <v>2676.110000000001</v>
+        <v>2844.820000000002</v>
       </c>
       <c r="F83">
-        <v>13665.51</v>
+        <v>13834.22</v>
       </c>
       <c r="G83">
         <v>719.3</v>
@@ -8361,37 +8361,37 @@
         <v>1434.75</v>
       </c>
       <c r="M83">
-        <v>2960.372792981404</v>
+        <v>2996.920605240434</v>
       </c>
       <c r="N83">
-        <v>-1525.622792981404</v>
+        <v>-1562.170605240434</v>
       </c>
       <c r="O83">
-        <v>-381.4056982453509</v>
+        <v>-390.5426513101085</v>
       </c>
       <c r="P83">
-        <v>-1144.217094736053</v>
+        <v>-1171.627953930325</v>
       </c>
       <c r="Q83">
-        <v>-823.7170947360528</v>
+        <v>-851.1279539303255</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3983760093587198</v>
+        <v>0.4179635654342042</v>
       </c>
       <c r="T83">
-        <v>5.454238732171583</v>
+        <v>5.757251995070004</v>
       </c>
       <c r="U83">
         <v>0.2166309777667576</v>
       </c>
       <c r="V83">
-        <v>0.121162949764433</v>
+        <v>0.1196853528160862</v>
       </c>
       <c r="W83">
-        <v>0.190383329490184</v>
+        <v>0.1907034227618495</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.484651799057732</v>
+        <v>0.4787414112643449</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2316102484428733</v>
+        <v>0.2333185582205409</v>
       </c>
       <c r="C84">
-        <v>-4460.415988555542</v>
+        <v>-4690.732970022089</v>
       </c>
       <c r="D84">
-        <v>8654.50401144446</v>
+        <v>8592.897029977912</v>
       </c>
       <c r="E84">
-        <v>2844.820000000002</v>
+        <v>3013.530000000001</v>
       </c>
       <c r="F84">
-        <v>13834.22</v>
+        <v>14002.93</v>
       </c>
       <c r="G84">
         <v>719.3</v>
@@ -8443,37 +8443,37 @@
         <v>1434.75</v>
       </c>
       <c r="M84">
-        <v>2996.920605240434</v>
+        <v>3033.468417499463</v>
       </c>
       <c r="N84">
-        <v>-1562.170605240434</v>
+        <v>-1598.718417499463</v>
       </c>
       <c r="O84">
-        <v>-390.5426513101085</v>
+        <v>-399.6796043748658</v>
       </c>
       <c r="P84">
-        <v>-1171.627953930325</v>
+        <v>-1199.038813124597</v>
       </c>
       <c r="Q84">
-        <v>-851.1279539303255</v>
+        <v>-878.5388131245973</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4179635654342042</v>
+        <v>0.4398555398715104</v>
       </c>
       <c r="T84">
-        <v>5.757251995070004</v>
+        <v>6.095913877132946</v>
       </c>
       <c r="U84">
         <v>0.2166309777667576</v>
       </c>
       <c r="V84">
-        <v>0.1196853528160862</v>
+        <v>0.1182433606134828</v>
       </c>
       <c r="W84">
-        <v>0.1907034227618495</v>
+        <v>0.1910158029426315</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4787414112643449</v>
+        <v>0.4729734424539311</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2333185582205409</v>
+        <v>0.2350268679982085</v>
       </c>
       <c r="C85">
-        <v>-4690.732970022089</v>
+        <v>-4920.179053867321</v>
       </c>
       <c r="D85">
-        <v>8592.897029977912</v>
+        <v>8532.160946132681</v>
       </c>
       <c r="E85">
-        <v>3013.530000000001</v>
+        <v>3182.240000000002</v>
       </c>
       <c r="F85">
-        <v>14002.93</v>
+        <v>14171.64</v>
       </c>
       <c r="G85">
         <v>719.3</v>
@@ -8525,37 +8525,37 @@
         <v>1434.75</v>
       </c>
       <c r="M85">
-        <v>3033.468417499463</v>
+        <v>3070.016229758493</v>
       </c>
       <c r="N85">
-        <v>-1598.718417499463</v>
+        <v>-1635.266229758493</v>
       </c>
       <c r="O85">
-        <v>-399.6796043748658</v>
+        <v>-408.8165574396232</v>
       </c>
       <c r="P85">
-        <v>-1199.038813124597</v>
+        <v>-1226.44967231887</v>
       </c>
       <c r="Q85">
-        <v>-878.5388131245973</v>
+        <v>-905.9496723188697</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4398555398715104</v>
+        <v>0.4644840111134799</v>
       </c>
       <c r="T85">
-        <v>6.095913877132946</v>
+        <v>6.476908494453757</v>
       </c>
       <c r="U85">
         <v>0.2166309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1182433606134828</v>
+        <v>0.1168357015585604</v>
       </c>
       <c r="W85">
-        <v>0.1910158029426315</v>
+        <v>0.1913207455000616</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4729734424539311</v>
+        <v>0.4673428062342415</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2350268679982085</v>
+        <v>0.236735177775876</v>
       </c>
       <c r="C86">
-        <v>-4920.179053867319</v>
+        <v>-5148.772577445126</v>
       </c>
       <c r="D86">
-        <v>8532.160946132681</v>
+        <v>8472.277422554875</v>
       </c>
       <c r="E86">
-        <v>3182.24</v>
+        <v>3350.950000000001</v>
       </c>
       <c r="F86">
-        <v>14171.64</v>
+        <v>14340.35</v>
       </c>
       <c r="G86">
         <v>719.3</v>
@@ -8607,37 +8607,37 @@
         <v>1434.75</v>
       </c>
       <c r="M86">
-        <v>3070.016229758492</v>
+        <v>3106.564042017522</v>
       </c>
       <c r="N86">
-        <v>-1635.266229758492</v>
+        <v>-1671.814042017522</v>
       </c>
       <c r="O86">
-        <v>-408.8165574396231</v>
+        <v>-417.9535105043806</v>
       </c>
       <c r="P86">
-        <v>-1226.449672318869</v>
+        <v>-1253.860531513142</v>
       </c>
       <c r="Q86">
-        <v>-905.9496723188695</v>
+        <v>-933.3605315131417</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4644840111134795</v>
+        <v>0.4923962785210449</v>
       </c>
       <c r="T86">
-        <v>6.476908494453752</v>
+        <v>6.908702394084003</v>
       </c>
       <c r="U86">
         <v>0.2166309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1168357015585604</v>
+        <v>0.1154611638931656</v>
       </c>
       <c r="W86">
-        <v>0.1913207455000616</v>
+        <v>0.1916185129384933</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4673428062342415</v>
+        <v>0.4618446555726622</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.236735177775876</v>
+        <v>0.2384434875535436</v>
       </c>
       <c r="C87">
-        <v>-5148.772577445126</v>
+        <v>-5376.531366889809</v>
       </c>
       <c r="D87">
-        <v>8472.277422554875</v>
+        <v>8413.228633110191</v>
       </c>
       <c r="E87">
-        <v>3350.950000000001</v>
+        <v>3519.66</v>
       </c>
       <c r="F87">
-        <v>14340.35</v>
+        <v>14509.06</v>
       </c>
       <c r="G87">
         <v>719.3</v>
@@ -8689,37 +8689,37 @@
         <v>1434.75</v>
       </c>
       <c r="M87">
-        <v>3106.564042017522</v>
+        <v>3143.111854276552</v>
       </c>
       <c r="N87">
-        <v>-1671.814042017522</v>
+        <v>-1708.361854276552</v>
       </c>
       <c r="O87">
-        <v>-417.9535105043806</v>
+        <v>-427.090463569138</v>
       </c>
       <c r="P87">
-        <v>-1253.860531513142</v>
+        <v>-1281.271390707414</v>
       </c>
       <c r="Q87">
-        <v>-933.3605315131417</v>
+        <v>-960.771390707414</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4923962785210449</v>
+        <v>0.5242960127011196</v>
       </c>
       <c r="T87">
-        <v>6.908702394084003</v>
+        <v>7.402181136518575</v>
       </c>
       <c r="U87">
         <v>0.2166309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1154611638931656</v>
+        <v>0.1141185922199892</v>
       </c>
       <c r="W87">
-        <v>0.1916185129384933</v>
+        <v>0.1919093555527754</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4618446555726622</v>
+        <v>0.4564743688799568</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2384434875535436</v>
+        <v>0.2401517973312112</v>
       </c>
       <c r="C88">
-        <v>-5376.531366889809</v>
+        <v>-5603.472754807875</v>
       </c>
       <c r="D88">
-        <v>8413.228633110191</v>
+        <v>8354.997245192126</v>
       </c>
       <c r="E88">
-        <v>3519.66</v>
+        <v>3688.370000000001</v>
       </c>
       <c r="F88">
-        <v>14509.06</v>
+        <v>14677.77</v>
       </c>
       <c r="G88">
         <v>719.3</v>
@@ -8771,37 +8771,37 @@
         <v>1434.75</v>
       </c>
       <c r="M88">
-        <v>3143.111854276552</v>
+        <v>3179.659666535582</v>
       </c>
       <c r="N88">
-        <v>-1708.361854276552</v>
+        <v>-1744.909666535582</v>
       </c>
       <c r="O88">
-        <v>-427.090463569138</v>
+        <v>-436.2274166338955</v>
       </c>
       <c r="P88">
-        <v>-1281.271390707414</v>
+        <v>-1308.682249901686</v>
       </c>
       <c r="Q88">
-        <v>-960.771390707414</v>
+        <v>-988.1822499016864</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5242960127011196</v>
+        <v>0.5611033982935133</v>
       </c>
       <c r="T88">
-        <v>7.402181136518575</v>
+        <v>7.971579685481542</v>
       </c>
       <c r="U88">
         <v>0.2166309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1141185922199892</v>
+        <v>0.1128068842634376</v>
       </c>
       <c r="W88">
-        <v>0.1919093555527754</v>
+        <v>0.1921935121299477</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4564743688799568</v>
+        <v>0.4512275370537504</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2401517973312112</v>
+        <v>0.2418601071088788</v>
       </c>
       <c r="C89">
-        <v>-5603.472754807875</v>
+        <v>-5829.613597240168</v>
       </c>
       <c r="D89">
-        <v>8354.997245192126</v>
+        <v>8297.566402759832</v>
       </c>
       <c r="E89">
-        <v>3688.370000000001</v>
+        <v>3857.08</v>
       </c>
       <c r="F89">
-        <v>14677.77</v>
+        <v>14846.48</v>
       </c>
       <c r="G89">
         <v>719.3</v>
@@ -8853,37 +8853,37 @@
         <v>1434.75</v>
       </c>
       <c r="M89">
-        <v>3179.659666535582</v>
+        <v>3216.207478794611</v>
       </c>
       <c r="N89">
-        <v>-1744.909666535582</v>
+        <v>-1781.457478794611</v>
       </c>
       <c r="O89">
-        <v>-436.2274166338955</v>
+        <v>-445.3643696986528</v>
       </c>
       <c r="P89">
-        <v>-1308.682249901686</v>
+        <v>-1336.093109095958</v>
       </c>
       <c r="Q89">
-        <v>-988.1822499016864</v>
+        <v>-1015.593109095958</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5611033982935133</v>
+        <v>0.6040453481513061</v>
       </c>
       <c r="T89">
-        <v>7.971579685481542</v>
+        <v>8.635877992605003</v>
       </c>
       <c r="U89">
         <v>0.2166309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1128068842634376</v>
+        <v>0.1115249878513531</v>
       </c>
       <c r="W89">
-        <v>0.1921935121299477</v>
+        <v>0.1924712106030932</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4512275370537504</v>
+        <v>0.4460999514054124</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2418601071088788</v>
+        <v>0.2435684168865463</v>
       </c>
       <c r="C90">
-        <v>-5829.613597240168</v>
+        <v>-6054.970289929217</v>
       </c>
       <c r="D90">
-        <v>8297.566402759832</v>
+        <v>8240.919710070784</v>
       </c>
       <c r="E90">
-        <v>3857.08</v>
+        <v>4025.790000000001</v>
       </c>
       <c r="F90">
-        <v>14846.48</v>
+        <v>15015.19</v>
       </c>
       <c r="G90">
         <v>719.3</v>
@@ -8935,37 +8935,37 @@
         <v>1434.75</v>
       </c>
       <c r="M90">
-        <v>3216.207478794611</v>
+        <v>3252.755291053641</v>
       </c>
       <c r="N90">
-        <v>-1781.457478794611</v>
+        <v>-1818.005291053641</v>
       </c>
       <c r="O90">
-        <v>-445.3643696986528</v>
+        <v>-454.5013227634103</v>
       </c>
       <c r="P90">
-        <v>-1336.093109095958</v>
+        <v>-1363.503968290231</v>
       </c>
       <c r="Q90">
-        <v>-1015.593109095958</v>
+        <v>-1043.003968290231</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6040453481513061</v>
+        <v>0.6547949252559704</v>
       </c>
       <c r="T90">
-        <v>8.635877992605003</v>
+        <v>9.420957810114551</v>
       </c>
       <c r="U90">
         <v>0.2166309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1115249878513531</v>
+        <v>0.1102718981002143</v>
       </c>
       <c r="W90">
-        <v>0.1924712106030932</v>
+        <v>0.1927426686611119</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4460999514054124</v>
+        <v>0.4410875924008572</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2435684168865463</v>
+        <v>0.2452767266642139</v>
       </c>
       <c r="C91">
-        <v>-6054.970289929217</v>
+        <v>-6279.558783924756</v>
       </c>
       <c r="D91">
-        <v>8240.919710070784</v>
+        <v>8185.041216075243</v>
       </c>
       <c r="E91">
-        <v>4025.790000000001</v>
+        <v>4194.5</v>
       </c>
       <c r="F91">
-        <v>15015.19</v>
+        <v>15183.9</v>
       </c>
       <c r="G91">
         <v>719.3</v>
@@ -9017,37 +9017,37 @@
         <v>1434.75</v>
       </c>
       <c r="M91">
-        <v>3252.755291053641</v>
+        <v>3289.303103312671</v>
       </c>
       <c r="N91">
-        <v>-1818.005291053641</v>
+        <v>-1854.553103312671</v>
       </c>
       <c r="O91">
-        <v>-454.5013227634103</v>
+        <v>-463.6382758281677</v>
       </c>
       <c r="P91">
-        <v>-1363.503968290231</v>
+        <v>-1390.914827484503</v>
       </c>
       <c r="Q91">
-        <v>-1043.003968290231</v>
+        <v>-1070.414827484503</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6547949252559704</v>
+        <v>0.7156944177815675</v>
       </c>
       <c r="T91">
-        <v>9.420957810114551</v>
+        <v>10.36305359112601</v>
       </c>
       <c r="U91">
         <v>0.2166309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1102718981002143</v>
+        <v>0.1090466547879897</v>
       </c>
       <c r="W91">
-        <v>0.1927426686611119</v>
+        <v>0.1930080943178413</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4410875924008572</v>
+        <v>0.4361866191519588</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2452767266642139</v>
+        <v>0.2469850364418815</v>
       </c>
       <c r="C92">
-        <v>-6279.558783924756</v>
+        <v>-6503.394600558646</v>
       </c>
       <c r="D92">
-        <v>8185.041216075243</v>
+        <v>8129.915399441355</v>
       </c>
       <c r="E92">
-        <v>4194.5</v>
+        <v>4363.210000000001</v>
       </c>
       <c r="F92">
-        <v>15183.9</v>
+        <v>15352.61</v>
       </c>
       <c r="G92">
         <v>719.3</v>
@@ -9099,37 +9099,37 @@
         <v>1434.75</v>
       </c>
       <c r="M92">
-        <v>3289.303103312671</v>
+        <v>3325.850915571701</v>
       </c>
       <c r="N92">
-        <v>-1854.553103312671</v>
+        <v>-1891.100915571701</v>
       </c>
       <c r="O92">
-        <v>-463.6382758281677</v>
+        <v>-472.7752288929252</v>
       </c>
       <c r="P92">
-        <v>-1390.914827484503</v>
+        <v>-1418.325686678776</v>
       </c>
       <c r="Q92">
-        <v>-1070.414827484503</v>
+        <v>-1097.825686678776</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7156944177815675</v>
+        <v>0.7901271308684084</v>
       </c>
       <c r="T92">
-        <v>10.36305359112601</v>
+        <v>11.51450399014001</v>
       </c>
       <c r="U92">
         <v>0.2166309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1090466547879897</v>
+        <v>0.1078483399002096</v>
       </c>
       <c r="W92">
-        <v>0.1930080943178413</v>
+        <v>0.1932676864436536</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4361866191519588</v>
+        <v>0.4313933596008384</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2469850364418815</v>
+        <v>0.2486933462195491</v>
       </c>
       <c r="C93">
-        <v>-6503.394600558646</v>
+        <v>-6726.492845818682</v>
       </c>
       <c r="D93">
-        <v>8129.915399441355</v>
+        <v>8075.52715418132</v>
       </c>
       <c r="E93">
-        <v>4363.210000000001</v>
+        <v>4531.920000000002</v>
       </c>
       <c r="F93">
-        <v>15352.61</v>
+        <v>15521.32</v>
       </c>
       <c r="G93">
         <v>719.3</v>
@@ -9181,37 +9181,37 @@
         <v>1434.75</v>
       </c>
       <c r="M93">
-        <v>3325.850915571701</v>
+        <v>3362.39872783073</v>
       </c>
       <c r="N93">
-        <v>-1891.100915571701</v>
+        <v>-1927.64872783073</v>
       </c>
       <c r="O93">
-        <v>-472.7752288929252</v>
+        <v>-481.9121819576826</v>
       </c>
       <c r="P93">
-        <v>-1418.325686678776</v>
+        <v>-1445.736545873048</v>
       </c>
       <c r="Q93">
-        <v>-1097.825686678776</v>
+        <v>-1125.236545873048</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7901271308684084</v>
+        <v>0.8831680222269598</v>
       </c>
       <c r="T93">
-        <v>11.51450399014001</v>
+        <v>12.95381698890751</v>
       </c>
       <c r="U93">
         <v>0.2166309777667576</v>
       </c>
       <c r="V93">
-        <v>0.1078483399002096</v>
+        <v>0.1066760753360769</v>
       </c>
       <c r="W93">
-        <v>0.1932676864436536</v>
+        <v>0.193521635262383</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4313933596008384</v>
+        <v>0.4267043013443075</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2486933462195491</v>
+        <v>0.2504016559972166</v>
       </c>
       <c r="C94">
-        <v>-6726.492845818682</v>
+        <v>-6948.868224149308</v>
       </c>
       <c r="D94">
-        <v>8075.52715418132</v>
+        <v>8021.861775850693</v>
       </c>
       <c r="E94">
-        <v>4531.920000000002</v>
+        <v>4700.630000000001</v>
       </c>
       <c r="F94">
-        <v>15521.32</v>
+        <v>15690.03</v>
       </c>
       <c r="G94">
         <v>719.3</v>
@@ -9263,37 +9263,37 @@
         <v>1434.75</v>
       </c>
       <c r="M94">
-        <v>3362.39872783073</v>
+        <v>3398.94654008976</v>
       </c>
       <c r="N94">
-        <v>-1927.64872783073</v>
+        <v>-1964.19654008976</v>
       </c>
       <c r="O94">
-        <v>-481.9121819576826</v>
+        <v>-491.0491350224399</v>
       </c>
       <c r="P94">
-        <v>-1445.736545873048</v>
+        <v>-1473.14740506732</v>
       </c>
       <c r="Q94">
-        <v>-1125.236545873048</v>
+        <v>-1152.64740506732</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8831680222269598</v>
+        <v>1.00279202540224</v>
       </c>
       <c r="T94">
-        <v>12.95381698890751</v>
+        <v>14.80436227303716</v>
       </c>
       <c r="U94">
         <v>0.2166309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1066760753360769</v>
+        <v>0.1055290207625707</v>
       </c>
       <c r="W94">
-        <v>0.193521635262383</v>
+        <v>0.1937701228161935</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4267043013443075</v>
+        <v>0.4221160830502827</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2504016559972166</v>
+        <v>0.2521099657748843</v>
       </c>
       <c r="C95">
-        <v>-6948.868224149308</v>
+        <v>-7170.535051705716</v>
       </c>
       <c r="D95">
-        <v>8021.861775850693</v>
+        <v>7968.904948294286</v>
       </c>
       <c r="E95">
-        <v>4700.630000000001</v>
+        <v>4869.340000000002</v>
       </c>
       <c r="F95">
-        <v>15690.03</v>
+        <v>15858.74</v>
       </c>
       <c r="G95">
         <v>719.3</v>
@@ -9345,37 +9345,37 @@
         <v>1434.75</v>
       </c>
       <c r="M95">
-        <v>3398.94654008976</v>
+        <v>3435.49435234879</v>
       </c>
       <c r="N95">
-        <v>-1964.19654008976</v>
+        <v>-2000.74435234879</v>
       </c>
       <c r="O95">
-        <v>-491.0491350224399</v>
+        <v>-500.1860880871975</v>
       </c>
       <c r="P95">
-        <v>-1473.14740506732</v>
+        <v>-1500.558264261593</v>
       </c>
       <c r="Q95">
-        <v>-1152.64740506732</v>
+        <v>-1180.058264261593</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.00279202540224</v>
+        <v>1.162290696302613</v>
       </c>
       <c r="T95">
-        <v>14.80436227303716</v>
+        <v>17.27175598521002</v>
       </c>
       <c r="U95">
         <v>0.2166309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1055290207625707</v>
+        <v>0.104406371605522</v>
       </c>
       <c r="W95">
-        <v>0.1937701228161935</v>
+        <v>0.1940133234007739</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4221160830502827</v>
+        <v>0.4176254864220881</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2521099657748843</v>
+        <v>0.2538182755525519</v>
       </c>
       <c r="C96">
-        <v>-7170.535051705716</v>
+        <v>-7391.507269086322</v>
       </c>
       <c r="D96">
-        <v>7968.904948294286</v>
+        <v>7916.642730913679</v>
       </c>
       <c r="E96">
-        <v>4869.340000000002</v>
+        <v>5038.050000000001</v>
       </c>
       <c r="F96">
-        <v>15858.74</v>
+        <v>16027.45</v>
       </c>
       <c r="G96">
         <v>719.3</v>
@@ -9427,37 +9427,37 @@
         <v>1434.75</v>
       </c>
       <c r="M96">
-        <v>3435.49435234879</v>
+        <v>3472.042164607819</v>
       </c>
       <c r="N96">
-        <v>-2000.74435234879</v>
+        <v>-2037.292164607819</v>
       </c>
       <c r="O96">
-        <v>-500.1860880871975</v>
+        <v>-509.3230411519548</v>
       </c>
       <c r="P96">
-        <v>-1500.558264261593</v>
+        <v>-1527.969123455865</v>
       </c>
       <c r="Q96">
-        <v>-1180.058264261593</v>
+        <v>-1207.469123455865</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.162290696302613</v>
+        <v>1.385588835563137</v>
       </c>
       <c r="T96">
-        <v>17.27175598521002</v>
+        <v>20.72610718225204</v>
       </c>
       <c r="U96">
         <v>0.2166309777667576</v>
       </c>
       <c r="V96">
-        <v>0.104406371605522</v>
+        <v>0.1033073571675692</v>
       </c>
       <c r="W96">
-        <v>0.1940133234007739</v>
+        <v>0.1942514039730475</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4176254864220881</v>
+        <v>0.4132294286702767</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2538182755525519</v>
+        <v>0.2555265853302194</v>
       </c>
       <c r="C97">
-        <v>-7391.507269086322</v>
+        <v>-7611.798453567568</v>
       </c>
       <c r="D97">
-        <v>7916.642730913679</v>
+        <v>7865.061546432434</v>
       </c>
       <c r="E97">
-        <v>5038.050000000001</v>
+        <v>5206.760000000002</v>
       </c>
       <c r="F97">
-        <v>16027.45</v>
+        <v>16196.16</v>
       </c>
       <c r="G97">
         <v>719.3</v>
@@ -9509,37 +9509,37 @@
         <v>1434.75</v>
       </c>
       <c r="M97">
-        <v>3472.042164607819</v>
+        <v>3508.589976866849</v>
       </c>
       <c r="N97">
-        <v>-2037.292164607819</v>
+        <v>-2073.839976866849</v>
       </c>
       <c r="O97">
-        <v>-509.3230411519548</v>
+        <v>-518.4599942167123</v>
       </c>
       <c r="P97">
-        <v>-1527.969123455865</v>
+        <v>-1555.379982650137</v>
       </c>
       <c r="Q97">
-        <v>-1207.469123455865</v>
+        <v>-1234.879982650137</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.385588835563137</v>
+        <v>1.720536044453922</v>
       </c>
       <c r="T97">
-        <v>20.72610718225204</v>
+        <v>25.90763397781506</v>
       </c>
       <c r="U97">
         <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1033073571675692</v>
+        <v>0.1022312388637403</v>
       </c>
       <c r="W97">
-        <v>0.1942514039730475</v>
+        <v>0.1944845245333986</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4132294286702767</v>
+        <v>0.4089249554549613</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2555265853302194</v>
+        <v>0.2572348951078869</v>
       </c>
       <c r="C98">
-        <v>-7611.798453567564</v>
+        <v>-7831.421830863485</v>
       </c>
       <c r="D98">
-        <v>7865.061546432436</v>
+        <v>7814.148169136515</v>
       </c>
       <c r="E98">
-        <v>5206.76</v>
+        <v>5375.469999999999</v>
       </c>
       <c r="F98">
-        <v>16196.16</v>
+        <v>16364.87</v>
       </c>
       <c r="G98">
         <v>719.3</v>
@@ -9591,37 +9591,37 @@
         <v>1434.75</v>
       </c>
       <c r="M98">
-        <v>3508.589976866849</v>
+        <v>3545.137789125878</v>
       </c>
       <c r="N98">
-        <v>-2073.839976866849</v>
+        <v>-2110.387789125878</v>
       </c>
       <c r="O98">
-        <v>-518.4599942167122</v>
+        <v>-527.5969472814696</v>
       </c>
       <c r="P98">
-        <v>-1555.379982650137</v>
+        <v>-1582.790841844409</v>
       </c>
       <c r="Q98">
-        <v>-1234.879982650137</v>
+        <v>-1262.290841844409</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.720536044453917</v>
+        <v>2.278781392605222</v>
       </c>
       <c r="T98">
-        <v>25.90763397781499</v>
+        <v>34.54351197041998</v>
       </c>
       <c r="U98">
         <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1022312388637403</v>
+        <v>0.101177308566176</v>
       </c>
       <c r="W98">
-        <v>0.1944845245333986</v>
+        <v>0.194712838484258</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4089249554549613</v>
+        <v>0.404709234264704</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9637,22 +9637,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2572348951078869</v>
+        <v>0.2589432048855546</v>
       </c>
       <c r="C99">
-        <v>-7831.421830863485</v>
+        <v>-8050.390286431468</v>
       </c>
       <c r="D99">
-        <v>7814.148169136515</v>
+        <v>7763.88971356853</v>
       </c>
       <c r="E99">
-        <v>5375.469999999999</v>
+        <v>5544.179999999998</v>
       </c>
       <c r="F99">
-        <v>16364.87</v>
+        <v>16533.58</v>
       </c>
       <c r="G99">
         <v>719.3</v>
@@ -9673,37 +9673,37 @@
         <v>1434.75</v>
       </c>
       <c r="M99">
-        <v>3545.137789125878</v>
+        <v>3581.685601384908</v>
       </c>
       <c r="N99">
-        <v>-2110.387789125878</v>
+        <v>-2146.935601384908</v>
       </c>
       <c r="O99">
-        <v>-527.5969472814696</v>
+        <v>-536.733900346227</v>
       </c>
       <c r="P99">
-        <v>-1582.790841844409</v>
+        <v>-1610.201701038681</v>
       </c>
       <c r="Q99">
-        <v>-1262.290841844409</v>
+        <v>-1289.701701038681</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.278781392605222</v>
+        <v>3.395272088907834</v>
       </c>
       <c r="T99">
-        <v>34.54351197041998</v>
+        <v>51.81526795562998</v>
       </c>
       <c r="U99">
         <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.101177308566176</v>
+        <v>0.1001448870501946</v>
       </c>
       <c r="W99">
-        <v>0.194712838484258</v>
+        <v>0.1949364929667324</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.404709234264704</v>
+        <v>0.4005795482007785</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9719,22 +9719,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2589432048855546</v>
+        <v>0.2606515146632221</v>
       </c>
       <c r="C100">
-        <v>-8050.390286431468</v>
+        <v>-8268.716376344521</v>
       </c>
       <c r="D100">
-        <v>7763.88971356853</v>
+        <v>7714.273623655481</v>
       </c>
       <c r="E100">
-        <v>5544.179999999998</v>
+        <v>5712.890000000001</v>
       </c>
       <c r="F100">
-        <v>16533.58</v>
+        <v>16702.29</v>
       </c>
       <c r="G100">
         <v>719.3</v>
@@ -9755,37 +9755,37 @@
         <v>1434.75</v>
       </c>
       <c r="M100">
-        <v>3581.685601384908</v>
+        <v>3618.233413643938</v>
       </c>
       <c r="N100">
-        <v>-2146.935601384908</v>
+        <v>-2183.483413643938</v>
       </c>
       <c r="O100">
-        <v>-536.733900346227</v>
+        <v>-545.8708534109845</v>
       </c>
       <c r="P100">
-        <v>-1610.201701038681</v>
+        <v>-1637.612560232953</v>
       </c>
       <c r="Q100">
-        <v>-1289.701701038681</v>
+        <v>-1317.112560232953</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.395272088907834</v>
+        <v>6.744744177815669</v>
       </c>
       <c r="T100">
-        <v>51.81526795562998</v>
+        <v>103.63053591126</v>
       </c>
       <c r="U100">
         <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1001448870501946</v>
+        <v>0.09913332253453608</v>
       </c>
       <c r="W100">
-        <v>0.1949364929667324</v>
+        <v>0.1951556291768337</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9793,91 +9793,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4005795482007785</v>
+        <v>0.3965332901381443</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2606515146632221</v>
-      </c>
-      <c r="C101">
-        <v>-8268.716376344521</v>
-      </c>
-      <c r="D101">
-        <v>7714.273623655481</v>
-      </c>
-      <c r="E101">
-        <v>5712.890000000001</v>
-      </c>
-      <c r="F101">
-        <v>16702.29</v>
-      </c>
-      <c r="G101">
-        <v>719.3</v>
-      </c>
-      <c r="H101">
-        <v>5881.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1755.25</v>
-      </c>
-      <c r="K101">
-        <v>320.5</v>
-      </c>
-      <c r="L101">
-        <v>1434.75</v>
-      </c>
-      <c r="M101">
-        <v>3618.233413643938</v>
-      </c>
-      <c r="N101">
-        <v>-2183.483413643938</v>
-      </c>
-      <c r="O101">
-        <v>-545.8708534109845</v>
-      </c>
-      <c r="P101">
-        <v>-1637.612560232953</v>
-      </c>
-      <c r="Q101">
-        <v>-1317.112560232953</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.744744177815669</v>
-      </c>
-      <c r="T101">
-        <v>103.63053591126</v>
-      </c>
-      <c r="U101">
-        <v>0.2166309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.09913332253453608</v>
-      </c>
-      <c r="W101">
-        <v>0.1951556291768337</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3965332901381443</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
